--- a/العون/نموذج_مشتريات_شهري.xlsx
+++ b/العون/نموذج_مشتريات_شهري.xlsx
@@ -16,7 +16,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="0">'الفواتير'!$A$1:$I$208</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'البنود'!$1:$6</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'البنود'!$A$1:$F$608</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'التعليمات'!$A$1:$B$24</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'التعليمات'!$A$1:$B$29</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -26,7 +26,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.000"/>
-    <numFmt numFmtId="165" formatCode="DD/MM/YYYY"/>
+    <numFmt numFmtId="165" formatCode="00&quot;/&quot;00&quot;/&quot;0000"/>
   </numFmts>
   <fonts count="11">
     <font>
@@ -179,7 +179,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -241,6 +241,9 @@
     <xf numFmtId="0" fontId="6" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -257,7 +260,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="6">
+  <dxfs count="8">
     <dxf>
       <font>
         <name val="Arial"/>
@@ -318,9 +321,35 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <name val="Arial"/>
+        <b val="1"/>
+        <color rgb="00A11212"/>
+        <sz val="11"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="00FFD9A0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill patternType="solid">
           <bgColor rgb="00FBD5D5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <b val="1"/>
+        <color rgb="008A6A00"/>
+        <sz val="10"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="00FFF0C2"/>
         </patternFill>
       </fill>
     </dxf>
@@ -691,7 +720,7 @@
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
@@ -743,7 +772,7 @@
         <v/>
       </c>
       <c r="E4" s="7">
-        <f>IF(B4=0,"⛔ ما في فواتير مُدخلة",IF(COUNTIF(I7:I206,"⛔*")&gt;0,"⛔ في "&amp;COUNTIF(I7:I206,"⛔*")&amp;" فاتورة ناقصة","✅ كل الفواتير مكتملة"))</f>
+        <f>IF(B4=0,"⛔ ما في فواتير مُدخلة",IF(COUNTIF(I7:I206,"⛔*")+COUNTIF(I7:I206,"🟡*")&gt;0,"⛔ في "&amp;(COUNTIF(I7:I206,"⛔*")+COUNTIF(I7:I206,"🟡*"))&amp;" فاتورة ناقصة","✅ كل الفواتير مكتملة"))</f>
         <v/>
       </c>
     </row>
@@ -811,7 +840,7 @@
         <v/>
       </c>
       <c r="I7" s="15">
-        <f>IF(B7="","",IF(E7="","⛔ اختر النوع",IF(E7="مطبوعة","📷 مع الصورة",IF(D7="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D7,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D7,'البنود'!$F$7:$F$606)-N(F7),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F7)-SUMIF('البنود'!$B$7:$B$606,D7,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B7="","",IF(E7="","⛔ اختر النوع",IF(E7="مطبوعة","📷 مع الصورة",IF(D7="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D7,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D7,'البنود'!$F$7:$F$606)-N(F7),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F7)-SUMIF('البنود'!$B$7:$B$606,D7,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -831,7 +860,7 @@
         <v/>
       </c>
       <c r="I8" s="15">
-        <f>IF(B8="","",IF(E8="","⛔ اختر النوع",IF(E8="مطبوعة","📷 مع الصورة",IF(D8="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D8,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D8,'البنود'!$F$7:$F$606)-N(F8),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F8)-SUMIF('البنود'!$B$7:$B$606,D8,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B8="","",IF(E8="","⛔ اختر النوع",IF(E8="مطبوعة","📷 مع الصورة",IF(D8="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D8,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D8,'البنود'!$F$7:$F$606)-N(F8),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F8)-SUMIF('البنود'!$B$7:$B$606,D8,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -851,7 +880,7 @@
         <v/>
       </c>
       <c r="I9" s="15">
-        <f>IF(B9="","",IF(E9="","⛔ اختر النوع",IF(E9="مطبوعة","📷 مع الصورة",IF(D9="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D9,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D9,'البنود'!$F$7:$F$606)-N(F9),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F9)-SUMIF('البنود'!$B$7:$B$606,D9,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B9="","",IF(E9="","⛔ اختر النوع",IF(E9="مطبوعة","📷 مع الصورة",IF(D9="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D9,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D9,'البنود'!$F$7:$F$606)-N(F9),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F9)-SUMIF('البنود'!$B$7:$B$606,D9,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -871,7 +900,7 @@
         <v/>
       </c>
       <c r="I10" s="15">
-        <f>IF(B10="","",IF(E10="","⛔ اختر النوع",IF(E10="مطبوعة","📷 مع الصورة",IF(D10="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D10,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D10,'البنود'!$F$7:$F$606)-N(F10),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F10)-SUMIF('البنود'!$B$7:$B$606,D10,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B10="","",IF(E10="","⛔ اختر النوع",IF(E10="مطبوعة","📷 مع الصورة",IF(D10="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D10,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D10,'البنود'!$F$7:$F$606)-N(F10),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F10)-SUMIF('البنود'!$B$7:$B$606,D10,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -891,7 +920,7 @@
         <v/>
       </c>
       <c r="I11" s="15">
-        <f>IF(B11="","",IF(E11="","⛔ اختر النوع",IF(E11="مطبوعة","📷 مع الصورة",IF(D11="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D11,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D11,'البنود'!$F$7:$F$606)-N(F11),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F11)-SUMIF('البنود'!$B$7:$B$606,D11,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B11="","",IF(E11="","⛔ اختر النوع",IF(E11="مطبوعة","📷 مع الصورة",IF(D11="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D11,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D11,'البنود'!$F$7:$F$606)-N(F11),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F11)-SUMIF('البنود'!$B$7:$B$606,D11,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -911,7 +940,7 @@
         <v/>
       </c>
       <c r="I12" s="15">
-        <f>IF(B12="","",IF(E12="","⛔ اختر النوع",IF(E12="مطبوعة","📷 مع الصورة",IF(D12="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D12,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D12,'البنود'!$F$7:$F$606)-N(F12),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F12)-SUMIF('البنود'!$B$7:$B$606,D12,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B12="","",IF(E12="","⛔ اختر النوع",IF(E12="مطبوعة","📷 مع الصورة",IF(D12="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D12,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D12,'البنود'!$F$7:$F$606)-N(F12),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F12)-SUMIF('البنود'!$B$7:$B$606,D12,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -931,7 +960,7 @@
         <v/>
       </c>
       <c r="I13" s="15">
-        <f>IF(B13="","",IF(E13="","⛔ اختر النوع",IF(E13="مطبوعة","📷 مع الصورة",IF(D13="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D13,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D13,'البنود'!$F$7:$F$606)-N(F13),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F13)-SUMIF('البنود'!$B$7:$B$606,D13,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B13="","",IF(E13="","⛔ اختر النوع",IF(E13="مطبوعة","📷 مع الصورة",IF(D13="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D13,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D13,'البنود'!$F$7:$F$606)-N(F13),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F13)-SUMIF('البنود'!$B$7:$B$606,D13,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -951,7 +980,7 @@
         <v/>
       </c>
       <c r="I14" s="15">
-        <f>IF(B14="","",IF(E14="","⛔ اختر النوع",IF(E14="مطبوعة","📷 مع الصورة",IF(D14="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D14,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D14,'البنود'!$F$7:$F$606)-N(F14),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F14)-SUMIF('البنود'!$B$7:$B$606,D14,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B14="","",IF(E14="","⛔ اختر النوع",IF(E14="مطبوعة","📷 مع الصورة",IF(D14="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D14,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D14,'البنود'!$F$7:$F$606)-N(F14),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F14)-SUMIF('البنود'!$B$7:$B$606,D14,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -971,7 +1000,7 @@
         <v/>
       </c>
       <c r="I15" s="15">
-        <f>IF(B15="","",IF(E15="","⛔ اختر النوع",IF(E15="مطبوعة","📷 مع الصورة",IF(D15="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D15,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D15,'البنود'!$F$7:$F$606)-N(F15),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F15)-SUMIF('البنود'!$B$7:$B$606,D15,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B15="","",IF(E15="","⛔ اختر النوع",IF(E15="مطبوعة","📷 مع الصورة",IF(D15="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D15,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D15,'البنود'!$F$7:$F$606)-N(F15),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F15)-SUMIF('البنود'!$B$7:$B$606,D15,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -991,7 +1020,7 @@
         <v/>
       </c>
       <c r="I16" s="15">
-        <f>IF(B16="","",IF(E16="","⛔ اختر النوع",IF(E16="مطبوعة","📷 مع الصورة",IF(D16="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D16,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D16,'البنود'!$F$7:$F$606)-N(F16),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F16)-SUMIF('البنود'!$B$7:$B$606,D16,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B16="","",IF(E16="","⛔ اختر النوع",IF(E16="مطبوعة","📷 مع الصورة",IF(D16="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D16,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D16,'البنود'!$F$7:$F$606)-N(F16),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F16)-SUMIF('البنود'!$B$7:$B$606,D16,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -1011,7 +1040,7 @@
         <v/>
       </c>
       <c r="I17" s="15">
-        <f>IF(B17="","",IF(E17="","⛔ اختر النوع",IF(E17="مطبوعة","📷 مع الصورة",IF(D17="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D17,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D17,'البنود'!$F$7:$F$606)-N(F17),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F17)-SUMIF('البنود'!$B$7:$B$606,D17,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B17="","",IF(E17="","⛔ اختر النوع",IF(E17="مطبوعة","📷 مع الصورة",IF(D17="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D17,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D17,'البنود'!$F$7:$F$606)-N(F17),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F17)-SUMIF('البنود'!$B$7:$B$606,D17,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -1031,7 +1060,7 @@
         <v/>
       </c>
       <c r="I18" s="15">
-        <f>IF(B18="","",IF(E18="","⛔ اختر النوع",IF(E18="مطبوعة","📷 مع الصورة",IF(D18="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D18,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D18,'البنود'!$F$7:$F$606)-N(F18),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F18)-SUMIF('البنود'!$B$7:$B$606,D18,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B18="","",IF(E18="","⛔ اختر النوع",IF(E18="مطبوعة","📷 مع الصورة",IF(D18="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D18,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D18,'البنود'!$F$7:$F$606)-N(F18),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F18)-SUMIF('البنود'!$B$7:$B$606,D18,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -1051,7 +1080,7 @@
         <v/>
       </c>
       <c r="I19" s="15">
-        <f>IF(B19="","",IF(E19="","⛔ اختر النوع",IF(E19="مطبوعة","📷 مع الصورة",IF(D19="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D19,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D19,'البنود'!$F$7:$F$606)-N(F19),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F19)-SUMIF('البنود'!$B$7:$B$606,D19,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B19="","",IF(E19="","⛔ اختر النوع",IF(E19="مطبوعة","📷 مع الصورة",IF(D19="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D19,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D19,'البنود'!$F$7:$F$606)-N(F19),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F19)-SUMIF('البنود'!$B$7:$B$606,D19,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -1071,7 +1100,7 @@
         <v/>
       </c>
       <c r="I20" s="15">
-        <f>IF(B20="","",IF(E20="","⛔ اختر النوع",IF(E20="مطبوعة","📷 مع الصورة",IF(D20="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D20,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D20,'البنود'!$F$7:$F$606)-N(F20),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F20)-SUMIF('البنود'!$B$7:$B$606,D20,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B20="","",IF(E20="","⛔ اختر النوع",IF(E20="مطبوعة","📷 مع الصورة",IF(D20="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D20,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D20,'البنود'!$F$7:$F$606)-N(F20),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F20)-SUMIF('البنود'!$B$7:$B$606,D20,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -1091,7 +1120,7 @@
         <v/>
       </c>
       <c r="I21" s="15">
-        <f>IF(B21="","",IF(E21="","⛔ اختر النوع",IF(E21="مطبوعة","📷 مع الصورة",IF(D21="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D21,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D21,'البنود'!$F$7:$F$606)-N(F21),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F21)-SUMIF('البنود'!$B$7:$B$606,D21,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B21="","",IF(E21="","⛔ اختر النوع",IF(E21="مطبوعة","📷 مع الصورة",IF(D21="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D21,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D21,'البنود'!$F$7:$F$606)-N(F21),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F21)-SUMIF('البنود'!$B$7:$B$606,D21,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -1111,7 +1140,7 @@
         <v/>
       </c>
       <c r="I22" s="15">
-        <f>IF(B22="","",IF(E22="","⛔ اختر النوع",IF(E22="مطبوعة","📷 مع الصورة",IF(D22="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D22,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D22,'البنود'!$F$7:$F$606)-N(F22),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F22)-SUMIF('البنود'!$B$7:$B$606,D22,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B22="","",IF(E22="","⛔ اختر النوع",IF(E22="مطبوعة","📷 مع الصورة",IF(D22="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D22,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D22,'البنود'!$F$7:$F$606)-N(F22),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F22)-SUMIF('البنود'!$B$7:$B$606,D22,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -1131,7 +1160,7 @@
         <v/>
       </c>
       <c r="I23" s="15">
-        <f>IF(B23="","",IF(E23="","⛔ اختر النوع",IF(E23="مطبوعة","📷 مع الصورة",IF(D23="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D23,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D23,'البنود'!$F$7:$F$606)-N(F23),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F23)-SUMIF('البنود'!$B$7:$B$606,D23,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B23="","",IF(E23="","⛔ اختر النوع",IF(E23="مطبوعة","📷 مع الصورة",IF(D23="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D23,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D23,'البنود'!$F$7:$F$606)-N(F23),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F23)-SUMIF('البنود'!$B$7:$B$606,D23,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -1151,7 +1180,7 @@
         <v/>
       </c>
       <c r="I24" s="15">
-        <f>IF(B24="","",IF(E24="","⛔ اختر النوع",IF(E24="مطبوعة","📷 مع الصورة",IF(D24="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D24,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D24,'البنود'!$F$7:$F$606)-N(F24),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F24)-SUMIF('البنود'!$B$7:$B$606,D24,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B24="","",IF(E24="","⛔ اختر النوع",IF(E24="مطبوعة","📷 مع الصورة",IF(D24="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D24,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D24,'البنود'!$F$7:$F$606)-N(F24),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F24)-SUMIF('البنود'!$B$7:$B$606,D24,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -1171,7 +1200,7 @@
         <v/>
       </c>
       <c r="I25" s="15">
-        <f>IF(B25="","",IF(E25="","⛔ اختر النوع",IF(E25="مطبوعة","📷 مع الصورة",IF(D25="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D25,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D25,'البنود'!$F$7:$F$606)-N(F25),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F25)-SUMIF('البنود'!$B$7:$B$606,D25,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B25="","",IF(E25="","⛔ اختر النوع",IF(E25="مطبوعة","📷 مع الصورة",IF(D25="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D25,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D25,'البنود'!$F$7:$F$606)-N(F25),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F25)-SUMIF('البنود'!$B$7:$B$606,D25,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -1191,7 +1220,7 @@
         <v/>
       </c>
       <c r="I26" s="15">
-        <f>IF(B26="","",IF(E26="","⛔ اختر النوع",IF(E26="مطبوعة","📷 مع الصورة",IF(D26="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D26,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D26,'البنود'!$F$7:$F$606)-N(F26),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F26)-SUMIF('البنود'!$B$7:$B$606,D26,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B26="","",IF(E26="","⛔ اختر النوع",IF(E26="مطبوعة","📷 مع الصورة",IF(D26="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D26,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D26,'البنود'!$F$7:$F$606)-N(F26),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F26)-SUMIF('البنود'!$B$7:$B$606,D26,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -1211,7 +1240,7 @@
         <v/>
       </c>
       <c r="I27" s="15">
-        <f>IF(B27="","",IF(E27="","⛔ اختر النوع",IF(E27="مطبوعة","📷 مع الصورة",IF(D27="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D27,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D27,'البنود'!$F$7:$F$606)-N(F27),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F27)-SUMIF('البنود'!$B$7:$B$606,D27,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B27="","",IF(E27="","⛔ اختر النوع",IF(E27="مطبوعة","📷 مع الصورة",IF(D27="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D27,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D27,'البنود'!$F$7:$F$606)-N(F27),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F27)-SUMIF('البنود'!$B$7:$B$606,D27,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -1231,7 +1260,7 @@
         <v/>
       </c>
       <c r="I28" s="15">
-        <f>IF(B28="","",IF(E28="","⛔ اختر النوع",IF(E28="مطبوعة","📷 مع الصورة",IF(D28="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D28,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D28,'البنود'!$F$7:$F$606)-N(F28),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F28)-SUMIF('البنود'!$B$7:$B$606,D28,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B28="","",IF(E28="","⛔ اختر النوع",IF(E28="مطبوعة","📷 مع الصورة",IF(D28="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D28,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D28,'البنود'!$F$7:$F$606)-N(F28),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F28)-SUMIF('البنود'!$B$7:$B$606,D28,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -1251,7 +1280,7 @@
         <v/>
       </c>
       <c r="I29" s="15">
-        <f>IF(B29="","",IF(E29="","⛔ اختر النوع",IF(E29="مطبوعة","📷 مع الصورة",IF(D29="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D29,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D29,'البنود'!$F$7:$F$606)-N(F29),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F29)-SUMIF('البنود'!$B$7:$B$606,D29,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B29="","",IF(E29="","⛔ اختر النوع",IF(E29="مطبوعة","📷 مع الصورة",IF(D29="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D29,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D29,'البنود'!$F$7:$F$606)-N(F29),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F29)-SUMIF('البنود'!$B$7:$B$606,D29,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -1271,7 +1300,7 @@
         <v/>
       </c>
       <c r="I30" s="15">
-        <f>IF(B30="","",IF(E30="","⛔ اختر النوع",IF(E30="مطبوعة","📷 مع الصورة",IF(D30="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D30,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D30,'البنود'!$F$7:$F$606)-N(F30),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F30)-SUMIF('البنود'!$B$7:$B$606,D30,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B30="","",IF(E30="","⛔ اختر النوع",IF(E30="مطبوعة","📷 مع الصورة",IF(D30="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D30,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D30,'البنود'!$F$7:$F$606)-N(F30),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F30)-SUMIF('البنود'!$B$7:$B$606,D30,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -1291,7 +1320,7 @@
         <v/>
       </c>
       <c r="I31" s="15">
-        <f>IF(B31="","",IF(E31="","⛔ اختر النوع",IF(E31="مطبوعة","📷 مع الصورة",IF(D31="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D31,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D31,'البنود'!$F$7:$F$606)-N(F31),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F31)-SUMIF('البنود'!$B$7:$B$606,D31,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B31="","",IF(E31="","⛔ اختر النوع",IF(E31="مطبوعة","📷 مع الصورة",IF(D31="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D31,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D31,'البنود'!$F$7:$F$606)-N(F31),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F31)-SUMIF('البنود'!$B$7:$B$606,D31,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -1311,7 +1340,7 @@
         <v/>
       </c>
       <c r="I32" s="15">
-        <f>IF(B32="","",IF(E32="","⛔ اختر النوع",IF(E32="مطبوعة","📷 مع الصورة",IF(D32="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D32,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D32,'البنود'!$F$7:$F$606)-N(F32),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F32)-SUMIF('البنود'!$B$7:$B$606,D32,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B32="","",IF(E32="","⛔ اختر النوع",IF(E32="مطبوعة","📷 مع الصورة",IF(D32="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D32,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D32,'البنود'!$F$7:$F$606)-N(F32),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F32)-SUMIF('البنود'!$B$7:$B$606,D32,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -1331,7 +1360,7 @@
         <v/>
       </c>
       <c r="I33" s="15">
-        <f>IF(B33="","",IF(E33="","⛔ اختر النوع",IF(E33="مطبوعة","📷 مع الصورة",IF(D33="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D33,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D33,'البنود'!$F$7:$F$606)-N(F33),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F33)-SUMIF('البنود'!$B$7:$B$606,D33,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B33="","",IF(E33="","⛔ اختر النوع",IF(E33="مطبوعة","📷 مع الصورة",IF(D33="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D33,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D33,'البنود'!$F$7:$F$606)-N(F33),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F33)-SUMIF('البنود'!$B$7:$B$606,D33,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -1351,7 +1380,7 @@
         <v/>
       </c>
       <c r="I34" s="15">
-        <f>IF(B34="","",IF(E34="","⛔ اختر النوع",IF(E34="مطبوعة","📷 مع الصورة",IF(D34="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D34,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D34,'البنود'!$F$7:$F$606)-N(F34),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F34)-SUMIF('البنود'!$B$7:$B$606,D34,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B34="","",IF(E34="","⛔ اختر النوع",IF(E34="مطبوعة","📷 مع الصورة",IF(D34="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D34,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D34,'البنود'!$F$7:$F$606)-N(F34),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F34)-SUMIF('البنود'!$B$7:$B$606,D34,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -1371,7 +1400,7 @@
         <v/>
       </c>
       <c r="I35" s="15">
-        <f>IF(B35="","",IF(E35="","⛔ اختر النوع",IF(E35="مطبوعة","📷 مع الصورة",IF(D35="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D35,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D35,'البنود'!$F$7:$F$606)-N(F35),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F35)-SUMIF('البنود'!$B$7:$B$606,D35,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B35="","",IF(E35="","⛔ اختر النوع",IF(E35="مطبوعة","📷 مع الصورة",IF(D35="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D35,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D35,'البنود'!$F$7:$F$606)-N(F35),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F35)-SUMIF('البنود'!$B$7:$B$606,D35,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -1391,7 +1420,7 @@
         <v/>
       </c>
       <c r="I36" s="15">
-        <f>IF(B36="","",IF(E36="","⛔ اختر النوع",IF(E36="مطبوعة","📷 مع الصورة",IF(D36="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D36,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D36,'البنود'!$F$7:$F$606)-N(F36),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F36)-SUMIF('البنود'!$B$7:$B$606,D36,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B36="","",IF(E36="","⛔ اختر النوع",IF(E36="مطبوعة","📷 مع الصورة",IF(D36="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D36,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D36,'البنود'!$F$7:$F$606)-N(F36),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F36)-SUMIF('البنود'!$B$7:$B$606,D36,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -1411,7 +1440,7 @@
         <v/>
       </c>
       <c r="I37" s="15">
-        <f>IF(B37="","",IF(E37="","⛔ اختر النوع",IF(E37="مطبوعة","📷 مع الصورة",IF(D37="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D37,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D37,'البنود'!$F$7:$F$606)-N(F37),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F37)-SUMIF('البنود'!$B$7:$B$606,D37,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B37="","",IF(E37="","⛔ اختر النوع",IF(E37="مطبوعة","📷 مع الصورة",IF(D37="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D37,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D37,'البنود'!$F$7:$F$606)-N(F37),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F37)-SUMIF('البنود'!$B$7:$B$606,D37,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -1431,7 +1460,7 @@
         <v/>
       </c>
       <c r="I38" s="15">
-        <f>IF(B38="","",IF(E38="","⛔ اختر النوع",IF(E38="مطبوعة","📷 مع الصورة",IF(D38="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D38,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D38,'البنود'!$F$7:$F$606)-N(F38),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F38)-SUMIF('البنود'!$B$7:$B$606,D38,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B38="","",IF(E38="","⛔ اختر النوع",IF(E38="مطبوعة","📷 مع الصورة",IF(D38="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D38,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D38,'البنود'!$F$7:$F$606)-N(F38),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F38)-SUMIF('البنود'!$B$7:$B$606,D38,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -1451,7 +1480,7 @@
         <v/>
       </c>
       <c r="I39" s="15">
-        <f>IF(B39="","",IF(E39="","⛔ اختر النوع",IF(E39="مطبوعة","📷 مع الصورة",IF(D39="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D39,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D39,'البنود'!$F$7:$F$606)-N(F39),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F39)-SUMIF('البنود'!$B$7:$B$606,D39,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B39="","",IF(E39="","⛔ اختر النوع",IF(E39="مطبوعة","📷 مع الصورة",IF(D39="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D39,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D39,'البنود'!$F$7:$F$606)-N(F39),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F39)-SUMIF('البنود'!$B$7:$B$606,D39,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -1471,7 +1500,7 @@
         <v/>
       </c>
       <c r="I40" s="15">
-        <f>IF(B40="","",IF(E40="","⛔ اختر النوع",IF(E40="مطبوعة","📷 مع الصورة",IF(D40="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D40,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D40,'البنود'!$F$7:$F$606)-N(F40),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F40)-SUMIF('البنود'!$B$7:$B$606,D40,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B40="","",IF(E40="","⛔ اختر النوع",IF(E40="مطبوعة","📷 مع الصورة",IF(D40="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D40,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D40,'البنود'!$F$7:$F$606)-N(F40),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F40)-SUMIF('البنود'!$B$7:$B$606,D40,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -1491,7 +1520,7 @@
         <v/>
       </c>
       <c r="I41" s="15">
-        <f>IF(B41="","",IF(E41="","⛔ اختر النوع",IF(E41="مطبوعة","📷 مع الصورة",IF(D41="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D41,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D41,'البنود'!$F$7:$F$606)-N(F41),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F41)-SUMIF('البنود'!$B$7:$B$606,D41,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B41="","",IF(E41="","⛔ اختر النوع",IF(E41="مطبوعة","📷 مع الصورة",IF(D41="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D41,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D41,'البنود'!$F$7:$F$606)-N(F41),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F41)-SUMIF('البنود'!$B$7:$B$606,D41,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -1511,7 +1540,7 @@
         <v/>
       </c>
       <c r="I42" s="15">
-        <f>IF(B42="","",IF(E42="","⛔ اختر النوع",IF(E42="مطبوعة","📷 مع الصورة",IF(D42="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D42,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D42,'البنود'!$F$7:$F$606)-N(F42),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F42)-SUMIF('البنود'!$B$7:$B$606,D42,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B42="","",IF(E42="","⛔ اختر النوع",IF(E42="مطبوعة","📷 مع الصورة",IF(D42="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D42,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D42,'البنود'!$F$7:$F$606)-N(F42),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F42)-SUMIF('البنود'!$B$7:$B$606,D42,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -1531,7 +1560,7 @@
         <v/>
       </c>
       <c r="I43" s="15">
-        <f>IF(B43="","",IF(E43="","⛔ اختر النوع",IF(E43="مطبوعة","📷 مع الصورة",IF(D43="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D43,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D43,'البنود'!$F$7:$F$606)-N(F43),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F43)-SUMIF('البنود'!$B$7:$B$606,D43,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B43="","",IF(E43="","⛔ اختر النوع",IF(E43="مطبوعة","📷 مع الصورة",IF(D43="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D43,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D43,'البنود'!$F$7:$F$606)-N(F43),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F43)-SUMIF('البنود'!$B$7:$B$606,D43,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -1551,7 +1580,7 @@
         <v/>
       </c>
       <c r="I44" s="15">
-        <f>IF(B44="","",IF(E44="","⛔ اختر النوع",IF(E44="مطبوعة","📷 مع الصورة",IF(D44="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D44,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D44,'البنود'!$F$7:$F$606)-N(F44),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F44)-SUMIF('البنود'!$B$7:$B$606,D44,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B44="","",IF(E44="","⛔ اختر النوع",IF(E44="مطبوعة","📷 مع الصورة",IF(D44="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D44,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D44,'البنود'!$F$7:$F$606)-N(F44),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F44)-SUMIF('البنود'!$B$7:$B$606,D44,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -1571,7 +1600,7 @@
         <v/>
       </c>
       <c r="I45" s="15">
-        <f>IF(B45="","",IF(E45="","⛔ اختر النوع",IF(E45="مطبوعة","📷 مع الصورة",IF(D45="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D45,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D45,'البنود'!$F$7:$F$606)-N(F45),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F45)-SUMIF('البنود'!$B$7:$B$606,D45,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B45="","",IF(E45="","⛔ اختر النوع",IF(E45="مطبوعة","📷 مع الصورة",IF(D45="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D45,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D45,'البنود'!$F$7:$F$606)-N(F45),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F45)-SUMIF('البنود'!$B$7:$B$606,D45,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -1591,7 +1620,7 @@
         <v/>
       </c>
       <c r="I46" s="15">
-        <f>IF(B46="","",IF(E46="","⛔ اختر النوع",IF(E46="مطبوعة","📷 مع الصورة",IF(D46="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D46,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D46,'البنود'!$F$7:$F$606)-N(F46),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F46)-SUMIF('البنود'!$B$7:$B$606,D46,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B46="","",IF(E46="","⛔ اختر النوع",IF(E46="مطبوعة","📷 مع الصورة",IF(D46="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D46,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D46,'البنود'!$F$7:$F$606)-N(F46),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F46)-SUMIF('البنود'!$B$7:$B$606,D46,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -1611,7 +1640,7 @@
         <v/>
       </c>
       <c r="I47" s="15">
-        <f>IF(B47="","",IF(E47="","⛔ اختر النوع",IF(E47="مطبوعة","📷 مع الصورة",IF(D47="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D47,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D47,'البنود'!$F$7:$F$606)-N(F47),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F47)-SUMIF('البنود'!$B$7:$B$606,D47,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B47="","",IF(E47="","⛔ اختر النوع",IF(E47="مطبوعة","📷 مع الصورة",IF(D47="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D47,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D47,'البنود'!$F$7:$F$606)-N(F47),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F47)-SUMIF('البنود'!$B$7:$B$606,D47,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -1631,7 +1660,7 @@
         <v/>
       </c>
       <c r="I48" s="15">
-        <f>IF(B48="","",IF(E48="","⛔ اختر النوع",IF(E48="مطبوعة","📷 مع الصورة",IF(D48="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D48,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D48,'البنود'!$F$7:$F$606)-N(F48),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F48)-SUMIF('البنود'!$B$7:$B$606,D48,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B48="","",IF(E48="","⛔ اختر النوع",IF(E48="مطبوعة","📷 مع الصورة",IF(D48="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D48,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D48,'البنود'!$F$7:$F$606)-N(F48),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F48)-SUMIF('البنود'!$B$7:$B$606,D48,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -1651,7 +1680,7 @@
         <v/>
       </c>
       <c r="I49" s="15">
-        <f>IF(B49="","",IF(E49="","⛔ اختر النوع",IF(E49="مطبوعة","📷 مع الصورة",IF(D49="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D49,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D49,'البنود'!$F$7:$F$606)-N(F49),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F49)-SUMIF('البنود'!$B$7:$B$606,D49,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B49="","",IF(E49="","⛔ اختر النوع",IF(E49="مطبوعة","📷 مع الصورة",IF(D49="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D49,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D49,'البنود'!$F$7:$F$606)-N(F49),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F49)-SUMIF('البنود'!$B$7:$B$606,D49,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -1671,7 +1700,7 @@
         <v/>
       </c>
       <c r="I50" s="15">
-        <f>IF(B50="","",IF(E50="","⛔ اختر النوع",IF(E50="مطبوعة","📷 مع الصورة",IF(D50="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D50,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D50,'البنود'!$F$7:$F$606)-N(F50),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F50)-SUMIF('البنود'!$B$7:$B$606,D50,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B50="","",IF(E50="","⛔ اختر النوع",IF(E50="مطبوعة","📷 مع الصورة",IF(D50="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D50,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D50,'البنود'!$F$7:$F$606)-N(F50),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F50)-SUMIF('البنود'!$B$7:$B$606,D50,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -1691,7 +1720,7 @@
         <v/>
       </c>
       <c r="I51" s="15">
-        <f>IF(B51="","",IF(E51="","⛔ اختر النوع",IF(E51="مطبوعة","📷 مع الصورة",IF(D51="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D51,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D51,'البنود'!$F$7:$F$606)-N(F51),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F51)-SUMIF('البنود'!$B$7:$B$606,D51,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B51="","",IF(E51="","⛔ اختر النوع",IF(E51="مطبوعة","📷 مع الصورة",IF(D51="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D51,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D51,'البنود'!$F$7:$F$606)-N(F51),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F51)-SUMIF('البنود'!$B$7:$B$606,D51,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -1711,7 +1740,7 @@
         <v/>
       </c>
       <c r="I52" s="15">
-        <f>IF(B52="","",IF(E52="","⛔ اختر النوع",IF(E52="مطبوعة","📷 مع الصورة",IF(D52="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D52,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D52,'البنود'!$F$7:$F$606)-N(F52),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F52)-SUMIF('البنود'!$B$7:$B$606,D52,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B52="","",IF(E52="","⛔ اختر النوع",IF(E52="مطبوعة","📷 مع الصورة",IF(D52="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D52,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D52,'البنود'!$F$7:$F$606)-N(F52),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F52)-SUMIF('البنود'!$B$7:$B$606,D52,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -1731,7 +1760,7 @@
         <v/>
       </c>
       <c r="I53" s="15">
-        <f>IF(B53="","",IF(E53="","⛔ اختر النوع",IF(E53="مطبوعة","📷 مع الصورة",IF(D53="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D53,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D53,'البنود'!$F$7:$F$606)-N(F53),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F53)-SUMIF('البنود'!$B$7:$B$606,D53,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B53="","",IF(E53="","⛔ اختر النوع",IF(E53="مطبوعة","📷 مع الصورة",IF(D53="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D53,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D53,'البنود'!$F$7:$F$606)-N(F53),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F53)-SUMIF('البنود'!$B$7:$B$606,D53,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -1751,7 +1780,7 @@
         <v/>
       </c>
       <c r="I54" s="15">
-        <f>IF(B54="","",IF(E54="","⛔ اختر النوع",IF(E54="مطبوعة","📷 مع الصورة",IF(D54="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D54,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D54,'البنود'!$F$7:$F$606)-N(F54),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F54)-SUMIF('البنود'!$B$7:$B$606,D54,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B54="","",IF(E54="","⛔ اختر النوع",IF(E54="مطبوعة","📷 مع الصورة",IF(D54="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D54,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D54,'البنود'!$F$7:$F$606)-N(F54),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F54)-SUMIF('البنود'!$B$7:$B$606,D54,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -1771,7 +1800,7 @@
         <v/>
       </c>
       <c r="I55" s="15">
-        <f>IF(B55="","",IF(E55="","⛔ اختر النوع",IF(E55="مطبوعة","📷 مع الصورة",IF(D55="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D55,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D55,'البنود'!$F$7:$F$606)-N(F55),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F55)-SUMIF('البنود'!$B$7:$B$606,D55,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B55="","",IF(E55="","⛔ اختر النوع",IF(E55="مطبوعة","📷 مع الصورة",IF(D55="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D55,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D55,'البنود'!$F$7:$F$606)-N(F55),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F55)-SUMIF('البنود'!$B$7:$B$606,D55,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -1791,7 +1820,7 @@
         <v/>
       </c>
       <c r="I56" s="15">
-        <f>IF(B56="","",IF(E56="","⛔ اختر النوع",IF(E56="مطبوعة","📷 مع الصورة",IF(D56="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D56,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D56,'البنود'!$F$7:$F$606)-N(F56),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F56)-SUMIF('البنود'!$B$7:$B$606,D56,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B56="","",IF(E56="","⛔ اختر النوع",IF(E56="مطبوعة","📷 مع الصورة",IF(D56="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D56,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D56,'البنود'!$F$7:$F$606)-N(F56),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F56)-SUMIF('البنود'!$B$7:$B$606,D56,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -1811,7 +1840,7 @@
         <v/>
       </c>
       <c r="I57" s="15">
-        <f>IF(B57="","",IF(E57="","⛔ اختر النوع",IF(E57="مطبوعة","📷 مع الصورة",IF(D57="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D57,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D57,'البنود'!$F$7:$F$606)-N(F57),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F57)-SUMIF('البنود'!$B$7:$B$606,D57,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B57="","",IF(E57="","⛔ اختر النوع",IF(E57="مطبوعة","📷 مع الصورة",IF(D57="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D57,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D57,'البنود'!$F$7:$F$606)-N(F57),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F57)-SUMIF('البنود'!$B$7:$B$606,D57,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -1831,7 +1860,7 @@
         <v/>
       </c>
       <c r="I58" s="15">
-        <f>IF(B58="","",IF(E58="","⛔ اختر النوع",IF(E58="مطبوعة","📷 مع الصورة",IF(D58="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D58,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D58,'البنود'!$F$7:$F$606)-N(F58),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F58)-SUMIF('البنود'!$B$7:$B$606,D58,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B58="","",IF(E58="","⛔ اختر النوع",IF(E58="مطبوعة","📷 مع الصورة",IF(D58="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D58,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D58,'البنود'!$F$7:$F$606)-N(F58),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F58)-SUMIF('البنود'!$B$7:$B$606,D58,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -1851,7 +1880,7 @@
         <v/>
       </c>
       <c r="I59" s="15">
-        <f>IF(B59="","",IF(E59="","⛔ اختر النوع",IF(E59="مطبوعة","📷 مع الصورة",IF(D59="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D59,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D59,'البنود'!$F$7:$F$606)-N(F59),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F59)-SUMIF('البنود'!$B$7:$B$606,D59,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B59="","",IF(E59="","⛔ اختر النوع",IF(E59="مطبوعة","📷 مع الصورة",IF(D59="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D59,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D59,'البنود'!$F$7:$F$606)-N(F59),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F59)-SUMIF('البنود'!$B$7:$B$606,D59,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -1871,7 +1900,7 @@
         <v/>
       </c>
       <c r="I60" s="15">
-        <f>IF(B60="","",IF(E60="","⛔ اختر النوع",IF(E60="مطبوعة","📷 مع الصورة",IF(D60="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D60,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D60,'البنود'!$F$7:$F$606)-N(F60),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F60)-SUMIF('البنود'!$B$7:$B$606,D60,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B60="","",IF(E60="","⛔ اختر النوع",IF(E60="مطبوعة","📷 مع الصورة",IF(D60="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D60,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D60,'البنود'!$F$7:$F$606)-N(F60),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F60)-SUMIF('البنود'!$B$7:$B$606,D60,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -1891,7 +1920,7 @@
         <v/>
       </c>
       <c r="I61" s="15">
-        <f>IF(B61="","",IF(E61="","⛔ اختر النوع",IF(E61="مطبوعة","📷 مع الصورة",IF(D61="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D61,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D61,'البنود'!$F$7:$F$606)-N(F61),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F61)-SUMIF('البنود'!$B$7:$B$606,D61,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B61="","",IF(E61="","⛔ اختر النوع",IF(E61="مطبوعة","📷 مع الصورة",IF(D61="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D61,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D61,'البنود'!$F$7:$F$606)-N(F61),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F61)-SUMIF('البنود'!$B$7:$B$606,D61,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -1911,7 +1940,7 @@
         <v/>
       </c>
       <c r="I62" s="15">
-        <f>IF(B62="","",IF(E62="","⛔ اختر النوع",IF(E62="مطبوعة","📷 مع الصورة",IF(D62="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D62,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D62,'البنود'!$F$7:$F$606)-N(F62),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F62)-SUMIF('البنود'!$B$7:$B$606,D62,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B62="","",IF(E62="","⛔ اختر النوع",IF(E62="مطبوعة","📷 مع الصورة",IF(D62="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D62,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D62,'البنود'!$F$7:$F$606)-N(F62),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F62)-SUMIF('البنود'!$B$7:$B$606,D62,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -1931,7 +1960,7 @@
         <v/>
       </c>
       <c r="I63" s="15">
-        <f>IF(B63="","",IF(E63="","⛔ اختر النوع",IF(E63="مطبوعة","📷 مع الصورة",IF(D63="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D63,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D63,'البنود'!$F$7:$F$606)-N(F63),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F63)-SUMIF('البنود'!$B$7:$B$606,D63,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B63="","",IF(E63="","⛔ اختر النوع",IF(E63="مطبوعة","📷 مع الصورة",IF(D63="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D63,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D63,'البنود'!$F$7:$F$606)-N(F63),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F63)-SUMIF('البنود'!$B$7:$B$606,D63,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -1951,7 +1980,7 @@
         <v/>
       </c>
       <c r="I64" s="15">
-        <f>IF(B64="","",IF(E64="","⛔ اختر النوع",IF(E64="مطبوعة","📷 مع الصورة",IF(D64="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D64,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D64,'البنود'!$F$7:$F$606)-N(F64),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F64)-SUMIF('البنود'!$B$7:$B$606,D64,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B64="","",IF(E64="","⛔ اختر النوع",IF(E64="مطبوعة","📷 مع الصورة",IF(D64="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D64,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D64,'البنود'!$F$7:$F$606)-N(F64),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F64)-SUMIF('البنود'!$B$7:$B$606,D64,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -1971,7 +2000,7 @@
         <v/>
       </c>
       <c r="I65" s="15">
-        <f>IF(B65="","",IF(E65="","⛔ اختر النوع",IF(E65="مطبوعة","📷 مع الصورة",IF(D65="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D65,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D65,'البنود'!$F$7:$F$606)-N(F65),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F65)-SUMIF('البنود'!$B$7:$B$606,D65,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B65="","",IF(E65="","⛔ اختر النوع",IF(E65="مطبوعة","📷 مع الصورة",IF(D65="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D65,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D65,'البنود'!$F$7:$F$606)-N(F65),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F65)-SUMIF('البنود'!$B$7:$B$606,D65,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -1991,7 +2020,7 @@
         <v/>
       </c>
       <c r="I66" s="15">
-        <f>IF(B66="","",IF(E66="","⛔ اختر النوع",IF(E66="مطبوعة","📷 مع الصورة",IF(D66="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D66,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D66,'البنود'!$F$7:$F$606)-N(F66),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F66)-SUMIF('البنود'!$B$7:$B$606,D66,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B66="","",IF(E66="","⛔ اختر النوع",IF(E66="مطبوعة","📷 مع الصورة",IF(D66="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D66,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D66,'البنود'!$F$7:$F$606)-N(F66),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F66)-SUMIF('البنود'!$B$7:$B$606,D66,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -2011,7 +2040,7 @@
         <v/>
       </c>
       <c r="I67" s="15">
-        <f>IF(B67="","",IF(E67="","⛔ اختر النوع",IF(E67="مطبوعة","📷 مع الصورة",IF(D67="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D67,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D67,'البنود'!$F$7:$F$606)-N(F67),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F67)-SUMIF('البنود'!$B$7:$B$606,D67,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B67="","",IF(E67="","⛔ اختر النوع",IF(E67="مطبوعة","📷 مع الصورة",IF(D67="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D67,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D67,'البنود'!$F$7:$F$606)-N(F67),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F67)-SUMIF('البنود'!$B$7:$B$606,D67,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -2031,7 +2060,7 @@
         <v/>
       </c>
       <c r="I68" s="15">
-        <f>IF(B68="","",IF(E68="","⛔ اختر النوع",IF(E68="مطبوعة","📷 مع الصورة",IF(D68="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D68,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D68,'البنود'!$F$7:$F$606)-N(F68),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F68)-SUMIF('البنود'!$B$7:$B$606,D68,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B68="","",IF(E68="","⛔ اختر النوع",IF(E68="مطبوعة","📷 مع الصورة",IF(D68="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D68,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D68,'البنود'!$F$7:$F$606)-N(F68),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F68)-SUMIF('البنود'!$B$7:$B$606,D68,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -2051,7 +2080,7 @@
         <v/>
       </c>
       <c r="I69" s="15">
-        <f>IF(B69="","",IF(E69="","⛔ اختر النوع",IF(E69="مطبوعة","📷 مع الصورة",IF(D69="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D69,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D69,'البنود'!$F$7:$F$606)-N(F69),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F69)-SUMIF('البنود'!$B$7:$B$606,D69,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B69="","",IF(E69="","⛔ اختر النوع",IF(E69="مطبوعة","📷 مع الصورة",IF(D69="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D69,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D69,'البنود'!$F$7:$F$606)-N(F69),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F69)-SUMIF('البنود'!$B$7:$B$606,D69,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -2071,7 +2100,7 @@
         <v/>
       </c>
       <c r="I70" s="15">
-        <f>IF(B70="","",IF(E70="","⛔ اختر النوع",IF(E70="مطبوعة","📷 مع الصورة",IF(D70="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D70,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D70,'البنود'!$F$7:$F$606)-N(F70),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F70)-SUMIF('البنود'!$B$7:$B$606,D70,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B70="","",IF(E70="","⛔ اختر النوع",IF(E70="مطبوعة","📷 مع الصورة",IF(D70="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D70,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D70,'البنود'!$F$7:$F$606)-N(F70),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F70)-SUMIF('البنود'!$B$7:$B$606,D70,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -2091,7 +2120,7 @@
         <v/>
       </c>
       <c r="I71" s="15">
-        <f>IF(B71="","",IF(E71="","⛔ اختر النوع",IF(E71="مطبوعة","📷 مع الصورة",IF(D71="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D71,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D71,'البنود'!$F$7:$F$606)-N(F71),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F71)-SUMIF('البنود'!$B$7:$B$606,D71,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B71="","",IF(E71="","⛔ اختر النوع",IF(E71="مطبوعة","📷 مع الصورة",IF(D71="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D71,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D71,'البنود'!$F$7:$F$606)-N(F71),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F71)-SUMIF('البنود'!$B$7:$B$606,D71,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -2111,7 +2140,7 @@
         <v/>
       </c>
       <c r="I72" s="15">
-        <f>IF(B72="","",IF(E72="","⛔ اختر النوع",IF(E72="مطبوعة","📷 مع الصورة",IF(D72="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D72,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D72,'البنود'!$F$7:$F$606)-N(F72),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F72)-SUMIF('البنود'!$B$7:$B$606,D72,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B72="","",IF(E72="","⛔ اختر النوع",IF(E72="مطبوعة","📷 مع الصورة",IF(D72="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D72,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D72,'البنود'!$F$7:$F$606)-N(F72),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F72)-SUMIF('البنود'!$B$7:$B$606,D72,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -2131,7 +2160,7 @@
         <v/>
       </c>
       <c r="I73" s="15">
-        <f>IF(B73="","",IF(E73="","⛔ اختر النوع",IF(E73="مطبوعة","📷 مع الصورة",IF(D73="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D73,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D73,'البنود'!$F$7:$F$606)-N(F73),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F73)-SUMIF('البنود'!$B$7:$B$606,D73,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B73="","",IF(E73="","⛔ اختر النوع",IF(E73="مطبوعة","📷 مع الصورة",IF(D73="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D73,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D73,'البنود'!$F$7:$F$606)-N(F73),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F73)-SUMIF('البنود'!$B$7:$B$606,D73,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -2151,7 +2180,7 @@
         <v/>
       </c>
       <c r="I74" s="15">
-        <f>IF(B74="","",IF(E74="","⛔ اختر النوع",IF(E74="مطبوعة","📷 مع الصورة",IF(D74="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D74,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D74,'البنود'!$F$7:$F$606)-N(F74),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F74)-SUMIF('البنود'!$B$7:$B$606,D74,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B74="","",IF(E74="","⛔ اختر النوع",IF(E74="مطبوعة","📷 مع الصورة",IF(D74="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D74,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D74,'البنود'!$F$7:$F$606)-N(F74),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F74)-SUMIF('البنود'!$B$7:$B$606,D74,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -2171,7 +2200,7 @@
         <v/>
       </c>
       <c r="I75" s="15">
-        <f>IF(B75="","",IF(E75="","⛔ اختر النوع",IF(E75="مطبوعة","📷 مع الصورة",IF(D75="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D75,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D75,'البنود'!$F$7:$F$606)-N(F75),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F75)-SUMIF('البنود'!$B$7:$B$606,D75,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B75="","",IF(E75="","⛔ اختر النوع",IF(E75="مطبوعة","📷 مع الصورة",IF(D75="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D75,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D75,'البنود'!$F$7:$F$606)-N(F75),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F75)-SUMIF('البنود'!$B$7:$B$606,D75,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -2191,7 +2220,7 @@
         <v/>
       </c>
       <c r="I76" s="15">
-        <f>IF(B76="","",IF(E76="","⛔ اختر النوع",IF(E76="مطبوعة","📷 مع الصورة",IF(D76="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D76,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D76,'البنود'!$F$7:$F$606)-N(F76),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F76)-SUMIF('البنود'!$B$7:$B$606,D76,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B76="","",IF(E76="","⛔ اختر النوع",IF(E76="مطبوعة","📷 مع الصورة",IF(D76="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D76,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D76,'البنود'!$F$7:$F$606)-N(F76),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F76)-SUMIF('البنود'!$B$7:$B$606,D76,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -2211,7 +2240,7 @@
         <v/>
       </c>
       <c r="I77" s="15">
-        <f>IF(B77="","",IF(E77="","⛔ اختر النوع",IF(E77="مطبوعة","📷 مع الصورة",IF(D77="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D77,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D77,'البنود'!$F$7:$F$606)-N(F77),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F77)-SUMIF('البنود'!$B$7:$B$606,D77,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B77="","",IF(E77="","⛔ اختر النوع",IF(E77="مطبوعة","📷 مع الصورة",IF(D77="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D77,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D77,'البنود'!$F$7:$F$606)-N(F77),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F77)-SUMIF('البنود'!$B$7:$B$606,D77,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -2231,7 +2260,7 @@
         <v/>
       </c>
       <c r="I78" s="15">
-        <f>IF(B78="","",IF(E78="","⛔ اختر النوع",IF(E78="مطبوعة","📷 مع الصورة",IF(D78="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D78,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D78,'البنود'!$F$7:$F$606)-N(F78),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F78)-SUMIF('البنود'!$B$7:$B$606,D78,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B78="","",IF(E78="","⛔ اختر النوع",IF(E78="مطبوعة","📷 مع الصورة",IF(D78="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D78,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D78,'البنود'!$F$7:$F$606)-N(F78),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F78)-SUMIF('البنود'!$B$7:$B$606,D78,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -2251,7 +2280,7 @@
         <v/>
       </c>
       <c r="I79" s="15">
-        <f>IF(B79="","",IF(E79="","⛔ اختر النوع",IF(E79="مطبوعة","📷 مع الصورة",IF(D79="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D79,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D79,'البنود'!$F$7:$F$606)-N(F79),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F79)-SUMIF('البنود'!$B$7:$B$606,D79,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B79="","",IF(E79="","⛔ اختر النوع",IF(E79="مطبوعة","📷 مع الصورة",IF(D79="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D79,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D79,'البنود'!$F$7:$F$606)-N(F79),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F79)-SUMIF('البنود'!$B$7:$B$606,D79,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -2271,7 +2300,7 @@
         <v/>
       </c>
       <c r="I80" s="15">
-        <f>IF(B80="","",IF(E80="","⛔ اختر النوع",IF(E80="مطبوعة","📷 مع الصورة",IF(D80="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D80,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D80,'البنود'!$F$7:$F$606)-N(F80),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F80)-SUMIF('البنود'!$B$7:$B$606,D80,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B80="","",IF(E80="","⛔ اختر النوع",IF(E80="مطبوعة","📷 مع الصورة",IF(D80="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D80,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D80,'البنود'!$F$7:$F$606)-N(F80),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F80)-SUMIF('البنود'!$B$7:$B$606,D80,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -2291,7 +2320,7 @@
         <v/>
       </c>
       <c r="I81" s="15">
-        <f>IF(B81="","",IF(E81="","⛔ اختر النوع",IF(E81="مطبوعة","📷 مع الصورة",IF(D81="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D81,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D81,'البنود'!$F$7:$F$606)-N(F81),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F81)-SUMIF('البنود'!$B$7:$B$606,D81,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B81="","",IF(E81="","⛔ اختر النوع",IF(E81="مطبوعة","📷 مع الصورة",IF(D81="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D81,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D81,'البنود'!$F$7:$F$606)-N(F81),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F81)-SUMIF('البنود'!$B$7:$B$606,D81,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -2311,7 +2340,7 @@
         <v/>
       </c>
       <c r="I82" s="15">
-        <f>IF(B82="","",IF(E82="","⛔ اختر النوع",IF(E82="مطبوعة","📷 مع الصورة",IF(D82="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D82,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D82,'البنود'!$F$7:$F$606)-N(F82),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F82)-SUMIF('البنود'!$B$7:$B$606,D82,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B82="","",IF(E82="","⛔ اختر النوع",IF(E82="مطبوعة","📷 مع الصورة",IF(D82="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D82,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D82,'البنود'!$F$7:$F$606)-N(F82),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F82)-SUMIF('البنود'!$B$7:$B$606,D82,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -2331,7 +2360,7 @@
         <v/>
       </c>
       <c r="I83" s="15">
-        <f>IF(B83="","",IF(E83="","⛔ اختر النوع",IF(E83="مطبوعة","📷 مع الصورة",IF(D83="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D83,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D83,'البنود'!$F$7:$F$606)-N(F83),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F83)-SUMIF('البنود'!$B$7:$B$606,D83,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B83="","",IF(E83="","⛔ اختر النوع",IF(E83="مطبوعة","📷 مع الصورة",IF(D83="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D83,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D83,'البنود'!$F$7:$F$606)-N(F83),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F83)-SUMIF('البنود'!$B$7:$B$606,D83,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -2351,7 +2380,7 @@
         <v/>
       </c>
       <c r="I84" s="15">
-        <f>IF(B84="","",IF(E84="","⛔ اختر النوع",IF(E84="مطبوعة","📷 مع الصورة",IF(D84="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D84,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D84,'البنود'!$F$7:$F$606)-N(F84),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F84)-SUMIF('البنود'!$B$7:$B$606,D84,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B84="","",IF(E84="","⛔ اختر النوع",IF(E84="مطبوعة","📷 مع الصورة",IF(D84="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D84,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D84,'البنود'!$F$7:$F$606)-N(F84),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F84)-SUMIF('البنود'!$B$7:$B$606,D84,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -2371,7 +2400,7 @@
         <v/>
       </c>
       <c r="I85" s="15">
-        <f>IF(B85="","",IF(E85="","⛔ اختر النوع",IF(E85="مطبوعة","📷 مع الصورة",IF(D85="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D85,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D85,'البنود'!$F$7:$F$606)-N(F85),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F85)-SUMIF('البنود'!$B$7:$B$606,D85,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B85="","",IF(E85="","⛔ اختر النوع",IF(E85="مطبوعة","📷 مع الصورة",IF(D85="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D85,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D85,'البنود'!$F$7:$F$606)-N(F85),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F85)-SUMIF('البنود'!$B$7:$B$606,D85,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -2391,7 +2420,7 @@
         <v/>
       </c>
       <c r="I86" s="15">
-        <f>IF(B86="","",IF(E86="","⛔ اختر النوع",IF(E86="مطبوعة","📷 مع الصورة",IF(D86="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D86,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D86,'البنود'!$F$7:$F$606)-N(F86),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F86)-SUMIF('البنود'!$B$7:$B$606,D86,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B86="","",IF(E86="","⛔ اختر النوع",IF(E86="مطبوعة","📷 مع الصورة",IF(D86="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D86,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D86,'البنود'!$F$7:$F$606)-N(F86),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F86)-SUMIF('البنود'!$B$7:$B$606,D86,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -2411,7 +2440,7 @@
         <v/>
       </c>
       <c r="I87" s="15">
-        <f>IF(B87="","",IF(E87="","⛔ اختر النوع",IF(E87="مطبوعة","📷 مع الصورة",IF(D87="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D87,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D87,'البنود'!$F$7:$F$606)-N(F87),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F87)-SUMIF('البنود'!$B$7:$B$606,D87,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B87="","",IF(E87="","⛔ اختر النوع",IF(E87="مطبوعة","📷 مع الصورة",IF(D87="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D87,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D87,'البنود'!$F$7:$F$606)-N(F87),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F87)-SUMIF('البنود'!$B$7:$B$606,D87,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -2431,7 +2460,7 @@
         <v/>
       </c>
       <c r="I88" s="15">
-        <f>IF(B88="","",IF(E88="","⛔ اختر النوع",IF(E88="مطبوعة","📷 مع الصورة",IF(D88="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D88,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D88,'البنود'!$F$7:$F$606)-N(F88),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F88)-SUMIF('البنود'!$B$7:$B$606,D88,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B88="","",IF(E88="","⛔ اختر النوع",IF(E88="مطبوعة","📷 مع الصورة",IF(D88="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D88,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D88,'البنود'!$F$7:$F$606)-N(F88),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F88)-SUMIF('البنود'!$B$7:$B$606,D88,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -2451,7 +2480,7 @@
         <v/>
       </c>
       <c r="I89" s="15">
-        <f>IF(B89="","",IF(E89="","⛔ اختر النوع",IF(E89="مطبوعة","📷 مع الصورة",IF(D89="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D89,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D89,'البنود'!$F$7:$F$606)-N(F89),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F89)-SUMIF('البنود'!$B$7:$B$606,D89,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B89="","",IF(E89="","⛔ اختر النوع",IF(E89="مطبوعة","📷 مع الصورة",IF(D89="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D89,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D89,'البنود'!$F$7:$F$606)-N(F89),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F89)-SUMIF('البنود'!$B$7:$B$606,D89,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -2471,7 +2500,7 @@
         <v/>
       </c>
       <c r="I90" s="15">
-        <f>IF(B90="","",IF(E90="","⛔ اختر النوع",IF(E90="مطبوعة","📷 مع الصورة",IF(D90="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D90,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D90,'البنود'!$F$7:$F$606)-N(F90),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F90)-SUMIF('البنود'!$B$7:$B$606,D90,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B90="","",IF(E90="","⛔ اختر النوع",IF(E90="مطبوعة","📷 مع الصورة",IF(D90="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D90,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D90,'البنود'!$F$7:$F$606)-N(F90),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F90)-SUMIF('البنود'!$B$7:$B$606,D90,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -2491,7 +2520,7 @@
         <v/>
       </c>
       <c r="I91" s="15">
-        <f>IF(B91="","",IF(E91="","⛔ اختر النوع",IF(E91="مطبوعة","📷 مع الصورة",IF(D91="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D91,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D91,'البنود'!$F$7:$F$606)-N(F91),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F91)-SUMIF('البنود'!$B$7:$B$606,D91,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B91="","",IF(E91="","⛔ اختر النوع",IF(E91="مطبوعة","📷 مع الصورة",IF(D91="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D91,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D91,'البنود'!$F$7:$F$606)-N(F91),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F91)-SUMIF('البنود'!$B$7:$B$606,D91,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -2511,7 +2540,7 @@
         <v/>
       </c>
       <c r="I92" s="15">
-        <f>IF(B92="","",IF(E92="","⛔ اختر النوع",IF(E92="مطبوعة","📷 مع الصورة",IF(D92="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D92,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D92,'البنود'!$F$7:$F$606)-N(F92),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F92)-SUMIF('البنود'!$B$7:$B$606,D92,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B92="","",IF(E92="","⛔ اختر النوع",IF(E92="مطبوعة","📷 مع الصورة",IF(D92="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D92,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D92,'البنود'!$F$7:$F$606)-N(F92),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F92)-SUMIF('البنود'!$B$7:$B$606,D92,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -2531,7 +2560,7 @@
         <v/>
       </c>
       <c r="I93" s="15">
-        <f>IF(B93="","",IF(E93="","⛔ اختر النوع",IF(E93="مطبوعة","📷 مع الصورة",IF(D93="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D93,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D93,'البنود'!$F$7:$F$606)-N(F93),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F93)-SUMIF('البنود'!$B$7:$B$606,D93,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B93="","",IF(E93="","⛔ اختر النوع",IF(E93="مطبوعة","📷 مع الصورة",IF(D93="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D93,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D93,'البنود'!$F$7:$F$606)-N(F93),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F93)-SUMIF('البنود'!$B$7:$B$606,D93,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -2551,7 +2580,7 @@
         <v/>
       </c>
       <c r="I94" s="15">
-        <f>IF(B94="","",IF(E94="","⛔ اختر النوع",IF(E94="مطبوعة","📷 مع الصورة",IF(D94="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D94,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D94,'البنود'!$F$7:$F$606)-N(F94),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F94)-SUMIF('البنود'!$B$7:$B$606,D94,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B94="","",IF(E94="","⛔ اختر النوع",IF(E94="مطبوعة","📷 مع الصورة",IF(D94="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D94,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D94,'البنود'!$F$7:$F$606)-N(F94),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F94)-SUMIF('البنود'!$B$7:$B$606,D94,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -2571,7 +2600,7 @@
         <v/>
       </c>
       <c r="I95" s="15">
-        <f>IF(B95="","",IF(E95="","⛔ اختر النوع",IF(E95="مطبوعة","📷 مع الصورة",IF(D95="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D95,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D95,'البنود'!$F$7:$F$606)-N(F95),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F95)-SUMIF('البنود'!$B$7:$B$606,D95,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B95="","",IF(E95="","⛔ اختر النوع",IF(E95="مطبوعة","📷 مع الصورة",IF(D95="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D95,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D95,'البنود'!$F$7:$F$606)-N(F95),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F95)-SUMIF('البنود'!$B$7:$B$606,D95,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -2591,7 +2620,7 @@
         <v/>
       </c>
       <c r="I96" s="15">
-        <f>IF(B96="","",IF(E96="","⛔ اختر النوع",IF(E96="مطبوعة","📷 مع الصورة",IF(D96="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D96,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D96,'البنود'!$F$7:$F$606)-N(F96),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F96)-SUMIF('البنود'!$B$7:$B$606,D96,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B96="","",IF(E96="","⛔ اختر النوع",IF(E96="مطبوعة","📷 مع الصورة",IF(D96="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D96,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D96,'البنود'!$F$7:$F$606)-N(F96),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F96)-SUMIF('البنود'!$B$7:$B$606,D96,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -2611,7 +2640,7 @@
         <v/>
       </c>
       <c r="I97" s="15">
-        <f>IF(B97="","",IF(E97="","⛔ اختر النوع",IF(E97="مطبوعة","📷 مع الصورة",IF(D97="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D97,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D97,'البنود'!$F$7:$F$606)-N(F97),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F97)-SUMIF('البنود'!$B$7:$B$606,D97,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B97="","",IF(E97="","⛔ اختر النوع",IF(E97="مطبوعة","📷 مع الصورة",IF(D97="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D97,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D97,'البنود'!$F$7:$F$606)-N(F97),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F97)-SUMIF('البنود'!$B$7:$B$606,D97,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -2631,7 +2660,7 @@
         <v/>
       </c>
       <c r="I98" s="15">
-        <f>IF(B98="","",IF(E98="","⛔ اختر النوع",IF(E98="مطبوعة","📷 مع الصورة",IF(D98="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D98,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D98,'البنود'!$F$7:$F$606)-N(F98),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F98)-SUMIF('البنود'!$B$7:$B$606,D98,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B98="","",IF(E98="","⛔ اختر النوع",IF(E98="مطبوعة","📷 مع الصورة",IF(D98="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D98,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D98,'البنود'!$F$7:$F$606)-N(F98),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F98)-SUMIF('البنود'!$B$7:$B$606,D98,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -2651,7 +2680,7 @@
         <v/>
       </c>
       <c r="I99" s="15">
-        <f>IF(B99="","",IF(E99="","⛔ اختر النوع",IF(E99="مطبوعة","📷 مع الصورة",IF(D99="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D99,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D99,'البنود'!$F$7:$F$606)-N(F99),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F99)-SUMIF('البنود'!$B$7:$B$606,D99,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B99="","",IF(E99="","⛔ اختر النوع",IF(E99="مطبوعة","📷 مع الصورة",IF(D99="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D99,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D99,'البنود'!$F$7:$F$606)-N(F99),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F99)-SUMIF('البنود'!$B$7:$B$606,D99,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -2671,7 +2700,7 @@
         <v/>
       </c>
       <c r="I100" s="15">
-        <f>IF(B100="","",IF(E100="","⛔ اختر النوع",IF(E100="مطبوعة","📷 مع الصورة",IF(D100="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D100,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D100,'البنود'!$F$7:$F$606)-N(F100),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F100)-SUMIF('البنود'!$B$7:$B$606,D100,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B100="","",IF(E100="","⛔ اختر النوع",IF(E100="مطبوعة","📷 مع الصورة",IF(D100="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D100,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D100,'البنود'!$F$7:$F$606)-N(F100),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F100)-SUMIF('البنود'!$B$7:$B$606,D100,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -2691,7 +2720,7 @@
         <v/>
       </c>
       <c r="I101" s="15">
-        <f>IF(B101="","",IF(E101="","⛔ اختر النوع",IF(E101="مطبوعة","📷 مع الصورة",IF(D101="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D101,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D101,'البنود'!$F$7:$F$606)-N(F101),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F101)-SUMIF('البنود'!$B$7:$B$606,D101,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B101="","",IF(E101="","⛔ اختر النوع",IF(E101="مطبوعة","📷 مع الصورة",IF(D101="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D101,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D101,'البنود'!$F$7:$F$606)-N(F101),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F101)-SUMIF('البنود'!$B$7:$B$606,D101,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -2711,7 +2740,7 @@
         <v/>
       </c>
       <c r="I102" s="15">
-        <f>IF(B102="","",IF(E102="","⛔ اختر النوع",IF(E102="مطبوعة","📷 مع الصورة",IF(D102="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D102,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D102,'البنود'!$F$7:$F$606)-N(F102),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F102)-SUMIF('البنود'!$B$7:$B$606,D102,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B102="","",IF(E102="","⛔ اختر النوع",IF(E102="مطبوعة","📷 مع الصورة",IF(D102="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D102,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D102,'البنود'!$F$7:$F$606)-N(F102),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F102)-SUMIF('البنود'!$B$7:$B$606,D102,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -2731,7 +2760,7 @@
         <v/>
       </c>
       <c r="I103" s="15">
-        <f>IF(B103="","",IF(E103="","⛔ اختر النوع",IF(E103="مطبوعة","📷 مع الصورة",IF(D103="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D103,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D103,'البنود'!$F$7:$F$606)-N(F103),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F103)-SUMIF('البنود'!$B$7:$B$606,D103,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B103="","",IF(E103="","⛔ اختر النوع",IF(E103="مطبوعة","📷 مع الصورة",IF(D103="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D103,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D103,'البنود'!$F$7:$F$606)-N(F103),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F103)-SUMIF('البنود'!$B$7:$B$606,D103,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -2751,7 +2780,7 @@
         <v/>
       </c>
       <c r="I104" s="15">
-        <f>IF(B104="","",IF(E104="","⛔ اختر النوع",IF(E104="مطبوعة","📷 مع الصورة",IF(D104="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D104,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D104,'البنود'!$F$7:$F$606)-N(F104),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F104)-SUMIF('البنود'!$B$7:$B$606,D104,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B104="","",IF(E104="","⛔ اختر النوع",IF(E104="مطبوعة","📷 مع الصورة",IF(D104="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D104,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D104,'البنود'!$F$7:$F$606)-N(F104),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F104)-SUMIF('البنود'!$B$7:$B$606,D104,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -2771,7 +2800,7 @@
         <v/>
       </c>
       <c r="I105" s="15">
-        <f>IF(B105="","",IF(E105="","⛔ اختر النوع",IF(E105="مطبوعة","📷 مع الصورة",IF(D105="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D105,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D105,'البنود'!$F$7:$F$606)-N(F105),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F105)-SUMIF('البنود'!$B$7:$B$606,D105,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B105="","",IF(E105="","⛔ اختر النوع",IF(E105="مطبوعة","📷 مع الصورة",IF(D105="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D105,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D105,'البنود'!$F$7:$F$606)-N(F105),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F105)-SUMIF('البنود'!$B$7:$B$606,D105,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -2791,7 +2820,7 @@
         <v/>
       </c>
       <c r="I106" s="15">
-        <f>IF(B106="","",IF(E106="","⛔ اختر النوع",IF(E106="مطبوعة","📷 مع الصورة",IF(D106="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D106,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D106,'البنود'!$F$7:$F$606)-N(F106),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F106)-SUMIF('البنود'!$B$7:$B$606,D106,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B106="","",IF(E106="","⛔ اختر النوع",IF(E106="مطبوعة","📷 مع الصورة",IF(D106="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D106,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D106,'البنود'!$F$7:$F$606)-N(F106),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F106)-SUMIF('البنود'!$B$7:$B$606,D106,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -2811,7 +2840,7 @@
         <v/>
       </c>
       <c r="I107" s="15">
-        <f>IF(B107="","",IF(E107="","⛔ اختر النوع",IF(E107="مطبوعة","📷 مع الصورة",IF(D107="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D107,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D107,'البنود'!$F$7:$F$606)-N(F107),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F107)-SUMIF('البنود'!$B$7:$B$606,D107,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B107="","",IF(E107="","⛔ اختر النوع",IF(E107="مطبوعة","📷 مع الصورة",IF(D107="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D107,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D107,'البنود'!$F$7:$F$606)-N(F107),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F107)-SUMIF('البنود'!$B$7:$B$606,D107,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -2831,7 +2860,7 @@
         <v/>
       </c>
       <c r="I108" s="15">
-        <f>IF(B108="","",IF(E108="","⛔ اختر النوع",IF(E108="مطبوعة","📷 مع الصورة",IF(D108="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D108,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D108,'البنود'!$F$7:$F$606)-N(F108),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F108)-SUMIF('البنود'!$B$7:$B$606,D108,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B108="","",IF(E108="","⛔ اختر النوع",IF(E108="مطبوعة","📷 مع الصورة",IF(D108="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D108,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D108,'البنود'!$F$7:$F$606)-N(F108),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F108)-SUMIF('البنود'!$B$7:$B$606,D108,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -2851,7 +2880,7 @@
         <v/>
       </c>
       <c r="I109" s="15">
-        <f>IF(B109="","",IF(E109="","⛔ اختر النوع",IF(E109="مطبوعة","📷 مع الصورة",IF(D109="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D109,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D109,'البنود'!$F$7:$F$606)-N(F109),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F109)-SUMIF('البنود'!$B$7:$B$606,D109,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B109="","",IF(E109="","⛔ اختر النوع",IF(E109="مطبوعة","📷 مع الصورة",IF(D109="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D109,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D109,'البنود'!$F$7:$F$606)-N(F109),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F109)-SUMIF('البنود'!$B$7:$B$606,D109,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -2871,7 +2900,7 @@
         <v/>
       </c>
       <c r="I110" s="15">
-        <f>IF(B110="","",IF(E110="","⛔ اختر النوع",IF(E110="مطبوعة","📷 مع الصورة",IF(D110="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D110,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D110,'البنود'!$F$7:$F$606)-N(F110),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F110)-SUMIF('البنود'!$B$7:$B$606,D110,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B110="","",IF(E110="","⛔ اختر النوع",IF(E110="مطبوعة","📷 مع الصورة",IF(D110="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D110,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D110,'البنود'!$F$7:$F$606)-N(F110),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F110)-SUMIF('البنود'!$B$7:$B$606,D110,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -2891,7 +2920,7 @@
         <v/>
       </c>
       <c r="I111" s="15">
-        <f>IF(B111="","",IF(E111="","⛔ اختر النوع",IF(E111="مطبوعة","📷 مع الصورة",IF(D111="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D111,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D111,'البنود'!$F$7:$F$606)-N(F111),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F111)-SUMIF('البنود'!$B$7:$B$606,D111,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B111="","",IF(E111="","⛔ اختر النوع",IF(E111="مطبوعة","📷 مع الصورة",IF(D111="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D111,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D111,'البنود'!$F$7:$F$606)-N(F111),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F111)-SUMIF('البنود'!$B$7:$B$606,D111,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -2911,7 +2940,7 @@
         <v/>
       </c>
       <c r="I112" s="15">
-        <f>IF(B112="","",IF(E112="","⛔ اختر النوع",IF(E112="مطبوعة","📷 مع الصورة",IF(D112="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D112,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D112,'البنود'!$F$7:$F$606)-N(F112),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F112)-SUMIF('البنود'!$B$7:$B$606,D112,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B112="","",IF(E112="","⛔ اختر النوع",IF(E112="مطبوعة","📷 مع الصورة",IF(D112="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D112,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D112,'البنود'!$F$7:$F$606)-N(F112),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F112)-SUMIF('البنود'!$B$7:$B$606,D112,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -2931,7 +2960,7 @@
         <v/>
       </c>
       <c r="I113" s="15">
-        <f>IF(B113="","",IF(E113="","⛔ اختر النوع",IF(E113="مطبوعة","📷 مع الصورة",IF(D113="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D113,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D113,'البنود'!$F$7:$F$606)-N(F113),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F113)-SUMIF('البنود'!$B$7:$B$606,D113,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B113="","",IF(E113="","⛔ اختر النوع",IF(E113="مطبوعة","📷 مع الصورة",IF(D113="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D113,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D113,'البنود'!$F$7:$F$606)-N(F113),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F113)-SUMIF('البنود'!$B$7:$B$606,D113,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -2951,7 +2980,7 @@
         <v/>
       </c>
       <c r="I114" s="15">
-        <f>IF(B114="","",IF(E114="","⛔ اختر النوع",IF(E114="مطبوعة","📷 مع الصورة",IF(D114="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D114,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D114,'البنود'!$F$7:$F$606)-N(F114),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F114)-SUMIF('البنود'!$B$7:$B$606,D114,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B114="","",IF(E114="","⛔ اختر النوع",IF(E114="مطبوعة","📷 مع الصورة",IF(D114="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D114,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D114,'البنود'!$F$7:$F$606)-N(F114),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F114)-SUMIF('البنود'!$B$7:$B$606,D114,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -2971,7 +3000,7 @@
         <v/>
       </c>
       <c r="I115" s="15">
-        <f>IF(B115="","",IF(E115="","⛔ اختر النوع",IF(E115="مطبوعة","📷 مع الصورة",IF(D115="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D115,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D115,'البنود'!$F$7:$F$606)-N(F115),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F115)-SUMIF('البنود'!$B$7:$B$606,D115,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B115="","",IF(E115="","⛔ اختر النوع",IF(E115="مطبوعة","📷 مع الصورة",IF(D115="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D115,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D115,'البنود'!$F$7:$F$606)-N(F115),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F115)-SUMIF('البنود'!$B$7:$B$606,D115,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -2991,7 +3020,7 @@
         <v/>
       </c>
       <c r="I116" s="15">
-        <f>IF(B116="","",IF(E116="","⛔ اختر النوع",IF(E116="مطبوعة","📷 مع الصورة",IF(D116="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D116,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D116,'البنود'!$F$7:$F$606)-N(F116),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F116)-SUMIF('البنود'!$B$7:$B$606,D116,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B116="","",IF(E116="","⛔ اختر النوع",IF(E116="مطبوعة","📷 مع الصورة",IF(D116="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D116,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D116,'البنود'!$F$7:$F$606)-N(F116),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F116)-SUMIF('البنود'!$B$7:$B$606,D116,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -3011,7 +3040,7 @@
         <v/>
       </c>
       <c r="I117" s="15">
-        <f>IF(B117="","",IF(E117="","⛔ اختر النوع",IF(E117="مطبوعة","📷 مع الصورة",IF(D117="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D117,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D117,'البنود'!$F$7:$F$606)-N(F117),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F117)-SUMIF('البنود'!$B$7:$B$606,D117,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B117="","",IF(E117="","⛔ اختر النوع",IF(E117="مطبوعة","📷 مع الصورة",IF(D117="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D117,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D117,'البنود'!$F$7:$F$606)-N(F117),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F117)-SUMIF('البنود'!$B$7:$B$606,D117,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -3031,7 +3060,7 @@
         <v/>
       </c>
       <c r="I118" s="15">
-        <f>IF(B118="","",IF(E118="","⛔ اختر النوع",IF(E118="مطبوعة","📷 مع الصورة",IF(D118="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D118,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D118,'البنود'!$F$7:$F$606)-N(F118),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F118)-SUMIF('البنود'!$B$7:$B$606,D118,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B118="","",IF(E118="","⛔ اختر النوع",IF(E118="مطبوعة","📷 مع الصورة",IF(D118="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D118,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D118,'البنود'!$F$7:$F$606)-N(F118),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F118)-SUMIF('البنود'!$B$7:$B$606,D118,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -3051,7 +3080,7 @@
         <v/>
       </c>
       <c r="I119" s="15">
-        <f>IF(B119="","",IF(E119="","⛔ اختر النوع",IF(E119="مطبوعة","📷 مع الصورة",IF(D119="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D119,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D119,'البنود'!$F$7:$F$606)-N(F119),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F119)-SUMIF('البنود'!$B$7:$B$606,D119,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B119="","",IF(E119="","⛔ اختر النوع",IF(E119="مطبوعة","📷 مع الصورة",IF(D119="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D119,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D119,'البنود'!$F$7:$F$606)-N(F119),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F119)-SUMIF('البنود'!$B$7:$B$606,D119,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -3071,7 +3100,7 @@
         <v/>
       </c>
       <c r="I120" s="15">
-        <f>IF(B120="","",IF(E120="","⛔ اختر النوع",IF(E120="مطبوعة","📷 مع الصورة",IF(D120="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D120,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D120,'البنود'!$F$7:$F$606)-N(F120),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F120)-SUMIF('البنود'!$B$7:$B$606,D120,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B120="","",IF(E120="","⛔ اختر النوع",IF(E120="مطبوعة","📷 مع الصورة",IF(D120="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D120,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D120,'البنود'!$F$7:$F$606)-N(F120),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F120)-SUMIF('البنود'!$B$7:$B$606,D120,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -3091,7 +3120,7 @@
         <v/>
       </c>
       <c r="I121" s="15">
-        <f>IF(B121="","",IF(E121="","⛔ اختر النوع",IF(E121="مطبوعة","📷 مع الصورة",IF(D121="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D121,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D121,'البنود'!$F$7:$F$606)-N(F121),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F121)-SUMIF('البنود'!$B$7:$B$606,D121,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B121="","",IF(E121="","⛔ اختر النوع",IF(E121="مطبوعة","📷 مع الصورة",IF(D121="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D121,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D121,'البنود'!$F$7:$F$606)-N(F121),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F121)-SUMIF('البنود'!$B$7:$B$606,D121,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -3111,7 +3140,7 @@
         <v/>
       </c>
       <c r="I122" s="15">
-        <f>IF(B122="","",IF(E122="","⛔ اختر النوع",IF(E122="مطبوعة","📷 مع الصورة",IF(D122="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D122,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D122,'البنود'!$F$7:$F$606)-N(F122),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F122)-SUMIF('البنود'!$B$7:$B$606,D122,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B122="","",IF(E122="","⛔ اختر النوع",IF(E122="مطبوعة","📷 مع الصورة",IF(D122="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D122,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D122,'البنود'!$F$7:$F$606)-N(F122),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F122)-SUMIF('البنود'!$B$7:$B$606,D122,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -3131,7 +3160,7 @@
         <v/>
       </c>
       <c r="I123" s="15">
-        <f>IF(B123="","",IF(E123="","⛔ اختر النوع",IF(E123="مطبوعة","📷 مع الصورة",IF(D123="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D123,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D123,'البنود'!$F$7:$F$606)-N(F123),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F123)-SUMIF('البنود'!$B$7:$B$606,D123,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B123="","",IF(E123="","⛔ اختر النوع",IF(E123="مطبوعة","📷 مع الصورة",IF(D123="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D123,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D123,'البنود'!$F$7:$F$606)-N(F123),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F123)-SUMIF('البنود'!$B$7:$B$606,D123,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -3151,7 +3180,7 @@
         <v/>
       </c>
       <c r="I124" s="15">
-        <f>IF(B124="","",IF(E124="","⛔ اختر النوع",IF(E124="مطبوعة","📷 مع الصورة",IF(D124="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D124,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D124,'البنود'!$F$7:$F$606)-N(F124),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F124)-SUMIF('البنود'!$B$7:$B$606,D124,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B124="","",IF(E124="","⛔ اختر النوع",IF(E124="مطبوعة","📷 مع الصورة",IF(D124="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D124,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D124,'البنود'!$F$7:$F$606)-N(F124),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F124)-SUMIF('البنود'!$B$7:$B$606,D124,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -3171,7 +3200,7 @@
         <v/>
       </c>
       <c r="I125" s="15">
-        <f>IF(B125="","",IF(E125="","⛔ اختر النوع",IF(E125="مطبوعة","📷 مع الصورة",IF(D125="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D125,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D125,'البنود'!$F$7:$F$606)-N(F125),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F125)-SUMIF('البنود'!$B$7:$B$606,D125,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B125="","",IF(E125="","⛔ اختر النوع",IF(E125="مطبوعة","📷 مع الصورة",IF(D125="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D125,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D125,'البنود'!$F$7:$F$606)-N(F125),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F125)-SUMIF('البنود'!$B$7:$B$606,D125,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -3191,7 +3220,7 @@
         <v/>
       </c>
       <c r="I126" s="15">
-        <f>IF(B126="","",IF(E126="","⛔ اختر النوع",IF(E126="مطبوعة","📷 مع الصورة",IF(D126="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D126,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D126,'البنود'!$F$7:$F$606)-N(F126),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F126)-SUMIF('البنود'!$B$7:$B$606,D126,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B126="","",IF(E126="","⛔ اختر النوع",IF(E126="مطبوعة","📷 مع الصورة",IF(D126="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D126,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D126,'البنود'!$F$7:$F$606)-N(F126),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F126)-SUMIF('البنود'!$B$7:$B$606,D126,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -3211,7 +3240,7 @@
         <v/>
       </c>
       <c r="I127" s="15">
-        <f>IF(B127="","",IF(E127="","⛔ اختر النوع",IF(E127="مطبوعة","📷 مع الصورة",IF(D127="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D127,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D127,'البنود'!$F$7:$F$606)-N(F127),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F127)-SUMIF('البنود'!$B$7:$B$606,D127,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B127="","",IF(E127="","⛔ اختر النوع",IF(E127="مطبوعة","📷 مع الصورة",IF(D127="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D127,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D127,'البنود'!$F$7:$F$606)-N(F127),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F127)-SUMIF('البنود'!$B$7:$B$606,D127,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -3231,7 +3260,7 @@
         <v/>
       </c>
       <c r="I128" s="15">
-        <f>IF(B128="","",IF(E128="","⛔ اختر النوع",IF(E128="مطبوعة","📷 مع الصورة",IF(D128="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D128,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D128,'البنود'!$F$7:$F$606)-N(F128),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F128)-SUMIF('البنود'!$B$7:$B$606,D128,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B128="","",IF(E128="","⛔ اختر النوع",IF(E128="مطبوعة","📷 مع الصورة",IF(D128="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D128,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D128,'البنود'!$F$7:$F$606)-N(F128),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F128)-SUMIF('البنود'!$B$7:$B$606,D128,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -3251,7 +3280,7 @@
         <v/>
       </c>
       <c r="I129" s="15">
-        <f>IF(B129="","",IF(E129="","⛔ اختر النوع",IF(E129="مطبوعة","📷 مع الصورة",IF(D129="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D129,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D129,'البنود'!$F$7:$F$606)-N(F129),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F129)-SUMIF('البنود'!$B$7:$B$606,D129,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B129="","",IF(E129="","⛔ اختر النوع",IF(E129="مطبوعة","📷 مع الصورة",IF(D129="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D129,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D129,'البنود'!$F$7:$F$606)-N(F129),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F129)-SUMIF('البنود'!$B$7:$B$606,D129,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -3271,7 +3300,7 @@
         <v/>
       </c>
       <c r="I130" s="15">
-        <f>IF(B130="","",IF(E130="","⛔ اختر النوع",IF(E130="مطبوعة","📷 مع الصورة",IF(D130="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D130,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D130,'البنود'!$F$7:$F$606)-N(F130),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F130)-SUMIF('البنود'!$B$7:$B$606,D130,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B130="","",IF(E130="","⛔ اختر النوع",IF(E130="مطبوعة","📷 مع الصورة",IF(D130="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D130,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D130,'البنود'!$F$7:$F$606)-N(F130),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F130)-SUMIF('البنود'!$B$7:$B$606,D130,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -3291,7 +3320,7 @@
         <v/>
       </c>
       <c r="I131" s="15">
-        <f>IF(B131="","",IF(E131="","⛔ اختر النوع",IF(E131="مطبوعة","📷 مع الصورة",IF(D131="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D131,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D131,'البنود'!$F$7:$F$606)-N(F131),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F131)-SUMIF('البنود'!$B$7:$B$606,D131,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B131="","",IF(E131="","⛔ اختر النوع",IF(E131="مطبوعة","📷 مع الصورة",IF(D131="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D131,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D131,'البنود'!$F$7:$F$606)-N(F131),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F131)-SUMIF('البنود'!$B$7:$B$606,D131,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -3311,7 +3340,7 @@
         <v/>
       </c>
       <c r="I132" s="15">
-        <f>IF(B132="","",IF(E132="","⛔ اختر النوع",IF(E132="مطبوعة","📷 مع الصورة",IF(D132="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D132,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D132,'البنود'!$F$7:$F$606)-N(F132),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F132)-SUMIF('البنود'!$B$7:$B$606,D132,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B132="","",IF(E132="","⛔ اختر النوع",IF(E132="مطبوعة","📷 مع الصورة",IF(D132="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D132,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D132,'البنود'!$F$7:$F$606)-N(F132),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F132)-SUMIF('البنود'!$B$7:$B$606,D132,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -3331,7 +3360,7 @@
         <v/>
       </c>
       <c r="I133" s="15">
-        <f>IF(B133="","",IF(E133="","⛔ اختر النوع",IF(E133="مطبوعة","📷 مع الصورة",IF(D133="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D133,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D133,'البنود'!$F$7:$F$606)-N(F133),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F133)-SUMIF('البنود'!$B$7:$B$606,D133,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B133="","",IF(E133="","⛔ اختر النوع",IF(E133="مطبوعة","📷 مع الصورة",IF(D133="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D133,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D133,'البنود'!$F$7:$F$606)-N(F133),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F133)-SUMIF('البنود'!$B$7:$B$606,D133,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -3351,7 +3380,7 @@
         <v/>
       </c>
       <c r="I134" s="15">
-        <f>IF(B134="","",IF(E134="","⛔ اختر النوع",IF(E134="مطبوعة","📷 مع الصورة",IF(D134="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D134,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D134,'البنود'!$F$7:$F$606)-N(F134),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F134)-SUMIF('البنود'!$B$7:$B$606,D134,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B134="","",IF(E134="","⛔ اختر النوع",IF(E134="مطبوعة","📷 مع الصورة",IF(D134="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D134,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D134,'البنود'!$F$7:$F$606)-N(F134),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F134)-SUMIF('البنود'!$B$7:$B$606,D134,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -3371,7 +3400,7 @@
         <v/>
       </c>
       <c r="I135" s="15">
-        <f>IF(B135="","",IF(E135="","⛔ اختر النوع",IF(E135="مطبوعة","📷 مع الصورة",IF(D135="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D135,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D135,'البنود'!$F$7:$F$606)-N(F135),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F135)-SUMIF('البنود'!$B$7:$B$606,D135,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B135="","",IF(E135="","⛔ اختر النوع",IF(E135="مطبوعة","📷 مع الصورة",IF(D135="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D135,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D135,'البنود'!$F$7:$F$606)-N(F135),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F135)-SUMIF('البنود'!$B$7:$B$606,D135,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -3391,7 +3420,7 @@
         <v/>
       </c>
       <c r="I136" s="15">
-        <f>IF(B136="","",IF(E136="","⛔ اختر النوع",IF(E136="مطبوعة","📷 مع الصورة",IF(D136="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D136,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D136,'البنود'!$F$7:$F$606)-N(F136),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F136)-SUMIF('البنود'!$B$7:$B$606,D136,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B136="","",IF(E136="","⛔ اختر النوع",IF(E136="مطبوعة","📷 مع الصورة",IF(D136="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D136,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D136,'البنود'!$F$7:$F$606)-N(F136),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F136)-SUMIF('البنود'!$B$7:$B$606,D136,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -3411,7 +3440,7 @@
         <v/>
       </c>
       <c r="I137" s="15">
-        <f>IF(B137="","",IF(E137="","⛔ اختر النوع",IF(E137="مطبوعة","📷 مع الصورة",IF(D137="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D137,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D137,'البنود'!$F$7:$F$606)-N(F137),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F137)-SUMIF('البنود'!$B$7:$B$606,D137,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B137="","",IF(E137="","⛔ اختر النوع",IF(E137="مطبوعة","📷 مع الصورة",IF(D137="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D137,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D137,'البنود'!$F$7:$F$606)-N(F137),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F137)-SUMIF('البنود'!$B$7:$B$606,D137,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -3431,7 +3460,7 @@
         <v/>
       </c>
       <c r="I138" s="15">
-        <f>IF(B138="","",IF(E138="","⛔ اختر النوع",IF(E138="مطبوعة","📷 مع الصورة",IF(D138="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D138,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D138,'البنود'!$F$7:$F$606)-N(F138),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F138)-SUMIF('البنود'!$B$7:$B$606,D138,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B138="","",IF(E138="","⛔ اختر النوع",IF(E138="مطبوعة","📷 مع الصورة",IF(D138="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D138,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D138,'البنود'!$F$7:$F$606)-N(F138),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F138)-SUMIF('البنود'!$B$7:$B$606,D138,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -3451,7 +3480,7 @@
         <v/>
       </c>
       <c r="I139" s="15">
-        <f>IF(B139="","",IF(E139="","⛔ اختر النوع",IF(E139="مطبوعة","📷 مع الصورة",IF(D139="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D139,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D139,'البنود'!$F$7:$F$606)-N(F139),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F139)-SUMIF('البنود'!$B$7:$B$606,D139,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B139="","",IF(E139="","⛔ اختر النوع",IF(E139="مطبوعة","📷 مع الصورة",IF(D139="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D139,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D139,'البنود'!$F$7:$F$606)-N(F139),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F139)-SUMIF('البنود'!$B$7:$B$606,D139,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -3471,7 +3500,7 @@
         <v/>
       </c>
       <c r="I140" s="15">
-        <f>IF(B140="","",IF(E140="","⛔ اختر النوع",IF(E140="مطبوعة","📷 مع الصورة",IF(D140="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D140,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D140,'البنود'!$F$7:$F$606)-N(F140),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F140)-SUMIF('البنود'!$B$7:$B$606,D140,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B140="","",IF(E140="","⛔ اختر النوع",IF(E140="مطبوعة","📷 مع الصورة",IF(D140="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D140,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D140,'البنود'!$F$7:$F$606)-N(F140),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F140)-SUMIF('البنود'!$B$7:$B$606,D140,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -3491,7 +3520,7 @@
         <v/>
       </c>
       <c r="I141" s="15">
-        <f>IF(B141="","",IF(E141="","⛔ اختر النوع",IF(E141="مطبوعة","📷 مع الصورة",IF(D141="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D141,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D141,'البنود'!$F$7:$F$606)-N(F141),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F141)-SUMIF('البنود'!$B$7:$B$606,D141,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B141="","",IF(E141="","⛔ اختر النوع",IF(E141="مطبوعة","📷 مع الصورة",IF(D141="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D141,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D141,'البنود'!$F$7:$F$606)-N(F141),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F141)-SUMIF('البنود'!$B$7:$B$606,D141,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -3511,7 +3540,7 @@
         <v/>
       </c>
       <c r="I142" s="15">
-        <f>IF(B142="","",IF(E142="","⛔ اختر النوع",IF(E142="مطبوعة","📷 مع الصورة",IF(D142="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D142,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D142,'البنود'!$F$7:$F$606)-N(F142),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F142)-SUMIF('البنود'!$B$7:$B$606,D142,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B142="","",IF(E142="","⛔ اختر النوع",IF(E142="مطبوعة","📷 مع الصورة",IF(D142="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D142,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D142,'البنود'!$F$7:$F$606)-N(F142),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F142)-SUMIF('البنود'!$B$7:$B$606,D142,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -3531,7 +3560,7 @@
         <v/>
       </c>
       <c r="I143" s="15">
-        <f>IF(B143="","",IF(E143="","⛔ اختر النوع",IF(E143="مطبوعة","📷 مع الصورة",IF(D143="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D143,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D143,'البنود'!$F$7:$F$606)-N(F143),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F143)-SUMIF('البنود'!$B$7:$B$606,D143,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B143="","",IF(E143="","⛔ اختر النوع",IF(E143="مطبوعة","📷 مع الصورة",IF(D143="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D143,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D143,'البنود'!$F$7:$F$606)-N(F143),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F143)-SUMIF('البنود'!$B$7:$B$606,D143,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -3551,7 +3580,7 @@
         <v/>
       </c>
       <c r="I144" s="15">
-        <f>IF(B144="","",IF(E144="","⛔ اختر النوع",IF(E144="مطبوعة","📷 مع الصورة",IF(D144="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D144,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D144,'البنود'!$F$7:$F$606)-N(F144),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F144)-SUMIF('البنود'!$B$7:$B$606,D144,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B144="","",IF(E144="","⛔ اختر النوع",IF(E144="مطبوعة","📷 مع الصورة",IF(D144="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D144,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D144,'البنود'!$F$7:$F$606)-N(F144),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F144)-SUMIF('البنود'!$B$7:$B$606,D144,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -3571,7 +3600,7 @@
         <v/>
       </c>
       <c r="I145" s="15">
-        <f>IF(B145="","",IF(E145="","⛔ اختر النوع",IF(E145="مطبوعة","📷 مع الصورة",IF(D145="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D145,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D145,'البنود'!$F$7:$F$606)-N(F145),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F145)-SUMIF('البنود'!$B$7:$B$606,D145,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B145="","",IF(E145="","⛔ اختر النوع",IF(E145="مطبوعة","📷 مع الصورة",IF(D145="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D145,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D145,'البنود'!$F$7:$F$606)-N(F145),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F145)-SUMIF('البنود'!$B$7:$B$606,D145,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -3591,7 +3620,7 @@
         <v/>
       </c>
       <c r="I146" s="15">
-        <f>IF(B146="","",IF(E146="","⛔ اختر النوع",IF(E146="مطبوعة","📷 مع الصورة",IF(D146="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D146,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D146,'البنود'!$F$7:$F$606)-N(F146),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F146)-SUMIF('البنود'!$B$7:$B$606,D146,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B146="","",IF(E146="","⛔ اختر النوع",IF(E146="مطبوعة","📷 مع الصورة",IF(D146="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D146,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D146,'البنود'!$F$7:$F$606)-N(F146),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F146)-SUMIF('البنود'!$B$7:$B$606,D146,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -3611,7 +3640,7 @@
         <v/>
       </c>
       <c r="I147" s="15">
-        <f>IF(B147="","",IF(E147="","⛔ اختر النوع",IF(E147="مطبوعة","📷 مع الصورة",IF(D147="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D147,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D147,'البنود'!$F$7:$F$606)-N(F147),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F147)-SUMIF('البنود'!$B$7:$B$606,D147,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B147="","",IF(E147="","⛔ اختر النوع",IF(E147="مطبوعة","📷 مع الصورة",IF(D147="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D147,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D147,'البنود'!$F$7:$F$606)-N(F147),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F147)-SUMIF('البنود'!$B$7:$B$606,D147,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -3631,7 +3660,7 @@
         <v/>
       </c>
       <c r="I148" s="15">
-        <f>IF(B148="","",IF(E148="","⛔ اختر النوع",IF(E148="مطبوعة","📷 مع الصورة",IF(D148="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D148,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D148,'البنود'!$F$7:$F$606)-N(F148),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F148)-SUMIF('البنود'!$B$7:$B$606,D148,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B148="","",IF(E148="","⛔ اختر النوع",IF(E148="مطبوعة","📷 مع الصورة",IF(D148="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D148,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D148,'البنود'!$F$7:$F$606)-N(F148),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F148)-SUMIF('البنود'!$B$7:$B$606,D148,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -3651,7 +3680,7 @@
         <v/>
       </c>
       <c r="I149" s="15">
-        <f>IF(B149="","",IF(E149="","⛔ اختر النوع",IF(E149="مطبوعة","📷 مع الصورة",IF(D149="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D149,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D149,'البنود'!$F$7:$F$606)-N(F149),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F149)-SUMIF('البنود'!$B$7:$B$606,D149,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B149="","",IF(E149="","⛔ اختر النوع",IF(E149="مطبوعة","📷 مع الصورة",IF(D149="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D149,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D149,'البنود'!$F$7:$F$606)-N(F149),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F149)-SUMIF('البنود'!$B$7:$B$606,D149,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -3671,7 +3700,7 @@
         <v/>
       </c>
       <c r="I150" s="15">
-        <f>IF(B150="","",IF(E150="","⛔ اختر النوع",IF(E150="مطبوعة","📷 مع الصورة",IF(D150="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D150,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D150,'البنود'!$F$7:$F$606)-N(F150),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F150)-SUMIF('البنود'!$B$7:$B$606,D150,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B150="","",IF(E150="","⛔ اختر النوع",IF(E150="مطبوعة","📷 مع الصورة",IF(D150="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D150,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D150,'البنود'!$F$7:$F$606)-N(F150),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F150)-SUMIF('البنود'!$B$7:$B$606,D150,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -3691,7 +3720,7 @@
         <v/>
       </c>
       <c r="I151" s="15">
-        <f>IF(B151="","",IF(E151="","⛔ اختر النوع",IF(E151="مطبوعة","📷 مع الصورة",IF(D151="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D151,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D151,'البنود'!$F$7:$F$606)-N(F151),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F151)-SUMIF('البنود'!$B$7:$B$606,D151,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B151="","",IF(E151="","⛔ اختر النوع",IF(E151="مطبوعة","📷 مع الصورة",IF(D151="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D151,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D151,'البنود'!$F$7:$F$606)-N(F151),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F151)-SUMIF('البنود'!$B$7:$B$606,D151,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -3711,7 +3740,7 @@
         <v/>
       </c>
       <c r="I152" s="15">
-        <f>IF(B152="","",IF(E152="","⛔ اختر النوع",IF(E152="مطبوعة","📷 مع الصورة",IF(D152="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D152,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D152,'البنود'!$F$7:$F$606)-N(F152),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F152)-SUMIF('البنود'!$B$7:$B$606,D152,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B152="","",IF(E152="","⛔ اختر النوع",IF(E152="مطبوعة","📷 مع الصورة",IF(D152="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D152,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D152,'البنود'!$F$7:$F$606)-N(F152),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F152)-SUMIF('البنود'!$B$7:$B$606,D152,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -3731,7 +3760,7 @@
         <v/>
       </c>
       <c r="I153" s="15">
-        <f>IF(B153="","",IF(E153="","⛔ اختر النوع",IF(E153="مطبوعة","📷 مع الصورة",IF(D153="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D153,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D153,'البنود'!$F$7:$F$606)-N(F153),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F153)-SUMIF('البنود'!$B$7:$B$606,D153,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B153="","",IF(E153="","⛔ اختر النوع",IF(E153="مطبوعة","📷 مع الصورة",IF(D153="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D153,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D153,'البنود'!$F$7:$F$606)-N(F153),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F153)-SUMIF('البنود'!$B$7:$B$606,D153,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -3751,7 +3780,7 @@
         <v/>
       </c>
       <c r="I154" s="15">
-        <f>IF(B154="","",IF(E154="","⛔ اختر النوع",IF(E154="مطبوعة","📷 مع الصورة",IF(D154="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D154,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D154,'البنود'!$F$7:$F$606)-N(F154),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F154)-SUMIF('البنود'!$B$7:$B$606,D154,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B154="","",IF(E154="","⛔ اختر النوع",IF(E154="مطبوعة","📷 مع الصورة",IF(D154="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D154,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D154,'البنود'!$F$7:$F$606)-N(F154),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F154)-SUMIF('البنود'!$B$7:$B$606,D154,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -3771,7 +3800,7 @@
         <v/>
       </c>
       <c r="I155" s="15">
-        <f>IF(B155="","",IF(E155="","⛔ اختر النوع",IF(E155="مطبوعة","📷 مع الصورة",IF(D155="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D155,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D155,'البنود'!$F$7:$F$606)-N(F155),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F155)-SUMIF('البنود'!$B$7:$B$606,D155,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B155="","",IF(E155="","⛔ اختر النوع",IF(E155="مطبوعة","📷 مع الصورة",IF(D155="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D155,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D155,'البنود'!$F$7:$F$606)-N(F155),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F155)-SUMIF('البنود'!$B$7:$B$606,D155,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -3791,7 +3820,7 @@
         <v/>
       </c>
       <c r="I156" s="15">
-        <f>IF(B156="","",IF(E156="","⛔ اختر النوع",IF(E156="مطبوعة","📷 مع الصورة",IF(D156="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D156,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D156,'البنود'!$F$7:$F$606)-N(F156),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F156)-SUMIF('البنود'!$B$7:$B$606,D156,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B156="","",IF(E156="","⛔ اختر النوع",IF(E156="مطبوعة","📷 مع الصورة",IF(D156="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D156,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D156,'البنود'!$F$7:$F$606)-N(F156),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F156)-SUMIF('البنود'!$B$7:$B$606,D156,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -3811,7 +3840,7 @@
         <v/>
       </c>
       <c r="I157" s="15">
-        <f>IF(B157="","",IF(E157="","⛔ اختر النوع",IF(E157="مطبوعة","📷 مع الصورة",IF(D157="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D157,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D157,'البنود'!$F$7:$F$606)-N(F157),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F157)-SUMIF('البنود'!$B$7:$B$606,D157,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B157="","",IF(E157="","⛔ اختر النوع",IF(E157="مطبوعة","📷 مع الصورة",IF(D157="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D157,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D157,'البنود'!$F$7:$F$606)-N(F157),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F157)-SUMIF('البنود'!$B$7:$B$606,D157,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -3831,7 +3860,7 @@
         <v/>
       </c>
       <c r="I158" s="15">
-        <f>IF(B158="","",IF(E158="","⛔ اختر النوع",IF(E158="مطبوعة","📷 مع الصورة",IF(D158="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D158,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D158,'البنود'!$F$7:$F$606)-N(F158),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F158)-SUMIF('البنود'!$B$7:$B$606,D158,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B158="","",IF(E158="","⛔ اختر النوع",IF(E158="مطبوعة","📷 مع الصورة",IF(D158="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D158,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D158,'البنود'!$F$7:$F$606)-N(F158),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F158)-SUMIF('البنود'!$B$7:$B$606,D158,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -3851,7 +3880,7 @@
         <v/>
       </c>
       <c r="I159" s="15">
-        <f>IF(B159="","",IF(E159="","⛔ اختر النوع",IF(E159="مطبوعة","📷 مع الصورة",IF(D159="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D159,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D159,'البنود'!$F$7:$F$606)-N(F159),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F159)-SUMIF('البنود'!$B$7:$B$606,D159,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B159="","",IF(E159="","⛔ اختر النوع",IF(E159="مطبوعة","📷 مع الصورة",IF(D159="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D159,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D159,'البنود'!$F$7:$F$606)-N(F159),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F159)-SUMIF('البنود'!$B$7:$B$606,D159,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -3871,7 +3900,7 @@
         <v/>
       </c>
       <c r="I160" s="15">
-        <f>IF(B160="","",IF(E160="","⛔ اختر النوع",IF(E160="مطبوعة","📷 مع الصورة",IF(D160="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D160,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D160,'البنود'!$F$7:$F$606)-N(F160),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F160)-SUMIF('البنود'!$B$7:$B$606,D160,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B160="","",IF(E160="","⛔ اختر النوع",IF(E160="مطبوعة","📷 مع الصورة",IF(D160="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D160,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D160,'البنود'!$F$7:$F$606)-N(F160),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F160)-SUMIF('البنود'!$B$7:$B$606,D160,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -3891,7 +3920,7 @@
         <v/>
       </c>
       <c r="I161" s="15">
-        <f>IF(B161="","",IF(E161="","⛔ اختر النوع",IF(E161="مطبوعة","📷 مع الصورة",IF(D161="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D161,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D161,'البنود'!$F$7:$F$606)-N(F161),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F161)-SUMIF('البنود'!$B$7:$B$606,D161,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B161="","",IF(E161="","⛔ اختر النوع",IF(E161="مطبوعة","📷 مع الصورة",IF(D161="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D161,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D161,'البنود'!$F$7:$F$606)-N(F161),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F161)-SUMIF('البنود'!$B$7:$B$606,D161,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -3911,7 +3940,7 @@
         <v/>
       </c>
       <c r="I162" s="15">
-        <f>IF(B162="","",IF(E162="","⛔ اختر النوع",IF(E162="مطبوعة","📷 مع الصورة",IF(D162="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D162,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D162,'البنود'!$F$7:$F$606)-N(F162),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F162)-SUMIF('البنود'!$B$7:$B$606,D162,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B162="","",IF(E162="","⛔ اختر النوع",IF(E162="مطبوعة","📷 مع الصورة",IF(D162="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D162,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D162,'البنود'!$F$7:$F$606)-N(F162),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F162)-SUMIF('البنود'!$B$7:$B$606,D162,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -3931,7 +3960,7 @@
         <v/>
       </c>
       <c r="I163" s="15">
-        <f>IF(B163="","",IF(E163="","⛔ اختر النوع",IF(E163="مطبوعة","📷 مع الصورة",IF(D163="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D163,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D163,'البنود'!$F$7:$F$606)-N(F163),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F163)-SUMIF('البنود'!$B$7:$B$606,D163,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B163="","",IF(E163="","⛔ اختر النوع",IF(E163="مطبوعة","📷 مع الصورة",IF(D163="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D163,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D163,'البنود'!$F$7:$F$606)-N(F163),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F163)-SUMIF('البنود'!$B$7:$B$606,D163,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -3951,7 +3980,7 @@
         <v/>
       </c>
       <c r="I164" s="15">
-        <f>IF(B164="","",IF(E164="","⛔ اختر النوع",IF(E164="مطبوعة","📷 مع الصورة",IF(D164="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D164,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D164,'البنود'!$F$7:$F$606)-N(F164),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F164)-SUMIF('البنود'!$B$7:$B$606,D164,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B164="","",IF(E164="","⛔ اختر النوع",IF(E164="مطبوعة","📷 مع الصورة",IF(D164="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D164,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D164,'البنود'!$F$7:$F$606)-N(F164),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F164)-SUMIF('البنود'!$B$7:$B$606,D164,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -3971,7 +4000,7 @@
         <v/>
       </c>
       <c r="I165" s="15">
-        <f>IF(B165="","",IF(E165="","⛔ اختر النوع",IF(E165="مطبوعة","📷 مع الصورة",IF(D165="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D165,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D165,'البنود'!$F$7:$F$606)-N(F165),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F165)-SUMIF('البنود'!$B$7:$B$606,D165,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B165="","",IF(E165="","⛔ اختر النوع",IF(E165="مطبوعة","📷 مع الصورة",IF(D165="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D165,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D165,'البنود'!$F$7:$F$606)-N(F165),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F165)-SUMIF('البنود'!$B$7:$B$606,D165,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -3991,7 +4020,7 @@
         <v/>
       </c>
       <c r="I166" s="15">
-        <f>IF(B166="","",IF(E166="","⛔ اختر النوع",IF(E166="مطبوعة","📷 مع الصورة",IF(D166="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D166,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D166,'البنود'!$F$7:$F$606)-N(F166),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F166)-SUMIF('البنود'!$B$7:$B$606,D166,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B166="","",IF(E166="","⛔ اختر النوع",IF(E166="مطبوعة","📷 مع الصورة",IF(D166="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D166,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D166,'البنود'!$F$7:$F$606)-N(F166),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F166)-SUMIF('البنود'!$B$7:$B$606,D166,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -4011,7 +4040,7 @@
         <v/>
       </c>
       <c r="I167" s="15">
-        <f>IF(B167="","",IF(E167="","⛔ اختر النوع",IF(E167="مطبوعة","📷 مع الصورة",IF(D167="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D167,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D167,'البنود'!$F$7:$F$606)-N(F167),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F167)-SUMIF('البنود'!$B$7:$B$606,D167,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B167="","",IF(E167="","⛔ اختر النوع",IF(E167="مطبوعة","📷 مع الصورة",IF(D167="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D167,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D167,'البنود'!$F$7:$F$606)-N(F167),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F167)-SUMIF('البنود'!$B$7:$B$606,D167,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -4031,7 +4060,7 @@
         <v/>
       </c>
       <c r="I168" s="15">
-        <f>IF(B168="","",IF(E168="","⛔ اختر النوع",IF(E168="مطبوعة","📷 مع الصورة",IF(D168="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D168,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D168,'البنود'!$F$7:$F$606)-N(F168),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F168)-SUMIF('البنود'!$B$7:$B$606,D168,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B168="","",IF(E168="","⛔ اختر النوع",IF(E168="مطبوعة","📷 مع الصورة",IF(D168="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D168,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D168,'البنود'!$F$7:$F$606)-N(F168),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F168)-SUMIF('البنود'!$B$7:$B$606,D168,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -4051,7 +4080,7 @@
         <v/>
       </c>
       <c r="I169" s="15">
-        <f>IF(B169="","",IF(E169="","⛔ اختر النوع",IF(E169="مطبوعة","📷 مع الصورة",IF(D169="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D169,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D169,'البنود'!$F$7:$F$606)-N(F169),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F169)-SUMIF('البنود'!$B$7:$B$606,D169,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B169="","",IF(E169="","⛔ اختر النوع",IF(E169="مطبوعة","📷 مع الصورة",IF(D169="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D169,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D169,'البنود'!$F$7:$F$606)-N(F169),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F169)-SUMIF('البنود'!$B$7:$B$606,D169,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -4071,7 +4100,7 @@
         <v/>
       </c>
       <c r="I170" s="15">
-        <f>IF(B170="","",IF(E170="","⛔ اختر النوع",IF(E170="مطبوعة","📷 مع الصورة",IF(D170="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D170,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D170,'البنود'!$F$7:$F$606)-N(F170),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F170)-SUMIF('البنود'!$B$7:$B$606,D170,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B170="","",IF(E170="","⛔ اختر النوع",IF(E170="مطبوعة","📷 مع الصورة",IF(D170="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D170,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D170,'البنود'!$F$7:$F$606)-N(F170),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F170)-SUMIF('البنود'!$B$7:$B$606,D170,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -4091,7 +4120,7 @@
         <v/>
       </c>
       <c r="I171" s="15">
-        <f>IF(B171="","",IF(E171="","⛔ اختر النوع",IF(E171="مطبوعة","📷 مع الصورة",IF(D171="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D171,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D171,'البنود'!$F$7:$F$606)-N(F171),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F171)-SUMIF('البنود'!$B$7:$B$606,D171,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B171="","",IF(E171="","⛔ اختر النوع",IF(E171="مطبوعة","📷 مع الصورة",IF(D171="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D171,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D171,'البنود'!$F$7:$F$606)-N(F171),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F171)-SUMIF('البنود'!$B$7:$B$606,D171,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -4111,7 +4140,7 @@
         <v/>
       </c>
       <c r="I172" s="15">
-        <f>IF(B172="","",IF(E172="","⛔ اختر النوع",IF(E172="مطبوعة","📷 مع الصورة",IF(D172="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D172,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D172,'البنود'!$F$7:$F$606)-N(F172),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F172)-SUMIF('البنود'!$B$7:$B$606,D172,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B172="","",IF(E172="","⛔ اختر النوع",IF(E172="مطبوعة","📷 مع الصورة",IF(D172="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D172,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D172,'البنود'!$F$7:$F$606)-N(F172),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F172)-SUMIF('البنود'!$B$7:$B$606,D172,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -4131,7 +4160,7 @@
         <v/>
       </c>
       <c r="I173" s="15">
-        <f>IF(B173="","",IF(E173="","⛔ اختر النوع",IF(E173="مطبوعة","📷 مع الصورة",IF(D173="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D173,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D173,'البنود'!$F$7:$F$606)-N(F173),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F173)-SUMIF('البنود'!$B$7:$B$606,D173,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B173="","",IF(E173="","⛔ اختر النوع",IF(E173="مطبوعة","📷 مع الصورة",IF(D173="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D173,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D173,'البنود'!$F$7:$F$606)-N(F173),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F173)-SUMIF('البنود'!$B$7:$B$606,D173,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -4151,7 +4180,7 @@
         <v/>
       </c>
       <c r="I174" s="15">
-        <f>IF(B174="","",IF(E174="","⛔ اختر النوع",IF(E174="مطبوعة","📷 مع الصورة",IF(D174="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D174,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D174,'البنود'!$F$7:$F$606)-N(F174),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F174)-SUMIF('البنود'!$B$7:$B$606,D174,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B174="","",IF(E174="","⛔ اختر النوع",IF(E174="مطبوعة","📷 مع الصورة",IF(D174="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D174,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D174,'البنود'!$F$7:$F$606)-N(F174),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F174)-SUMIF('البنود'!$B$7:$B$606,D174,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -4171,7 +4200,7 @@
         <v/>
       </c>
       <c r="I175" s="15">
-        <f>IF(B175="","",IF(E175="","⛔ اختر النوع",IF(E175="مطبوعة","📷 مع الصورة",IF(D175="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D175,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D175,'البنود'!$F$7:$F$606)-N(F175),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F175)-SUMIF('البنود'!$B$7:$B$606,D175,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B175="","",IF(E175="","⛔ اختر النوع",IF(E175="مطبوعة","📷 مع الصورة",IF(D175="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D175,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D175,'البنود'!$F$7:$F$606)-N(F175),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F175)-SUMIF('البنود'!$B$7:$B$606,D175,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -4191,7 +4220,7 @@
         <v/>
       </c>
       <c r="I176" s="15">
-        <f>IF(B176="","",IF(E176="","⛔ اختر النوع",IF(E176="مطبوعة","📷 مع الصورة",IF(D176="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D176,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D176,'البنود'!$F$7:$F$606)-N(F176),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F176)-SUMIF('البنود'!$B$7:$B$606,D176,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B176="","",IF(E176="","⛔ اختر النوع",IF(E176="مطبوعة","📷 مع الصورة",IF(D176="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D176,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D176,'البنود'!$F$7:$F$606)-N(F176),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F176)-SUMIF('البنود'!$B$7:$B$606,D176,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -4211,7 +4240,7 @@
         <v/>
       </c>
       <c r="I177" s="15">
-        <f>IF(B177="","",IF(E177="","⛔ اختر النوع",IF(E177="مطبوعة","📷 مع الصورة",IF(D177="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D177,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D177,'البنود'!$F$7:$F$606)-N(F177),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F177)-SUMIF('البنود'!$B$7:$B$606,D177,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B177="","",IF(E177="","⛔ اختر النوع",IF(E177="مطبوعة","📷 مع الصورة",IF(D177="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D177,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D177,'البنود'!$F$7:$F$606)-N(F177),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F177)-SUMIF('البنود'!$B$7:$B$606,D177,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -4231,7 +4260,7 @@
         <v/>
       </c>
       <c r="I178" s="15">
-        <f>IF(B178="","",IF(E178="","⛔ اختر النوع",IF(E178="مطبوعة","📷 مع الصورة",IF(D178="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D178,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D178,'البنود'!$F$7:$F$606)-N(F178),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F178)-SUMIF('البنود'!$B$7:$B$606,D178,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B178="","",IF(E178="","⛔ اختر النوع",IF(E178="مطبوعة","📷 مع الصورة",IF(D178="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D178,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D178,'البنود'!$F$7:$F$606)-N(F178),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F178)-SUMIF('البنود'!$B$7:$B$606,D178,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -4251,7 +4280,7 @@
         <v/>
       </c>
       <c r="I179" s="15">
-        <f>IF(B179="","",IF(E179="","⛔ اختر النوع",IF(E179="مطبوعة","📷 مع الصورة",IF(D179="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D179,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D179,'البنود'!$F$7:$F$606)-N(F179),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F179)-SUMIF('البنود'!$B$7:$B$606,D179,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B179="","",IF(E179="","⛔ اختر النوع",IF(E179="مطبوعة","📷 مع الصورة",IF(D179="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D179,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D179,'البنود'!$F$7:$F$606)-N(F179),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F179)-SUMIF('البنود'!$B$7:$B$606,D179,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -4271,7 +4300,7 @@
         <v/>
       </c>
       <c r="I180" s="15">
-        <f>IF(B180="","",IF(E180="","⛔ اختر النوع",IF(E180="مطبوعة","📷 مع الصورة",IF(D180="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D180,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D180,'البنود'!$F$7:$F$606)-N(F180),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F180)-SUMIF('البنود'!$B$7:$B$606,D180,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B180="","",IF(E180="","⛔ اختر النوع",IF(E180="مطبوعة","📷 مع الصورة",IF(D180="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D180,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D180,'البنود'!$F$7:$F$606)-N(F180),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F180)-SUMIF('البنود'!$B$7:$B$606,D180,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -4291,7 +4320,7 @@
         <v/>
       </c>
       <c r="I181" s="15">
-        <f>IF(B181="","",IF(E181="","⛔ اختر النوع",IF(E181="مطبوعة","📷 مع الصورة",IF(D181="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D181,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D181,'البنود'!$F$7:$F$606)-N(F181),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F181)-SUMIF('البنود'!$B$7:$B$606,D181,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B181="","",IF(E181="","⛔ اختر النوع",IF(E181="مطبوعة","📷 مع الصورة",IF(D181="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D181,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D181,'البنود'!$F$7:$F$606)-N(F181),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F181)-SUMIF('البنود'!$B$7:$B$606,D181,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -4311,7 +4340,7 @@
         <v/>
       </c>
       <c r="I182" s="15">
-        <f>IF(B182="","",IF(E182="","⛔ اختر النوع",IF(E182="مطبوعة","📷 مع الصورة",IF(D182="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D182,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D182,'البنود'!$F$7:$F$606)-N(F182),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F182)-SUMIF('البنود'!$B$7:$B$606,D182,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B182="","",IF(E182="","⛔ اختر النوع",IF(E182="مطبوعة","📷 مع الصورة",IF(D182="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D182,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D182,'البنود'!$F$7:$F$606)-N(F182),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F182)-SUMIF('البنود'!$B$7:$B$606,D182,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -4331,7 +4360,7 @@
         <v/>
       </c>
       <c r="I183" s="15">
-        <f>IF(B183="","",IF(E183="","⛔ اختر النوع",IF(E183="مطبوعة","📷 مع الصورة",IF(D183="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D183,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D183,'البنود'!$F$7:$F$606)-N(F183),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F183)-SUMIF('البنود'!$B$7:$B$606,D183,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B183="","",IF(E183="","⛔ اختر النوع",IF(E183="مطبوعة","📷 مع الصورة",IF(D183="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D183,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D183,'البنود'!$F$7:$F$606)-N(F183),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F183)-SUMIF('البنود'!$B$7:$B$606,D183,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -4351,7 +4380,7 @@
         <v/>
       </c>
       <c r="I184" s="15">
-        <f>IF(B184="","",IF(E184="","⛔ اختر النوع",IF(E184="مطبوعة","📷 مع الصورة",IF(D184="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D184,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D184,'البنود'!$F$7:$F$606)-N(F184),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F184)-SUMIF('البنود'!$B$7:$B$606,D184,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B184="","",IF(E184="","⛔ اختر النوع",IF(E184="مطبوعة","📷 مع الصورة",IF(D184="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D184,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D184,'البنود'!$F$7:$F$606)-N(F184),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F184)-SUMIF('البنود'!$B$7:$B$606,D184,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -4371,7 +4400,7 @@
         <v/>
       </c>
       <c r="I185" s="15">
-        <f>IF(B185="","",IF(E185="","⛔ اختر النوع",IF(E185="مطبوعة","📷 مع الصورة",IF(D185="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D185,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D185,'البنود'!$F$7:$F$606)-N(F185),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F185)-SUMIF('البنود'!$B$7:$B$606,D185,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B185="","",IF(E185="","⛔ اختر النوع",IF(E185="مطبوعة","📷 مع الصورة",IF(D185="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D185,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D185,'البنود'!$F$7:$F$606)-N(F185),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F185)-SUMIF('البنود'!$B$7:$B$606,D185,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -4391,7 +4420,7 @@
         <v/>
       </c>
       <c r="I186" s="15">
-        <f>IF(B186="","",IF(E186="","⛔ اختر النوع",IF(E186="مطبوعة","📷 مع الصورة",IF(D186="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D186,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D186,'البنود'!$F$7:$F$606)-N(F186),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F186)-SUMIF('البنود'!$B$7:$B$606,D186,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B186="","",IF(E186="","⛔ اختر النوع",IF(E186="مطبوعة","📷 مع الصورة",IF(D186="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D186,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D186,'البنود'!$F$7:$F$606)-N(F186),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F186)-SUMIF('البنود'!$B$7:$B$606,D186,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -4411,7 +4440,7 @@
         <v/>
       </c>
       <c r="I187" s="15">
-        <f>IF(B187="","",IF(E187="","⛔ اختر النوع",IF(E187="مطبوعة","📷 مع الصورة",IF(D187="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D187,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D187,'البنود'!$F$7:$F$606)-N(F187),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F187)-SUMIF('البنود'!$B$7:$B$606,D187,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B187="","",IF(E187="","⛔ اختر النوع",IF(E187="مطبوعة","📷 مع الصورة",IF(D187="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D187,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D187,'البنود'!$F$7:$F$606)-N(F187),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F187)-SUMIF('البنود'!$B$7:$B$606,D187,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -4431,7 +4460,7 @@
         <v/>
       </c>
       <c r="I188" s="15">
-        <f>IF(B188="","",IF(E188="","⛔ اختر النوع",IF(E188="مطبوعة","📷 مع الصورة",IF(D188="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D188,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D188,'البنود'!$F$7:$F$606)-N(F188),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F188)-SUMIF('البنود'!$B$7:$B$606,D188,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B188="","",IF(E188="","⛔ اختر النوع",IF(E188="مطبوعة","📷 مع الصورة",IF(D188="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D188,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D188,'البنود'!$F$7:$F$606)-N(F188),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F188)-SUMIF('البنود'!$B$7:$B$606,D188,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -4451,7 +4480,7 @@
         <v/>
       </c>
       <c r="I189" s="15">
-        <f>IF(B189="","",IF(E189="","⛔ اختر النوع",IF(E189="مطبوعة","📷 مع الصورة",IF(D189="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D189,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D189,'البنود'!$F$7:$F$606)-N(F189),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F189)-SUMIF('البنود'!$B$7:$B$606,D189,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B189="","",IF(E189="","⛔ اختر النوع",IF(E189="مطبوعة","📷 مع الصورة",IF(D189="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D189,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D189,'البنود'!$F$7:$F$606)-N(F189),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F189)-SUMIF('البنود'!$B$7:$B$606,D189,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -4471,7 +4500,7 @@
         <v/>
       </c>
       <c r="I190" s="15">
-        <f>IF(B190="","",IF(E190="","⛔ اختر النوع",IF(E190="مطبوعة","📷 مع الصورة",IF(D190="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D190,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D190,'البنود'!$F$7:$F$606)-N(F190),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F190)-SUMIF('البنود'!$B$7:$B$606,D190,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B190="","",IF(E190="","⛔ اختر النوع",IF(E190="مطبوعة","📷 مع الصورة",IF(D190="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D190,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D190,'البنود'!$F$7:$F$606)-N(F190),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F190)-SUMIF('البنود'!$B$7:$B$606,D190,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -4491,7 +4520,7 @@
         <v/>
       </c>
       <c r="I191" s="15">
-        <f>IF(B191="","",IF(E191="","⛔ اختر النوع",IF(E191="مطبوعة","📷 مع الصورة",IF(D191="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D191,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D191,'البنود'!$F$7:$F$606)-N(F191),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F191)-SUMIF('البنود'!$B$7:$B$606,D191,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B191="","",IF(E191="","⛔ اختر النوع",IF(E191="مطبوعة","📷 مع الصورة",IF(D191="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D191,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D191,'البنود'!$F$7:$F$606)-N(F191),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F191)-SUMIF('البنود'!$B$7:$B$606,D191,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -4511,7 +4540,7 @@
         <v/>
       </c>
       <c r="I192" s="15">
-        <f>IF(B192="","",IF(E192="","⛔ اختر النوع",IF(E192="مطبوعة","📷 مع الصورة",IF(D192="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D192,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D192,'البنود'!$F$7:$F$606)-N(F192),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F192)-SUMIF('البنود'!$B$7:$B$606,D192,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B192="","",IF(E192="","⛔ اختر النوع",IF(E192="مطبوعة","📷 مع الصورة",IF(D192="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D192,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D192,'البنود'!$F$7:$F$606)-N(F192),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F192)-SUMIF('البنود'!$B$7:$B$606,D192,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -4531,7 +4560,7 @@
         <v/>
       </c>
       <c r="I193" s="15">
-        <f>IF(B193="","",IF(E193="","⛔ اختر النوع",IF(E193="مطبوعة","📷 مع الصورة",IF(D193="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D193,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D193,'البنود'!$F$7:$F$606)-N(F193),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F193)-SUMIF('البنود'!$B$7:$B$606,D193,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B193="","",IF(E193="","⛔ اختر النوع",IF(E193="مطبوعة","📷 مع الصورة",IF(D193="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D193,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D193,'البنود'!$F$7:$F$606)-N(F193),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F193)-SUMIF('البنود'!$B$7:$B$606,D193,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -4551,7 +4580,7 @@
         <v/>
       </c>
       <c r="I194" s="15">
-        <f>IF(B194="","",IF(E194="","⛔ اختر النوع",IF(E194="مطبوعة","📷 مع الصورة",IF(D194="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D194,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D194,'البنود'!$F$7:$F$606)-N(F194),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F194)-SUMIF('البنود'!$B$7:$B$606,D194,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B194="","",IF(E194="","⛔ اختر النوع",IF(E194="مطبوعة","📷 مع الصورة",IF(D194="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D194,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D194,'البنود'!$F$7:$F$606)-N(F194),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F194)-SUMIF('البنود'!$B$7:$B$606,D194,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -4571,7 +4600,7 @@
         <v/>
       </c>
       <c r="I195" s="15">
-        <f>IF(B195="","",IF(E195="","⛔ اختر النوع",IF(E195="مطبوعة","📷 مع الصورة",IF(D195="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D195,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D195,'البنود'!$F$7:$F$606)-N(F195),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F195)-SUMIF('البنود'!$B$7:$B$606,D195,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B195="","",IF(E195="","⛔ اختر النوع",IF(E195="مطبوعة","📷 مع الصورة",IF(D195="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D195,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D195,'البنود'!$F$7:$F$606)-N(F195),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F195)-SUMIF('البنود'!$B$7:$B$606,D195,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -4591,7 +4620,7 @@
         <v/>
       </c>
       <c r="I196" s="15">
-        <f>IF(B196="","",IF(E196="","⛔ اختر النوع",IF(E196="مطبوعة","📷 مع الصورة",IF(D196="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D196,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D196,'البنود'!$F$7:$F$606)-N(F196),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F196)-SUMIF('البنود'!$B$7:$B$606,D196,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B196="","",IF(E196="","⛔ اختر النوع",IF(E196="مطبوعة","📷 مع الصورة",IF(D196="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D196,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D196,'البنود'!$F$7:$F$606)-N(F196),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F196)-SUMIF('البنود'!$B$7:$B$606,D196,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -4611,7 +4640,7 @@
         <v/>
       </c>
       <c r="I197" s="15">
-        <f>IF(B197="","",IF(E197="","⛔ اختر النوع",IF(E197="مطبوعة","📷 مع الصورة",IF(D197="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D197,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D197,'البنود'!$F$7:$F$606)-N(F197),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F197)-SUMIF('البنود'!$B$7:$B$606,D197,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B197="","",IF(E197="","⛔ اختر النوع",IF(E197="مطبوعة","📷 مع الصورة",IF(D197="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D197,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D197,'البنود'!$F$7:$F$606)-N(F197),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F197)-SUMIF('البنود'!$B$7:$B$606,D197,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -4631,7 +4660,7 @@
         <v/>
       </c>
       <c r="I198" s="15">
-        <f>IF(B198="","",IF(E198="","⛔ اختر النوع",IF(E198="مطبوعة","📷 مع الصورة",IF(D198="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D198,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D198,'البنود'!$F$7:$F$606)-N(F198),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F198)-SUMIF('البنود'!$B$7:$B$606,D198,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B198="","",IF(E198="","⛔ اختر النوع",IF(E198="مطبوعة","📷 مع الصورة",IF(D198="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D198,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D198,'البنود'!$F$7:$F$606)-N(F198),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F198)-SUMIF('البنود'!$B$7:$B$606,D198,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -4651,7 +4680,7 @@
         <v/>
       </c>
       <c r="I199" s="15">
-        <f>IF(B199="","",IF(E199="","⛔ اختر النوع",IF(E199="مطبوعة","📷 مع الصورة",IF(D199="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D199,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D199,'البنود'!$F$7:$F$606)-N(F199),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F199)-SUMIF('البنود'!$B$7:$B$606,D199,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B199="","",IF(E199="","⛔ اختر النوع",IF(E199="مطبوعة","📷 مع الصورة",IF(D199="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D199,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D199,'البنود'!$F$7:$F$606)-N(F199),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F199)-SUMIF('البنود'!$B$7:$B$606,D199,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -4671,7 +4700,7 @@
         <v/>
       </c>
       <c r="I200" s="15">
-        <f>IF(B200="","",IF(E200="","⛔ اختر النوع",IF(E200="مطبوعة","📷 مع الصورة",IF(D200="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D200,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D200,'البنود'!$F$7:$F$606)-N(F200),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F200)-SUMIF('البنود'!$B$7:$B$606,D200,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B200="","",IF(E200="","⛔ اختر النوع",IF(E200="مطبوعة","📷 مع الصورة",IF(D200="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D200,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D200,'البنود'!$F$7:$F$606)-N(F200),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F200)-SUMIF('البنود'!$B$7:$B$606,D200,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -4691,7 +4720,7 @@
         <v/>
       </c>
       <c r="I201" s="15">
-        <f>IF(B201="","",IF(E201="","⛔ اختر النوع",IF(E201="مطبوعة","📷 مع الصورة",IF(D201="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D201,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D201,'البنود'!$F$7:$F$606)-N(F201),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F201)-SUMIF('البنود'!$B$7:$B$606,D201,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B201="","",IF(E201="","⛔ اختر النوع",IF(E201="مطبوعة","📷 مع الصورة",IF(D201="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D201,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D201,'البنود'!$F$7:$F$606)-N(F201),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F201)-SUMIF('البنود'!$B$7:$B$606,D201,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -4711,7 +4740,7 @@
         <v/>
       </c>
       <c r="I202" s="15">
-        <f>IF(B202="","",IF(E202="","⛔ اختر النوع",IF(E202="مطبوعة","📷 مع الصورة",IF(D202="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D202,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D202,'البنود'!$F$7:$F$606)-N(F202),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F202)-SUMIF('البنود'!$B$7:$B$606,D202,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B202="","",IF(E202="","⛔ اختر النوع",IF(E202="مطبوعة","📷 مع الصورة",IF(D202="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D202,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D202,'البنود'!$F$7:$F$606)-N(F202),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F202)-SUMIF('البنود'!$B$7:$B$606,D202,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -4731,7 +4760,7 @@
         <v/>
       </c>
       <c r="I203" s="15">
-        <f>IF(B203="","",IF(E203="","⛔ اختر النوع",IF(E203="مطبوعة","📷 مع الصورة",IF(D203="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D203,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D203,'البنود'!$F$7:$F$606)-N(F203),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F203)-SUMIF('البنود'!$B$7:$B$606,D203,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B203="","",IF(E203="","⛔ اختر النوع",IF(E203="مطبوعة","📷 مع الصورة",IF(D203="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D203,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D203,'البنود'!$F$7:$F$606)-N(F203),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F203)-SUMIF('البنود'!$B$7:$B$606,D203,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -4751,7 +4780,7 @@
         <v/>
       </c>
       <c r="I204" s="15">
-        <f>IF(B204="","",IF(E204="","⛔ اختر النوع",IF(E204="مطبوعة","📷 مع الصورة",IF(D204="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D204,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D204,'البنود'!$F$7:$F$606)-N(F204),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F204)-SUMIF('البنود'!$B$7:$B$606,D204,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B204="","",IF(E204="","⛔ اختر النوع",IF(E204="مطبوعة","📷 مع الصورة",IF(D204="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D204,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D204,'البنود'!$F$7:$F$606)-N(F204),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F204)-SUMIF('البنود'!$B$7:$B$606,D204,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -4771,7 +4800,7 @@
         <v/>
       </c>
       <c r="I205" s="15">
-        <f>IF(B205="","",IF(E205="","⛔ اختر النوع",IF(E205="مطبوعة","📷 مع الصورة",IF(D205="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D205,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D205,'البنود'!$F$7:$F$606)-N(F205),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F205)-SUMIF('البنود'!$B$7:$B$606,D205,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B205="","",IF(E205="","⛔ اختر النوع",IF(E205="مطبوعة","📷 مع الصورة",IF(D205="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D205,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D205,'البنود'!$F$7:$F$606)-N(F205),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F205)-SUMIF('البنود'!$B$7:$B$606,D205,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -4791,7 +4820,7 @@
         <v/>
       </c>
       <c r="I206" s="15">
-        <f>IF(B206="","",IF(E206="","⛔ اختر النوع",IF(E206="مطبوعة","📷 مع الصورة",IF(D206="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D206,'البنود'!$F$7:$F$606)=0,"⛔ ما في بنود مُدخلة",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D206,'البنود'!$F$7:$F$606)-N(F206),3)=0,"✅ البنود مطابقة","⛔ فرق "&amp;TEXT(N(F206)-SUMIF('البنود'!$B$7:$B$606,D206,'البنود'!$F$7:$F$606),"0.000")))))))</f>
+        <f>IF(B206="","",IF(E206="","⛔ اختر النوع",IF(E206="مطبوعة","📷 مع الصورة",IF(D206="","⛔ اكتب رقم الفاتورة",IF(SUMIF('البنود'!$B$7:$B$606,D206,'البنود'!$F$7:$F$606)=0,"🟡 بنودها ما انزلت",IF(ROUND(SUMIF('البنود'!$B$7:$B$606,D206,'البنود'!$F$7:$F$606)-N(F206),3)=0,"✅ خلصت — البنود مطابقة","⛔ فرق "&amp;TEXT(N(F206)-SUMIF('البنود'!$B$7:$B$606,D206,'البنود'!$F$7:$F$606),"0.000")))))))</f>
         <v/>
       </c>
     </row>
@@ -4834,11 +4863,14 @@
   </conditionalFormatting>
   <conditionalFormatting sqref="C7:C206">
     <cfRule type="expression" priority="6" dxfId="5">
+      <formula>AND($B7&lt;&gt;"",$C7&lt;&gt;"",OR(INT($C7/1000000)&lt;1,INT($C7/1000000)&gt;31,MOD(INT($C7/10000),100)&lt;1,MOD(INT($C7/10000),100)&gt;12,MOD($C7,10000)&lt;2020))</formula>
+    </cfRule>
+    <cfRule type="expression" priority="7" dxfId="6">
       <formula>AND($B7&lt;&gt;"",$C7="")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F7:F206">
-    <cfRule type="expression" priority="7" dxfId="5">
+    <cfRule type="expression" priority="8" dxfId="6">
       <formula>AND($B7&lt;&gt;"",$F7="")</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4858,7 +4890,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F608"/>
+  <dimension ref="A1:K608"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -4867,6 +4899,11 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="3" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="26" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -4915,6 +4952,10 @@
         <f>IF(B4=0,"لا يوجد بنود",IF(COUNTIF(A7:A606,"⛔*")&gt;0,"⛔ في بند رقم فاتورته مش موجود","✅ كل البنود مربوطة"))</f>
         <v/>
       </c>
+      <c r="H4" s="7">
+        <f>IF(COUNTIF('الفواتير'!$E$7:$E$206,"يدوية")=0,"لا يوجد فواتير يدوية",COUNTIF(K7:K206,"✅*")&amp;" مكتملة من "&amp;COUNTIF('الفواتير'!$E$7:$E$206,"يدوية")&amp;" فاتورة يدوية")</f>
+        <v/>
+      </c>
     </row>
     <row r="5"/>
     <row r="6" ht="28" customHeight="1">
@@ -4948,6 +4989,26 @@
           <t>الإجمالي</t>
         </is>
       </c>
+      <c r="H6" s="20" t="inlineStr">
+        <is>
+          <t>رقم الفاتورة اليدوية</t>
+        </is>
+      </c>
+      <c r="I6" s="20" t="inlineStr">
+        <is>
+          <t>مجموع الفاتورة</t>
+        </is>
+      </c>
+      <c r="J6" s="20" t="inlineStr">
+        <is>
+          <t>مجموع بنودها</t>
+        </is>
+      </c>
+      <c r="K6" s="20" t="inlineStr">
+        <is>
+          <t>خلصت؟</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="21" customHeight="1">
       <c r="A7" s="9">
@@ -4962,6 +5023,22 @@
         <f>IF(C7="","",N(D7)*N(E7))</f>
         <v/>
       </c>
+      <c r="H7" s="9">
+        <f>IF('الفواتير'!$E7="يدوية",'الفواتير'!$D7,"")</f>
+        <v/>
+      </c>
+      <c r="I7" s="14">
+        <f>IF($H7="","",'الفواتير'!$F7)</f>
+        <v/>
+      </c>
+      <c r="J7" s="14">
+        <f>IF($H7="","",SUMIF($B$7:$B$606,$H7,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K7" s="15">
+        <f>IF($H7="","",IF($H7=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H7)=0,"🟡 ما انزلت بنودها",IF(ROUND($I7-$J7,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I7-$J7,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="8" ht="21" customHeight="1">
       <c r="A8" s="9">
@@ -4976,6 +5053,22 @@
         <f>IF(C8="","",N(D8)*N(E8))</f>
         <v/>
       </c>
+      <c r="H8" s="9">
+        <f>IF('الفواتير'!$E8="يدوية",'الفواتير'!$D8,"")</f>
+        <v/>
+      </c>
+      <c r="I8" s="14">
+        <f>IF($H8="","",'الفواتير'!$F8)</f>
+        <v/>
+      </c>
+      <c r="J8" s="14">
+        <f>IF($H8="","",SUMIF($B$7:$B$606,$H8,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K8" s="15">
+        <f>IF($H8="","",IF($H8=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H8)=0,"🟡 ما انزلت بنودها",IF(ROUND($I8-$J8,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I8-$J8,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="9" ht="21" customHeight="1">
       <c r="A9" s="9">
@@ -4990,6 +5083,22 @@
         <f>IF(C9="","",N(D9)*N(E9))</f>
         <v/>
       </c>
+      <c r="H9" s="9">
+        <f>IF('الفواتير'!$E9="يدوية",'الفواتير'!$D9,"")</f>
+        <v/>
+      </c>
+      <c r="I9" s="14">
+        <f>IF($H9="","",'الفواتير'!$F9)</f>
+        <v/>
+      </c>
+      <c r="J9" s="14">
+        <f>IF($H9="","",SUMIF($B$7:$B$606,$H9,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K9" s="15">
+        <f>IF($H9="","",IF($H9=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H9)=0,"🟡 ما انزلت بنودها",IF(ROUND($I9-$J9,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I9-$J9,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="10" ht="21" customHeight="1">
       <c r="A10" s="9">
@@ -5004,6 +5113,22 @@
         <f>IF(C10="","",N(D10)*N(E10))</f>
         <v/>
       </c>
+      <c r="H10" s="9">
+        <f>IF('الفواتير'!$E10="يدوية",'الفواتير'!$D10,"")</f>
+        <v/>
+      </c>
+      <c r="I10" s="14">
+        <f>IF($H10="","",'الفواتير'!$F10)</f>
+        <v/>
+      </c>
+      <c r="J10" s="14">
+        <f>IF($H10="","",SUMIF($B$7:$B$606,$H10,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K10" s="15">
+        <f>IF($H10="","",IF($H10=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H10)=0,"🟡 ما انزلت بنودها",IF(ROUND($I10-$J10,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I10-$J10,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="11" ht="21" customHeight="1">
       <c r="A11" s="9">
@@ -5018,6 +5143,22 @@
         <f>IF(C11="","",N(D11)*N(E11))</f>
         <v/>
       </c>
+      <c r="H11" s="9">
+        <f>IF('الفواتير'!$E11="يدوية",'الفواتير'!$D11,"")</f>
+        <v/>
+      </c>
+      <c r="I11" s="14">
+        <f>IF($H11="","",'الفواتير'!$F11)</f>
+        <v/>
+      </c>
+      <c r="J11" s="14">
+        <f>IF($H11="","",SUMIF($B$7:$B$606,$H11,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K11" s="15">
+        <f>IF($H11="","",IF($H11=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H11)=0,"🟡 ما انزلت بنودها",IF(ROUND($I11-$J11,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I11-$J11,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="12" ht="21" customHeight="1">
       <c r="A12" s="9">
@@ -5032,6 +5173,22 @@
         <f>IF(C12="","",N(D12)*N(E12))</f>
         <v/>
       </c>
+      <c r="H12" s="9">
+        <f>IF('الفواتير'!$E12="يدوية",'الفواتير'!$D12,"")</f>
+        <v/>
+      </c>
+      <c r="I12" s="14">
+        <f>IF($H12="","",'الفواتير'!$F12)</f>
+        <v/>
+      </c>
+      <c r="J12" s="14">
+        <f>IF($H12="","",SUMIF($B$7:$B$606,$H12,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K12" s="15">
+        <f>IF($H12="","",IF($H12=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H12)=0,"🟡 ما انزلت بنودها",IF(ROUND($I12-$J12,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I12-$J12,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="13" ht="21" customHeight="1">
       <c r="A13" s="9">
@@ -5046,6 +5203,22 @@
         <f>IF(C13="","",N(D13)*N(E13))</f>
         <v/>
       </c>
+      <c r="H13" s="9">
+        <f>IF('الفواتير'!$E13="يدوية",'الفواتير'!$D13,"")</f>
+        <v/>
+      </c>
+      <c r="I13" s="14">
+        <f>IF($H13="","",'الفواتير'!$F13)</f>
+        <v/>
+      </c>
+      <c r="J13" s="14">
+        <f>IF($H13="","",SUMIF($B$7:$B$606,$H13,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K13" s="15">
+        <f>IF($H13="","",IF($H13=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H13)=0,"🟡 ما انزلت بنودها",IF(ROUND($I13-$J13,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I13-$J13,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="14" ht="21" customHeight="1">
       <c r="A14" s="9">
@@ -5060,6 +5233,22 @@
         <f>IF(C14="","",N(D14)*N(E14))</f>
         <v/>
       </c>
+      <c r="H14" s="9">
+        <f>IF('الفواتير'!$E14="يدوية",'الفواتير'!$D14,"")</f>
+        <v/>
+      </c>
+      <c r="I14" s="14">
+        <f>IF($H14="","",'الفواتير'!$F14)</f>
+        <v/>
+      </c>
+      <c r="J14" s="14">
+        <f>IF($H14="","",SUMIF($B$7:$B$606,$H14,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K14" s="15">
+        <f>IF($H14="","",IF($H14=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H14)=0,"🟡 ما انزلت بنودها",IF(ROUND($I14-$J14,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I14-$J14,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="15" ht="21" customHeight="1">
       <c r="A15" s="9">
@@ -5074,6 +5263,22 @@
         <f>IF(C15="","",N(D15)*N(E15))</f>
         <v/>
       </c>
+      <c r="H15" s="9">
+        <f>IF('الفواتير'!$E15="يدوية",'الفواتير'!$D15,"")</f>
+        <v/>
+      </c>
+      <c r="I15" s="14">
+        <f>IF($H15="","",'الفواتير'!$F15)</f>
+        <v/>
+      </c>
+      <c r="J15" s="14">
+        <f>IF($H15="","",SUMIF($B$7:$B$606,$H15,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K15" s="15">
+        <f>IF($H15="","",IF($H15=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H15)=0,"🟡 ما انزلت بنودها",IF(ROUND($I15-$J15,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I15-$J15,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="16" ht="21" customHeight="1">
       <c r="A16" s="9">
@@ -5088,6 +5293,22 @@
         <f>IF(C16="","",N(D16)*N(E16))</f>
         <v/>
       </c>
+      <c r="H16" s="9">
+        <f>IF('الفواتير'!$E16="يدوية",'الفواتير'!$D16,"")</f>
+        <v/>
+      </c>
+      <c r="I16" s="14">
+        <f>IF($H16="","",'الفواتير'!$F16)</f>
+        <v/>
+      </c>
+      <c r="J16" s="14">
+        <f>IF($H16="","",SUMIF($B$7:$B$606,$H16,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K16" s="15">
+        <f>IF($H16="","",IF($H16=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H16)=0,"🟡 ما انزلت بنودها",IF(ROUND($I16-$J16,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I16-$J16,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="17" ht="21" customHeight="1">
       <c r="A17" s="9">
@@ -5102,6 +5323,22 @@
         <f>IF(C17="","",N(D17)*N(E17))</f>
         <v/>
       </c>
+      <c r="H17" s="9">
+        <f>IF('الفواتير'!$E17="يدوية",'الفواتير'!$D17,"")</f>
+        <v/>
+      </c>
+      <c r="I17" s="14">
+        <f>IF($H17="","",'الفواتير'!$F17)</f>
+        <v/>
+      </c>
+      <c r="J17" s="14">
+        <f>IF($H17="","",SUMIF($B$7:$B$606,$H17,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K17" s="15">
+        <f>IF($H17="","",IF($H17=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H17)=0,"🟡 ما انزلت بنودها",IF(ROUND($I17-$J17,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I17-$J17,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="18" ht="21" customHeight="1">
       <c r="A18" s="9">
@@ -5116,6 +5353,22 @@
         <f>IF(C18="","",N(D18)*N(E18))</f>
         <v/>
       </c>
+      <c r="H18" s="9">
+        <f>IF('الفواتير'!$E18="يدوية",'الفواتير'!$D18,"")</f>
+        <v/>
+      </c>
+      <c r="I18" s="14">
+        <f>IF($H18="","",'الفواتير'!$F18)</f>
+        <v/>
+      </c>
+      <c r="J18" s="14">
+        <f>IF($H18="","",SUMIF($B$7:$B$606,$H18,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K18" s="15">
+        <f>IF($H18="","",IF($H18=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H18)=0,"🟡 ما انزلت بنودها",IF(ROUND($I18-$J18,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I18-$J18,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="19" ht="21" customHeight="1">
       <c r="A19" s="9">
@@ -5130,6 +5383,22 @@
         <f>IF(C19="","",N(D19)*N(E19))</f>
         <v/>
       </c>
+      <c r="H19" s="9">
+        <f>IF('الفواتير'!$E19="يدوية",'الفواتير'!$D19,"")</f>
+        <v/>
+      </c>
+      <c r="I19" s="14">
+        <f>IF($H19="","",'الفواتير'!$F19)</f>
+        <v/>
+      </c>
+      <c r="J19" s="14">
+        <f>IF($H19="","",SUMIF($B$7:$B$606,$H19,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K19" s="15">
+        <f>IF($H19="","",IF($H19=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H19)=0,"🟡 ما انزلت بنودها",IF(ROUND($I19-$J19,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I19-$J19,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="20" ht="21" customHeight="1">
       <c r="A20" s="9">
@@ -5144,6 +5413,22 @@
         <f>IF(C20="","",N(D20)*N(E20))</f>
         <v/>
       </c>
+      <c r="H20" s="9">
+        <f>IF('الفواتير'!$E20="يدوية",'الفواتير'!$D20,"")</f>
+        <v/>
+      </c>
+      <c r="I20" s="14">
+        <f>IF($H20="","",'الفواتير'!$F20)</f>
+        <v/>
+      </c>
+      <c r="J20" s="14">
+        <f>IF($H20="","",SUMIF($B$7:$B$606,$H20,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K20" s="15">
+        <f>IF($H20="","",IF($H20=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H20)=0,"🟡 ما انزلت بنودها",IF(ROUND($I20-$J20,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I20-$J20,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="21" ht="21" customHeight="1">
       <c r="A21" s="9">
@@ -5158,6 +5443,22 @@
         <f>IF(C21="","",N(D21)*N(E21))</f>
         <v/>
       </c>
+      <c r="H21" s="9">
+        <f>IF('الفواتير'!$E21="يدوية",'الفواتير'!$D21,"")</f>
+        <v/>
+      </c>
+      <c r="I21" s="14">
+        <f>IF($H21="","",'الفواتير'!$F21)</f>
+        <v/>
+      </c>
+      <c r="J21" s="14">
+        <f>IF($H21="","",SUMIF($B$7:$B$606,$H21,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K21" s="15">
+        <f>IF($H21="","",IF($H21=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H21)=0,"🟡 ما انزلت بنودها",IF(ROUND($I21-$J21,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I21-$J21,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="22" ht="21" customHeight="1">
       <c r="A22" s="9">
@@ -5172,6 +5473,22 @@
         <f>IF(C22="","",N(D22)*N(E22))</f>
         <v/>
       </c>
+      <c r="H22" s="9">
+        <f>IF('الفواتير'!$E22="يدوية",'الفواتير'!$D22,"")</f>
+        <v/>
+      </c>
+      <c r="I22" s="14">
+        <f>IF($H22="","",'الفواتير'!$F22)</f>
+        <v/>
+      </c>
+      <c r="J22" s="14">
+        <f>IF($H22="","",SUMIF($B$7:$B$606,$H22,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K22" s="15">
+        <f>IF($H22="","",IF($H22=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H22)=0,"🟡 ما انزلت بنودها",IF(ROUND($I22-$J22,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I22-$J22,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="23" ht="21" customHeight="1">
       <c r="A23" s="9">
@@ -5186,6 +5503,22 @@
         <f>IF(C23="","",N(D23)*N(E23))</f>
         <v/>
       </c>
+      <c r="H23" s="9">
+        <f>IF('الفواتير'!$E23="يدوية",'الفواتير'!$D23,"")</f>
+        <v/>
+      </c>
+      <c r="I23" s="14">
+        <f>IF($H23="","",'الفواتير'!$F23)</f>
+        <v/>
+      </c>
+      <c r="J23" s="14">
+        <f>IF($H23="","",SUMIF($B$7:$B$606,$H23,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K23" s="15">
+        <f>IF($H23="","",IF($H23=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H23)=0,"🟡 ما انزلت بنودها",IF(ROUND($I23-$J23,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I23-$J23,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="24" ht="21" customHeight="1">
       <c r="A24" s="9">
@@ -5200,6 +5533,22 @@
         <f>IF(C24="","",N(D24)*N(E24))</f>
         <v/>
       </c>
+      <c r="H24" s="9">
+        <f>IF('الفواتير'!$E24="يدوية",'الفواتير'!$D24,"")</f>
+        <v/>
+      </c>
+      <c r="I24" s="14">
+        <f>IF($H24="","",'الفواتير'!$F24)</f>
+        <v/>
+      </c>
+      <c r="J24" s="14">
+        <f>IF($H24="","",SUMIF($B$7:$B$606,$H24,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K24" s="15">
+        <f>IF($H24="","",IF($H24=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H24)=0,"🟡 ما انزلت بنودها",IF(ROUND($I24-$J24,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I24-$J24,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="25" ht="21" customHeight="1">
       <c r="A25" s="9">
@@ -5214,6 +5563,22 @@
         <f>IF(C25="","",N(D25)*N(E25))</f>
         <v/>
       </c>
+      <c r="H25" s="9">
+        <f>IF('الفواتير'!$E25="يدوية",'الفواتير'!$D25,"")</f>
+        <v/>
+      </c>
+      <c r="I25" s="14">
+        <f>IF($H25="","",'الفواتير'!$F25)</f>
+        <v/>
+      </c>
+      <c r="J25" s="14">
+        <f>IF($H25="","",SUMIF($B$7:$B$606,$H25,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K25" s="15">
+        <f>IF($H25="","",IF($H25=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H25)=0,"🟡 ما انزلت بنودها",IF(ROUND($I25-$J25,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I25-$J25,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="26" ht="21" customHeight="1">
       <c r="A26" s="9">
@@ -5228,6 +5593,22 @@
         <f>IF(C26="","",N(D26)*N(E26))</f>
         <v/>
       </c>
+      <c r="H26" s="9">
+        <f>IF('الفواتير'!$E26="يدوية",'الفواتير'!$D26,"")</f>
+        <v/>
+      </c>
+      <c r="I26" s="14">
+        <f>IF($H26="","",'الفواتير'!$F26)</f>
+        <v/>
+      </c>
+      <c r="J26" s="14">
+        <f>IF($H26="","",SUMIF($B$7:$B$606,$H26,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K26" s="15">
+        <f>IF($H26="","",IF($H26=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H26)=0,"🟡 ما انزلت بنودها",IF(ROUND($I26-$J26,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I26-$J26,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="27" ht="21" customHeight="1">
       <c r="A27" s="9">
@@ -5242,6 +5623,22 @@
         <f>IF(C27="","",N(D27)*N(E27))</f>
         <v/>
       </c>
+      <c r="H27" s="9">
+        <f>IF('الفواتير'!$E27="يدوية",'الفواتير'!$D27,"")</f>
+        <v/>
+      </c>
+      <c r="I27" s="14">
+        <f>IF($H27="","",'الفواتير'!$F27)</f>
+        <v/>
+      </c>
+      <c r="J27" s="14">
+        <f>IF($H27="","",SUMIF($B$7:$B$606,$H27,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K27" s="15">
+        <f>IF($H27="","",IF($H27=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H27)=0,"🟡 ما انزلت بنودها",IF(ROUND($I27-$J27,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I27-$J27,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="28" ht="21" customHeight="1">
       <c r="A28" s="9">
@@ -5256,6 +5653,22 @@
         <f>IF(C28="","",N(D28)*N(E28))</f>
         <v/>
       </c>
+      <c r="H28" s="9">
+        <f>IF('الفواتير'!$E28="يدوية",'الفواتير'!$D28,"")</f>
+        <v/>
+      </c>
+      <c r="I28" s="14">
+        <f>IF($H28="","",'الفواتير'!$F28)</f>
+        <v/>
+      </c>
+      <c r="J28" s="14">
+        <f>IF($H28="","",SUMIF($B$7:$B$606,$H28,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K28" s="15">
+        <f>IF($H28="","",IF($H28=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H28)=0,"🟡 ما انزلت بنودها",IF(ROUND($I28-$J28,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I28-$J28,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="29" ht="21" customHeight="1">
       <c r="A29" s="9">
@@ -5270,6 +5683,22 @@
         <f>IF(C29="","",N(D29)*N(E29))</f>
         <v/>
       </c>
+      <c r="H29" s="9">
+        <f>IF('الفواتير'!$E29="يدوية",'الفواتير'!$D29,"")</f>
+        <v/>
+      </c>
+      <c r="I29" s="14">
+        <f>IF($H29="","",'الفواتير'!$F29)</f>
+        <v/>
+      </c>
+      <c r="J29" s="14">
+        <f>IF($H29="","",SUMIF($B$7:$B$606,$H29,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K29" s="15">
+        <f>IF($H29="","",IF($H29=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H29)=0,"🟡 ما انزلت بنودها",IF(ROUND($I29-$J29,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I29-$J29,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="30" ht="21" customHeight="1">
       <c r="A30" s="9">
@@ -5284,6 +5713,22 @@
         <f>IF(C30="","",N(D30)*N(E30))</f>
         <v/>
       </c>
+      <c r="H30" s="9">
+        <f>IF('الفواتير'!$E30="يدوية",'الفواتير'!$D30,"")</f>
+        <v/>
+      </c>
+      <c r="I30" s="14">
+        <f>IF($H30="","",'الفواتير'!$F30)</f>
+        <v/>
+      </c>
+      <c r="J30" s="14">
+        <f>IF($H30="","",SUMIF($B$7:$B$606,$H30,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K30" s="15">
+        <f>IF($H30="","",IF($H30=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H30)=0,"🟡 ما انزلت بنودها",IF(ROUND($I30-$J30,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I30-$J30,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="31" ht="21" customHeight="1">
       <c r="A31" s="9">
@@ -5298,6 +5743,22 @@
         <f>IF(C31="","",N(D31)*N(E31))</f>
         <v/>
       </c>
+      <c r="H31" s="9">
+        <f>IF('الفواتير'!$E31="يدوية",'الفواتير'!$D31,"")</f>
+        <v/>
+      </c>
+      <c r="I31" s="14">
+        <f>IF($H31="","",'الفواتير'!$F31)</f>
+        <v/>
+      </c>
+      <c r="J31" s="14">
+        <f>IF($H31="","",SUMIF($B$7:$B$606,$H31,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K31" s="15">
+        <f>IF($H31="","",IF($H31=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H31)=0,"🟡 ما انزلت بنودها",IF(ROUND($I31-$J31,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I31-$J31,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="32" ht="21" customHeight="1">
       <c r="A32" s="9">
@@ -5312,6 +5773,22 @@
         <f>IF(C32="","",N(D32)*N(E32))</f>
         <v/>
       </c>
+      <c r="H32" s="9">
+        <f>IF('الفواتير'!$E32="يدوية",'الفواتير'!$D32,"")</f>
+        <v/>
+      </c>
+      <c r="I32" s="14">
+        <f>IF($H32="","",'الفواتير'!$F32)</f>
+        <v/>
+      </c>
+      <c r="J32" s="14">
+        <f>IF($H32="","",SUMIF($B$7:$B$606,$H32,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K32" s="15">
+        <f>IF($H32="","",IF($H32=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H32)=0,"🟡 ما انزلت بنودها",IF(ROUND($I32-$J32,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I32-$J32,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="33" ht="21" customHeight="1">
       <c r="A33" s="9">
@@ -5326,6 +5803,22 @@
         <f>IF(C33="","",N(D33)*N(E33))</f>
         <v/>
       </c>
+      <c r="H33" s="9">
+        <f>IF('الفواتير'!$E33="يدوية",'الفواتير'!$D33,"")</f>
+        <v/>
+      </c>
+      <c r="I33" s="14">
+        <f>IF($H33="","",'الفواتير'!$F33)</f>
+        <v/>
+      </c>
+      <c r="J33" s="14">
+        <f>IF($H33="","",SUMIF($B$7:$B$606,$H33,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K33" s="15">
+        <f>IF($H33="","",IF($H33=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H33)=0,"🟡 ما انزلت بنودها",IF(ROUND($I33-$J33,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I33-$J33,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="34" ht="21" customHeight="1">
       <c r="A34" s="9">
@@ -5340,6 +5833,22 @@
         <f>IF(C34="","",N(D34)*N(E34))</f>
         <v/>
       </c>
+      <c r="H34" s="9">
+        <f>IF('الفواتير'!$E34="يدوية",'الفواتير'!$D34,"")</f>
+        <v/>
+      </c>
+      <c r="I34" s="14">
+        <f>IF($H34="","",'الفواتير'!$F34)</f>
+        <v/>
+      </c>
+      <c r="J34" s="14">
+        <f>IF($H34="","",SUMIF($B$7:$B$606,$H34,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K34" s="15">
+        <f>IF($H34="","",IF($H34=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H34)=0,"🟡 ما انزلت بنودها",IF(ROUND($I34-$J34,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I34-$J34,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="35" ht="21" customHeight="1">
       <c r="A35" s="9">
@@ -5354,6 +5863,22 @@
         <f>IF(C35="","",N(D35)*N(E35))</f>
         <v/>
       </c>
+      <c r="H35" s="9">
+        <f>IF('الفواتير'!$E35="يدوية",'الفواتير'!$D35,"")</f>
+        <v/>
+      </c>
+      <c r="I35" s="14">
+        <f>IF($H35="","",'الفواتير'!$F35)</f>
+        <v/>
+      </c>
+      <c r="J35" s="14">
+        <f>IF($H35="","",SUMIF($B$7:$B$606,$H35,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K35" s="15">
+        <f>IF($H35="","",IF($H35=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H35)=0,"🟡 ما انزلت بنودها",IF(ROUND($I35-$J35,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I35-$J35,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="36" ht="21" customHeight="1">
       <c r="A36" s="9">
@@ -5368,6 +5893,22 @@
         <f>IF(C36="","",N(D36)*N(E36))</f>
         <v/>
       </c>
+      <c r="H36" s="9">
+        <f>IF('الفواتير'!$E36="يدوية",'الفواتير'!$D36,"")</f>
+        <v/>
+      </c>
+      <c r="I36" s="14">
+        <f>IF($H36="","",'الفواتير'!$F36)</f>
+        <v/>
+      </c>
+      <c r="J36" s="14">
+        <f>IF($H36="","",SUMIF($B$7:$B$606,$H36,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K36" s="15">
+        <f>IF($H36="","",IF($H36=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H36)=0,"🟡 ما انزلت بنودها",IF(ROUND($I36-$J36,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I36-$J36,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="37" ht="21" customHeight="1">
       <c r="A37" s="9">
@@ -5382,6 +5923,22 @@
         <f>IF(C37="","",N(D37)*N(E37))</f>
         <v/>
       </c>
+      <c r="H37" s="9">
+        <f>IF('الفواتير'!$E37="يدوية",'الفواتير'!$D37,"")</f>
+        <v/>
+      </c>
+      <c r="I37" s="14">
+        <f>IF($H37="","",'الفواتير'!$F37)</f>
+        <v/>
+      </c>
+      <c r="J37" s="14">
+        <f>IF($H37="","",SUMIF($B$7:$B$606,$H37,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K37" s="15">
+        <f>IF($H37="","",IF($H37=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H37)=0,"🟡 ما انزلت بنودها",IF(ROUND($I37-$J37,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I37-$J37,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="38" ht="21" customHeight="1">
       <c r="A38" s="9">
@@ -5396,6 +5953,22 @@
         <f>IF(C38="","",N(D38)*N(E38))</f>
         <v/>
       </c>
+      <c r="H38" s="9">
+        <f>IF('الفواتير'!$E38="يدوية",'الفواتير'!$D38,"")</f>
+        <v/>
+      </c>
+      <c r="I38" s="14">
+        <f>IF($H38="","",'الفواتير'!$F38)</f>
+        <v/>
+      </c>
+      <c r="J38" s="14">
+        <f>IF($H38="","",SUMIF($B$7:$B$606,$H38,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K38" s="15">
+        <f>IF($H38="","",IF($H38=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H38)=0,"🟡 ما انزلت بنودها",IF(ROUND($I38-$J38,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I38-$J38,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="39" ht="21" customHeight="1">
       <c r="A39" s="9">
@@ -5410,6 +5983,22 @@
         <f>IF(C39="","",N(D39)*N(E39))</f>
         <v/>
       </c>
+      <c r="H39" s="9">
+        <f>IF('الفواتير'!$E39="يدوية",'الفواتير'!$D39,"")</f>
+        <v/>
+      </c>
+      <c r="I39" s="14">
+        <f>IF($H39="","",'الفواتير'!$F39)</f>
+        <v/>
+      </c>
+      <c r="J39" s="14">
+        <f>IF($H39="","",SUMIF($B$7:$B$606,$H39,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K39" s="15">
+        <f>IF($H39="","",IF($H39=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H39)=0,"🟡 ما انزلت بنودها",IF(ROUND($I39-$J39,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I39-$J39,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="40" ht="21" customHeight="1">
       <c r="A40" s="9">
@@ -5424,6 +6013,22 @@
         <f>IF(C40="","",N(D40)*N(E40))</f>
         <v/>
       </c>
+      <c r="H40" s="9">
+        <f>IF('الفواتير'!$E40="يدوية",'الفواتير'!$D40,"")</f>
+        <v/>
+      </c>
+      <c r="I40" s="14">
+        <f>IF($H40="","",'الفواتير'!$F40)</f>
+        <v/>
+      </c>
+      <c r="J40" s="14">
+        <f>IF($H40="","",SUMIF($B$7:$B$606,$H40,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K40" s="15">
+        <f>IF($H40="","",IF($H40=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H40)=0,"🟡 ما انزلت بنودها",IF(ROUND($I40-$J40,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I40-$J40,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="41" ht="21" customHeight="1">
       <c r="A41" s="9">
@@ -5438,6 +6043,22 @@
         <f>IF(C41="","",N(D41)*N(E41))</f>
         <v/>
       </c>
+      <c r="H41" s="9">
+        <f>IF('الفواتير'!$E41="يدوية",'الفواتير'!$D41,"")</f>
+        <v/>
+      </c>
+      <c r="I41" s="14">
+        <f>IF($H41="","",'الفواتير'!$F41)</f>
+        <v/>
+      </c>
+      <c r="J41" s="14">
+        <f>IF($H41="","",SUMIF($B$7:$B$606,$H41,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K41" s="15">
+        <f>IF($H41="","",IF($H41=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H41)=0,"🟡 ما انزلت بنودها",IF(ROUND($I41-$J41,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I41-$J41,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="42" ht="21" customHeight="1">
       <c r="A42" s="9">
@@ -5452,6 +6073,22 @@
         <f>IF(C42="","",N(D42)*N(E42))</f>
         <v/>
       </c>
+      <c r="H42" s="9">
+        <f>IF('الفواتير'!$E42="يدوية",'الفواتير'!$D42,"")</f>
+        <v/>
+      </c>
+      <c r="I42" s="14">
+        <f>IF($H42="","",'الفواتير'!$F42)</f>
+        <v/>
+      </c>
+      <c r="J42" s="14">
+        <f>IF($H42="","",SUMIF($B$7:$B$606,$H42,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K42" s="15">
+        <f>IF($H42="","",IF($H42=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H42)=0,"🟡 ما انزلت بنودها",IF(ROUND($I42-$J42,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I42-$J42,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="43" ht="21" customHeight="1">
       <c r="A43" s="9">
@@ -5466,6 +6103,22 @@
         <f>IF(C43="","",N(D43)*N(E43))</f>
         <v/>
       </c>
+      <c r="H43" s="9">
+        <f>IF('الفواتير'!$E43="يدوية",'الفواتير'!$D43,"")</f>
+        <v/>
+      </c>
+      <c r="I43" s="14">
+        <f>IF($H43="","",'الفواتير'!$F43)</f>
+        <v/>
+      </c>
+      <c r="J43" s="14">
+        <f>IF($H43="","",SUMIF($B$7:$B$606,$H43,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K43" s="15">
+        <f>IF($H43="","",IF($H43=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H43)=0,"🟡 ما انزلت بنودها",IF(ROUND($I43-$J43,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I43-$J43,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="44" ht="21" customHeight="1">
       <c r="A44" s="9">
@@ -5480,6 +6133,22 @@
         <f>IF(C44="","",N(D44)*N(E44))</f>
         <v/>
       </c>
+      <c r="H44" s="9">
+        <f>IF('الفواتير'!$E44="يدوية",'الفواتير'!$D44,"")</f>
+        <v/>
+      </c>
+      <c r="I44" s="14">
+        <f>IF($H44="","",'الفواتير'!$F44)</f>
+        <v/>
+      </c>
+      <c r="J44" s="14">
+        <f>IF($H44="","",SUMIF($B$7:$B$606,$H44,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K44" s="15">
+        <f>IF($H44="","",IF($H44=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H44)=0,"🟡 ما انزلت بنودها",IF(ROUND($I44-$J44,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I44-$J44,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="45" ht="21" customHeight="1">
       <c r="A45" s="9">
@@ -5494,6 +6163,22 @@
         <f>IF(C45="","",N(D45)*N(E45))</f>
         <v/>
       </c>
+      <c r="H45" s="9">
+        <f>IF('الفواتير'!$E45="يدوية",'الفواتير'!$D45,"")</f>
+        <v/>
+      </c>
+      <c r="I45" s="14">
+        <f>IF($H45="","",'الفواتير'!$F45)</f>
+        <v/>
+      </c>
+      <c r="J45" s="14">
+        <f>IF($H45="","",SUMIF($B$7:$B$606,$H45,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K45" s="15">
+        <f>IF($H45="","",IF($H45=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H45)=0,"🟡 ما انزلت بنودها",IF(ROUND($I45-$J45,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I45-$J45,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="46" ht="21" customHeight="1">
       <c r="A46" s="9">
@@ -5508,6 +6193,22 @@
         <f>IF(C46="","",N(D46)*N(E46))</f>
         <v/>
       </c>
+      <c r="H46" s="9">
+        <f>IF('الفواتير'!$E46="يدوية",'الفواتير'!$D46,"")</f>
+        <v/>
+      </c>
+      <c r="I46" s="14">
+        <f>IF($H46="","",'الفواتير'!$F46)</f>
+        <v/>
+      </c>
+      <c r="J46" s="14">
+        <f>IF($H46="","",SUMIF($B$7:$B$606,$H46,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K46" s="15">
+        <f>IF($H46="","",IF($H46=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H46)=0,"🟡 ما انزلت بنودها",IF(ROUND($I46-$J46,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I46-$J46,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="47" ht="21" customHeight="1">
       <c r="A47" s="9">
@@ -5522,6 +6223,22 @@
         <f>IF(C47="","",N(D47)*N(E47))</f>
         <v/>
       </c>
+      <c r="H47" s="9">
+        <f>IF('الفواتير'!$E47="يدوية",'الفواتير'!$D47,"")</f>
+        <v/>
+      </c>
+      <c r="I47" s="14">
+        <f>IF($H47="","",'الفواتير'!$F47)</f>
+        <v/>
+      </c>
+      <c r="J47" s="14">
+        <f>IF($H47="","",SUMIF($B$7:$B$606,$H47,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K47" s="15">
+        <f>IF($H47="","",IF($H47=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H47)=0,"🟡 ما انزلت بنودها",IF(ROUND($I47-$J47,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I47-$J47,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="48" ht="21" customHeight="1">
       <c r="A48" s="9">
@@ -5536,6 +6253,22 @@
         <f>IF(C48="","",N(D48)*N(E48))</f>
         <v/>
       </c>
+      <c r="H48" s="9">
+        <f>IF('الفواتير'!$E48="يدوية",'الفواتير'!$D48,"")</f>
+        <v/>
+      </c>
+      <c r="I48" s="14">
+        <f>IF($H48="","",'الفواتير'!$F48)</f>
+        <v/>
+      </c>
+      <c r="J48" s="14">
+        <f>IF($H48="","",SUMIF($B$7:$B$606,$H48,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K48" s="15">
+        <f>IF($H48="","",IF($H48=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H48)=0,"🟡 ما انزلت بنودها",IF(ROUND($I48-$J48,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I48-$J48,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="49" ht="21" customHeight="1">
       <c r="A49" s="9">
@@ -5550,6 +6283,22 @@
         <f>IF(C49="","",N(D49)*N(E49))</f>
         <v/>
       </c>
+      <c r="H49" s="9">
+        <f>IF('الفواتير'!$E49="يدوية",'الفواتير'!$D49,"")</f>
+        <v/>
+      </c>
+      <c r="I49" s="14">
+        <f>IF($H49="","",'الفواتير'!$F49)</f>
+        <v/>
+      </c>
+      <c r="J49" s="14">
+        <f>IF($H49="","",SUMIF($B$7:$B$606,$H49,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K49" s="15">
+        <f>IF($H49="","",IF($H49=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H49)=0,"🟡 ما انزلت بنودها",IF(ROUND($I49-$J49,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I49-$J49,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="50" ht="21" customHeight="1">
       <c r="A50" s="9">
@@ -5564,6 +6313,22 @@
         <f>IF(C50="","",N(D50)*N(E50))</f>
         <v/>
       </c>
+      <c r="H50" s="9">
+        <f>IF('الفواتير'!$E50="يدوية",'الفواتير'!$D50,"")</f>
+        <v/>
+      </c>
+      <c r="I50" s="14">
+        <f>IF($H50="","",'الفواتير'!$F50)</f>
+        <v/>
+      </c>
+      <c r="J50" s="14">
+        <f>IF($H50="","",SUMIF($B$7:$B$606,$H50,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K50" s="15">
+        <f>IF($H50="","",IF($H50=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H50)=0,"🟡 ما انزلت بنودها",IF(ROUND($I50-$J50,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I50-$J50,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="51" ht="21" customHeight="1">
       <c r="A51" s="9">
@@ -5578,6 +6343,22 @@
         <f>IF(C51="","",N(D51)*N(E51))</f>
         <v/>
       </c>
+      <c r="H51" s="9">
+        <f>IF('الفواتير'!$E51="يدوية",'الفواتير'!$D51,"")</f>
+        <v/>
+      </c>
+      <c r="I51" s="14">
+        <f>IF($H51="","",'الفواتير'!$F51)</f>
+        <v/>
+      </c>
+      <c r="J51" s="14">
+        <f>IF($H51="","",SUMIF($B$7:$B$606,$H51,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K51" s="15">
+        <f>IF($H51="","",IF($H51=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H51)=0,"🟡 ما انزلت بنودها",IF(ROUND($I51-$J51,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I51-$J51,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="52" ht="21" customHeight="1">
       <c r="A52" s="9">
@@ -5592,6 +6373,22 @@
         <f>IF(C52="","",N(D52)*N(E52))</f>
         <v/>
       </c>
+      <c r="H52" s="9">
+        <f>IF('الفواتير'!$E52="يدوية",'الفواتير'!$D52,"")</f>
+        <v/>
+      </c>
+      <c r="I52" s="14">
+        <f>IF($H52="","",'الفواتير'!$F52)</f>
+        <v/>
+      </c>
+      <c r="J52" s="14">
+        <f>IF($H52="","",SUMIF($B$7:$B$606,$H52,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K52" s="15">
+        <f>IF($H52="","",IF($H52=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H52)=0,"🟡 ما انزلت بنودها",IF(ROUND($I52-$J52,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I52-$J52,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="53" ht="21" customHeight="1">
       <c r="A53" s="9">
@@ -5606,6 +6403,22 @@
         <f>IF(C53="","",N(D53)*N(E53))</f>
         <v/>
       </c>
+      <c r="H53" s="9">
+        <f>IF('الفواتير'!$E53="يدوية",'الفواتير'!$D53,"")</f>
+        <v/>
+      </c>
+      <c r="I53" s="14">
+        <f>IF($H53="","",'الفواتير'!$F53)</f>
+        <v/>
+      </c>
+      <c r="J53" s="14">
+        <f>IF($H53="","",SUMIF($B$7:$B$606,$H53,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K53" s="15">
+        <f>IF($H53="","",IF($H53=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H53)=0,"🟡 ما انزلت بنودها",IF(ROUND($I53-$J53,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I53-$J53,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="54" ht="21" customHeight="1">
       <c r="A54" s="9">
@@ -5620,6 +6433,22 @@
         <f>IF(C54="","",N(D54)*N(E54))</f>
         <v/>
       </c>
+      <c r="H54" s="9">
+        <f>IF('الفواتير'!$E54="يدوية",'الفواتير'!$D54,"")</f>
+        <v/>
+      </c>
+      <c r="I54" s="14">
+        <f>IF($H54="","",'الفواتير'!$F54)</f>
+        <v/>
+      </c>
+      <c r="J54" s="14">
+        <f>IF($H54="","",SUMIF($B$7:$B$606,$H54,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K54" s="15">
+        <f>IF($H54="","",IF($H54=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H54)=0,"🟡 ما انزلت بنودها",IF(ROUND($I54-$J54,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I54-$J54,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="55" ht="21" customHeight="1">
       <c r="A55" s="9">
@@ -5634,6 +6463,22 @@
         <f>IF(C55="","",N(D55)*N(E55))</f>
         <v/>
       </c>
+      <c r="H55" s="9">
+        <f>IF('الفواتير'!$E55="يدوية",'الفواتير'!$D55,"")</f>
+        <v/>
+      </c>
+      <c r="I55" s="14">
+        <f>IF($H55="","",'الفواتير'!$F55)</f>
+        <v/>
+      </c>
+      <c r="J55" s="14">
+        <f>IF($H55="","",SUMIF($B$7:$B$606,$H55,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K55" s="15">
+        <f>IF($H55="","",IF($H55=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H55)=0,"🟡 ما انزلت بنودها",IF(ROUND($I55-$J55,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I55-$J55,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="56" ht="21" customHeight="1">
       <c r="A56" s="9">
@@ -5648,6 +6493,22 @@
         <f>IF(C56="","",N(D56)*N(E56))</f>
         <v/>
       </c>
+      <c r="H56" s="9">
+        <f>IF('الفواتير'!$E56="يدوية",'الفواتير'!$D56,"")</f>
+        <v/>
+      </c>
+      <c r="I56" s="14">
+        <f>IF($H56="","",'الفواتير'!$F56)</f>
+        <v/>
+      </c>
+      <c r="J56" s="14">
+        <f>IF($H56="","",SUMIF($B$7:$B$606,$H56,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K56" s="15">
+        <f>IF($H56="","",IF($H56=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H56)=0,"🟡 ما انزلت بنودها",IF(ROUND($I56-$J56,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I56-$J56,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="57" ht="21" customHeight="1">
       <c r="A57" s="9">
@@ -5662,6 +6523,22 @@
         <f>IF(C57="","",N(D57)*N(E57))</f>
         <v/>
       </c>
+      <c r="H57" s="9">
+        <f>IF('الفواتير'!$E57="يدوية",'الفواتير'!$D57,"")</f>
+        <v/>
+      </c>
+      <c r="I57" s="14">
+        <f>IF($H57="","",'الفواتير'!$F57)</f>
+        <v/>
+      </c>
+      <c r="J57" s="14">
+        <f>IF($H57="","",SUMIF($B$7:$B$606,$H57,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K57" s="15">
+        <f>IF($H57="","",IF($H57=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H57)=0,"🟡 ما انزلت بنودها",IF(ROUND($I57-$J57,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I57-$J57,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="58" ht="21" customHeight="1">
       <c r="A58" s="9">
@@ -5676,6 +6553,22 @@
         <f>IF(C58="","",N(D58)*N(E58))</f>
         <v/>
       </c>
+      <c r="H58" s="9">
+        <f>IF('الفواتير'!$E58="يدوية",'الفواتير'!$D58,"")</f>
+        <v/>
+      </c>
+      <c r="I58" s="14">
+        <f>IF($H58="","",'الفواتير'!$F58)</f>
+        <v/>
+      </c>
+      <c r="J58" s="14">
+        <f>IF($H58="","",SUMIF($B$7:$B$606,$H58,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K58" s="15">
+        <f>IF($H58="","",IF($H58=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H58)=0,"🟡 ما انزلت بنودها",IF(ROUND($I58-$J58,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I58-$J58,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="59" ht="21" customHeight="1">
       <c r="A59" s="9">
@@ -5690,6 +6583,22 @@
         <f>IF(C59="","",N(D59)*N(E59))</f>
         <v/>
       </c>
+      <c r="H59" s="9">
+        <f>IF('الفواتير'!$E59="يدوية",'الفواتير'!$D59,"")</f>
+        <v/>
+      </c>
+      <c r="I59" s="14">
+        <f>IF($H59="","",'الفواتير'!$F59)</f>
+        <v/>
+      </c>
+      <c r="J59" s="14">
+        <f>IF($H59="","",SUMIF($B$7:$B$606,$H59,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K59" s="15">
+        <f>IF($H59="","",IF($H59=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H59)=0,"🟡 ما انزلت بنودها",IF(ROUND($I59-$J59,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I59-$J59,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="60" ht="21" customHeight="1">
       <c r="A60" s="9">
@@ -5704,6 +6613,22 @@
         <f>IF(C60="","",N(D60)*N(E60))</f>
         <v/>
       </c>
+      <c r="H60" s="9">
+        <f>IF('الفواتير'!$E60="يدوية",'الفواتير'!$D60,"")</f>
+        <v/>
+      </c>
+      <c r="I60" s="14">
+        <f>IF($H60="","",'الفواتير'!$F60)</f>
+        <v/>
+      </c>
+      <c r="J60" s="14">
+        <f>IF($H60="","",SUMIF($B$7:$B$606,$H60,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K60" s="15">
+        <f>IF($H60="","",IF($H60=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H60)=0,"🟡 ما انزلت بنودها",IF(ROUND($I60-$J60,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I60-$J60,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="61" ht="21" customHeight="1">
       <c r="A61" s="9">
@@ -5718,6 +6643,22 @@
         <f>IF(C61="","",N(D61)*N(E61))</f>
         <v/>
       </c>
+      <c r="H61" s="9">
+        <f>IF('الفواتير'!$E61="يدوية",'الفواتير'!$D61,"")</f>
+        <v/>
+      </c>
+      <c r="I61" s="14">
+        <f>IF($H61="","",'الفواتير'!$F61)</f>
+        <v/>
+      </c>
+      <c r="J61" s="14">
+        <f>IF($H61="","",SUMIF($B$7:$B$606,$H61,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K61" s="15">
+        <f>IF($H61="","",IF($H61=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H61)=0,"🟡 ما انزلت بنودها",IF(ROUND($I61-$J61,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I61-$J61,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="62" ht="21" customHeight="1">
       <c r="A62" s="9">
@@ -5732,6 +6673,22 @@
         <f>IF(C62="","",N(D62)*N(E62))</f>
         <v/>
       </c>
+      <c r="H62" s="9">
+        <f>IF('الفواتير'!$E62="يدوية",'الفواتير'!$D62,"")</f>
+        <v/>
+      </c>
+      <c r="I62" s="14">
+        <f>IF($H62="","",'الفواتير'!$F62)</f>
+        <v/>
+      </c>
+      <c r="J62" s="14">
+        <f>IF($H62="","",SUMIF($B$7:$B$606,$H62,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K62" s="15">
+        <f>IF($H62="","",IF($H62=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H62)=0,"🟡 ما انزلت بنودها",IF(ROUND($I62-$J62,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I62-$J62,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="63" ht="21" customHeight="1">
       <c r="A63" s="9">
@@ -5746,6 +6703,22 @@
         <f>IF(C63="","",N(D63)*N(E63))</f>
         <v/>
       </c>
+      <c r="H63" s="9">
+        <f>IF('الفواتير'!$E63="يدوية",'الفواتير'!$D63,"")</f>
+        <v/>
+      </c>
+      <c r="I63" s="14">
+        <f>IF($H63="","",'الفواتير'!$F63)</f>
+        <v/>
+      </c>
+      <c r="J63" s="14">
+        <f>IF($H63="","",SUMIF($B$7:$B$606,$H63,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K63" s="15">
+        <f>IF($H63="","",IF($H63=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H63)=0,"🟡 ما انزلت بنودها",IF(ROUND($I63-$J63,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I63-$J63,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="64" ht="21" customHeight="1">
       <c r="A64" s="9">
@@ -5760,6 +6733,22 @@
         <f>IF(C64="","",N(D64)*N(E64))</f>
         <v/>
       </c>
+      <c r="H64" s="9">
+        <f>IF('الفواتير'!$E64="يدوية",'الفواتير'!$D64,"")</f>
+        <v/>
+      </c>
+      <c r="I64" s="14">
+        <f>IF($H64="","",'الفواتير'!$F64)</f>
+        <v/>
+      </c>
+      <c r="J64" s="14">
+        <f>IF($H64="","",SUMIF($B$7:$B$606,$H64,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K64" s="15">
+        <f>IF($H64="","",IF($H64=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H64)=0,"🟡 ما انزلت بنودها",IF(ROUND($I64-$J64,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I64-$J64,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="65" ht="21" customHeight="1">
       <c r="A65" s="9">
@@ -5774,6 +6763,22 @@
         <f>IF(C65="","",N(D65)*N(E65))</f>
         <v/>
       </c>
+      <c r="H65" s="9">
+        <f>IF('الفواتير'!$E65="يدوية",'الفواتير'!$D65,"")</f>
+        <v/>
+      </c>
+      <c r="I65" s="14">
+        <f>IF($H65="","",'الفواتير'!$F65)</f>
+        <v/>
+      </c>
+      <c r="J65" s="14">
+        <f>IF($H65="","",SUMIF($B$7:$B$606,$H65,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K65" s="15">
+        <f>IF($H65="","",IF($H65=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H65)=0,"🟡 ما انزلت بنودها",IF(ROUND($I65-$J65,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I65-$J65,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="66" ht="21" customHeight="1">
       <c r="A66" s="9">
@@ -5788,6 +6793,22 @@
         <f>IF(C66="","",N(D66)*N(E66))</f>
         <v/>
       </c>
+      <c r="H66" s="9">
+        <f>IF('الفواتير'!$E66="يدوية",'الفواتير'!$D66,"")</f>
+        <v/>
+      </c>
+      <c r="I66" s="14">
+        <f>IF($H66="","",'الفواتير'!$F66)</f>
+        <v/>
+      </c>
+      <c r="J66" s="14">
+        <f>IF($H66="","",SUMIF($B$7:$B$606,$H66,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K66" s="15">
+        <f>IF($H66="","",IF($H66=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H66)=0,"🟡 ما انزلت بنودها",IF(ROUND($I66-$J66,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I66-$J66,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="67" ht="21" customHeight="1">
       <c r="A67" s="9">
@@ -5802,6 +6823,22 @@
         <f>IF(C67="","",N(D67)*N(E67))</f>
         <v/>
       </c>
+      <c r="H67" s="9">
+        <f>IF('الفواتير'!$E67="يدوية",'الفواتير'!$D67,"")</f>
+        <v/>
+      </c>
+      <c r="I67" s="14">
+        <f>IF($H67="","",'الفواتير'!$F67)</f>
+        <v/>
+      </c>
+      <c r="J67" s="14">
+        <f>IF($H67="","",SUMIF($B$7:$B$606,$H67,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K67" s="15">
+        <f>IF($H67="","",IF($H67=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H67)=0,"🟡 ما انزلت بنودها",IF(ROUND($I67-$J67,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I67-$J67,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="68" ht="21" customHeight="1">
       <c r="A68" s="9">
@@ -5816,6 +6853,22 @@
         <f>IF(C68="","",N(D68)*N(E68))</f>
         <v/>
       </c>
+      <c r="H68" s="9">
+        <f>IF('الفواتير'!$E68="يدوية",'الفواتير'!$D68,"")</f>
+        <v/>
+      </c>
+      <c r="I68" s="14">
+        <f>IF($H68="","",'الفواتير'!$F68)</f>
+        <v/>
+      </c>
+      <c r="J68" s="14">
+        <f>IF($H68="","",SUMIF($B$7:$B$606,$H68,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K68" s="15">
+        <f>IF($H68="","",IF($H68=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H68)=0,"🟡 ما انزلت بنودها",IF(ROUND($I68-$J68,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I68-$J68,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="69" ht="21" customHeight="1">
       <c r="A69" s="9">
@@ -5830,6 +6883,22 @@
         <f>IF(C69="","",N(D69)*N(E69))</f>
         <v/>
       </c>
+      <c r="H69" s="9">
+        <f>IF('الفواتير'!$E69="يدوية",'الفواتير'!$D69,"")</f>
+        <v/>
+      </c>
+      <c r="I69" s="14">
+        <f>IF($H69="","",'الفواتير'!$F69)</f>
+        <v/>
+      </c>
+      <c r="J69" s="14">
+        <f>IF($H69="","",SUMIF($B$7:$B$606,$H69,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K69" s="15">
+        <f>IF($H69="","",IF($H69=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H69)=0,"🟡 ما انزلت بنودها",IF(ROUND($I69-$J69,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I69-$J69,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="70" ht="21" customHeight="1">
       <c r="A70" s="9">
@@ -5844,6 +6913,22 @@
         <f>IF(C70="","",N(D70)*N(E70))</f>
         <v/>
       </c>
+      <c r="H70" s="9">
+        <f>IF('الفواتير'!$E70="يدوية",'الفواتير'!$D70,"")</f>
+        <v/>
+      </c>
+      <c r="I70" s="14">
+        <f>IF($H70="","",'الفواتير'!$F70)</f>
+        <v/>
+      </c>
+      <c r="J70" s="14">
+        <f>IF($H70="","",SUMIF($B$7:$B$606,$H70,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K70" s="15">
+        <f>IF($H70="","",IF($H70=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H70)=0,"🟡 ما انزلت بنودها",IF(ROUND($I70-$J70,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I70-$J70,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="71" ht="21" customHeight="1">
       <c r="A71" s="9">
@@ -5858,6 +6943,22 @@
         <f>IF(C71="","",N(D71)*N(E71))</f>
         <v/>
       </c>
+      <c r="H71" s="9">
+        <f>IF('الفواتير'!$E71="يدوية",'الفواتير'!$D71,"")</f>
+        <v/>
+      </c>
+      <c r="I71" s="14">
+        <f>IF($H71="","",'الفواتير'!$F71)</f>
+        <v/>
+      </c>
+      <c r="J71" s="14">
+        <f>IF($H71="","",SUMIF($B$7:$B$606,$H71,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K71" s="15">
+        <f>IF($H71="","",IF($H71=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H71)=0,"🟡 ما انزلت بنودها",IF(ROUND($I71-$J71,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I71-$J71,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="72" ht="21" customHeight="1">
       <c r="A72" s="9">
@@ -5872,6 +6973,22 @@
         <f>IF(C72="","",N(D72)*N(E72))</f>
         <v/>
       </c>
+      <c r="H72" s="9">
+        <f>IF('الفواتير'!$E72="يدوية",'الفواتير'!$D72,"")</f>
+        <v/>
+      </c>
+      <c r="I72" s="14">
+        <f>IF($H72="","",'الفواتير'!$F72)</f>
+        <v/>
+      </c>
+      <c r="J72" s="14">
+        <f>IF($H72="","",SUMIF($B$7:$B$606,$H72,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K72" s="15">
+        <f>IF($H72="","",IF($H72=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H72)=0,"🟡 ما انزلت بنودها",IF(ROUND($I72-$J72,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I72-$J72,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="73" ht="21" customHeight="1">
       <c r="A73" s="9">
@@ -5886,6 +7003,22 @@
         <f>IF(C73="","",N(D73)*N(E73))</f>
         <v/>
       </c>
+      <c r="H73" s="9">
+        <f>IF('الفواتير'!$E73="يدوية",'الفواتير'!$D73,"")</f>
+        <v/>
+      </c>
+      <c r="I73" s="14">
+        <f>IF($H73="","",'الفواتير'!$F73)</f>
+        <v/>
+      </c>
+      <c r="J73" s="14">
+        <f>IF($H73="","",SUMIF($B$7:$B$606,$H73,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K73" s="15">
+        <f>IF($H73="","",IF($H73=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H73)=0,"🟡 ما انزلت بنودها",IF(ROUND($I73-$J73,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I73-$J73,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="74" ht="21" customHeight="1">
       <c r="A74" s="9">
@@ -5900,6 +7033,22 @@
         <f>IF(C74="","",N(D74)*N(E74))</f>
         <v/>
       </c>
+      <c r="H74" s="9">
+        <f>IF('الفواتير'!$E74="يدوية",'الفواتير'!$D74,"")</f>
+        <v/>
+      </c>
+      <c r="I74" s="14">
+        <f>IF($H74="","",'الفواتير'!$F74)</f>
+        <v/>
+      </c>
+      <c r="J74" s="14">
+        <f>IF($H74="","",SUMIF($B$7:$B$606,$H74,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K74" s="15">
+        <f>IF($H74="","",IF($H74=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H74)=0,"🟡 ما انزلت بنودها",IF(ROUND($I74-$J74,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I74-$J74,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="75" ht="21" customHeight="1">
       <c r="A75" s="9">
@@ -5914,6 +7063,22 @@
         <f>IF(C75="","",N(D75)*N(E75))</f>
         <v/>
       </c>
+      <c r="H75" s="9">
+        <f>IF('الفواتير'!$E75="يدوية",'الفواتير'!$D75,"")</f>
+        <v/>
+      </c>
+      <c r="I75" s="14">
+        <f>IF($H75="","",'الفواتير'!$F75)</f>
+        <v/>
+      </c>
+      <c r="J75" s="14">
+        <f>IF($H75="","",SUMIF($B$7:$B$606,$H75,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K75" s="15">
+        <f>IF($H75="","",IF($H75=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H75)=0,"🟡 ما انزلت بنودها",IF(ROUND($I75-$J75,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I75-$J75,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="76" ht="21" customHeight="1">
       <c r="A76" s="9">
@@ -5928,6 +7093,22 @@
         <f>IF(C76="","",N(D76)*N(E76))</f>
         <v/>
       </c>
+      <c r="H76" s="9">
+        <f>IF('الفواتير'!$E76="يدوية",'الفواتير'!$D76,"")</f>
+        <v/>
+      </c>
+      <c r="I76" s="14">
+        <f>IF($H76="","",'الفواتير'!$F76)</f>
+        <v/>
+      </c>
+      <c r="J76" s="14">
+        <f>IF($H76="","",SUMIF($B$7:$B$606,$H76,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K76" s="15">
+        <f>IF($H76="","",IF($H76=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H76)=0,"🟡 ما انزلت بنودها",IF(ROUND($I76-$J76,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I76-$J76,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="77" ht="21" customHeight="1">
       <c r="A77" s="9">
@@ -5942,6 +7123,22 @@
         <f>IF(C77="","",N(D77)*N(E77))</f>
         <v/>
       </c>
+      <c r="H77" s="9">
+        <f>IF('الفواتير'!$E77="يدوية",'الفواتير'!$D77,"")</f>
+        <v/>
+      </c>
+      <c r="I77" s="14">
+        <f>IF($H77="","",'الفواتير'!$F77)</f>
+        <v/>
+      </c>
+      <c r="J77" s="14">
+        <f>IF($H77="","",SUMIF($B$7:$B$606,$H77,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K77" s="15">
+        <f>IF($H77="","",IF($H77=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H77)=0,"🟡 ما انزلت بنودها",IF(ROUND($I77-$J77,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I77-$J77,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="78" ht="21" customHeight="1">
       <c r="A78" s="9">
@@ -5956,6 +7153,22 @@
         <f>IF(C78="","",N(D78)*N(E78))</f>
         <v/>
       </c>
+      <c r="H78" s="9">
+        <f>IF('الفواتير'!$E78="يدوية",'الفواتير'!$D78,"")</f>
+        <v/>
+      </c>
+      <c r="I78" s="14">
+        <f>IF($H78="","",'الفواتير'!$F78)</f>
+        <v/>
+      </c>
+      <c r="J78" s="14">
+        <f>IF($H78="","",SUMIF($B$7:$B$606,$H78,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K78" s="15">
+        <f>IF($H78="","",IF($H78=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H78)=0,"🟡 ما انزلت بنودها",IF(ROUND($I78-$J78,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I78-$J78,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="79" ht="21" customHeight="1">
       <c r="A79" s="9">
@@ -5970,6 +7183,22 @@
         <f>IF(C79="","",N(D79)*N(E79))</f>
         <v/>
       </c>
+      <c r="H79" s="9">
+        <f>IF('الفواتير'!$E79="يدوية",'الفواتير'!$D79,"")</f>
+        <v/>
+      </c>
+      <c r="I79" s="14">
+        <f>IF($H79="","",'الفواتير'!$F79)</f>
+        <v/>
+      </c>
+      <c r="J79" s="14">
+        <f>IF($H79="","",SUMIF($B$7:$B$606,$H79,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K79" s="15">
+        <f>IF($H79="","",IF($H79=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H79)=0,"🟡 ما انزلت بنودها",IF(ROUND($I79-$J79,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I79-$J79,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="80" ht="21" customHeight="1">
       <c r="A80" s="9">
@@ -5984,6 +7213,22 @@
         <f>IF(C80="","",N(D80)*N(E80))</f>
         <v/>
       </c>
+      <c r="H80" s="9">
+        <f>IF('الفواتير'!$E80="يدوية",'الفواتير'!$D80,"")</f>
+        <v/>
+      </c>
+      <c r="I80" s="14">
+        <f>IF($H80="","",'الفواتير'!$F80)</f>
+        <v/>
+      </c>
+      <c r="J80" s="14">
+        <f>IF($H80="","",SUMIF($B$7:$B$606,$H80,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K80" s="15">
+        <f>IF($H80="","",IF($H80=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H80)=0,"🟡 ما انزلت بنودها",IF(ROUND($I80-$J80,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I80-$J80,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="81" ht="21" customHeight="1">
       <c r="A81" s="9">
@@ -5998,6 +7243,22 @@
         <f>IF(C81="","",N(D81)*N(E81))</f>
         <v/>
       </c>
+      <c r="H81" s="9">
+        <f>IF('الفواتير'!$E81="يدوية",'الفواتير'!$D81,"")</f>
+        <v/>
+      </c>
+      <c r="I81" s="14">
+        <f>IF($H81="","",'الفواتير'!$F81)</f>
+        <v/>
+      </c>
+      <c r="J81" s="14">
+        <f>IF($H81="","",SUMIF($B$7:$B$606,$H81,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K81" s="15">
+        <f>IF($H81="","",IF($H81=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H81)=0,"🟡 ما انزلت بنودها",IF(ROUND($I81-$J81,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I81-$J81,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="82" ht="21" customHeight="1">
       <c r="A82" s="9">
@@ -6012,6 +7273,22 @@
         <f>IF(C82="","",N(D82)*N(E82))</f>
         <v/>
       </c>
+      <c r="H82" s="9">
+        <f>IF('الفواتير'!$E82="يدوية",'الفواتير'!$D82,"")</f>
+        <v/>
+      </c>
+      <c r="I82" s="14">
+        <f>IF($H82="","",'الفواتير'!$F82)</f>
+        <v/>
+      </c>
+      <c r="J82" s="14">
+        <f>IF($H82="","",SUMIF($B$7:$B$606,$H82,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K82" s="15">
+        <f>IF($H82="","",IF($H82=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H82)=0,"🟡 ما انزلت بنودها",IF(ROUND($I82-$J82,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I82-$J82,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="83" ht="21" customHeight="1">
       <c r="A83" s="9">
@@ -6026,6 +7303,22 @@
         <f>IF(C83="","",N(D83)*N(E83))</f>
         <v/>
       </c>
+      <c r="H83" s="9">
+        <f>IF('الفواتير'!$E83="يدوية",'الفواتير'!$D83,"")</f>
+        <v/>
+      </c>
+      <c r="I83" s="14">
+        <f>IF($H83="","",'الفواتير'!$F83)</f>
+        <v/>
+      </c>
+      <c r="J83" s="14">
+        <f>IF($H83="","",SUMIF($B$7:$B$606,$H83,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K83" s="15">
+        <f>IF($H83="","",IF($H83=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H83)=0,"🟡 ما انزلت بنودها",IF(ROUND($I83-$J83,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I83-$J83,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="84" ht="21" customHeight="1">
       <c r="A84" s="9">
@@ -6040,6 +7333,22 @@
         <f>IF(C84="","",N(D84)*N(E84))</f>
         <v/>
       </c>
+      <c r="H84" s="9">
+        <f>IF('الفواتير'!$E84="يدوية",'الفواتير'!$D84,"")</f>
+        <v/>
+      </c>
+      <c r="I84" s="14">
+        <f>IF($H84="","",'الفواتير'!$F84)</f>
+        <v/>
+      </c>
+      <c r="J84" s="14">
+        <f>IF($H84="","",SUMIF($B$7:$B$606,$H84,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K84" s="15">
+        <f>IF($H84="","",IF($H84=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H84)=0,"🟡 ما انزلت بنودها",IF(ROUND($I84-$J84,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I84-$J84,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="85" ht="21" customHeight="1">
       <c r="A85" s="9">
@@ -6054,6 +7363,22 @@
         <f>IF(C85="","",N(D85)*N(E85))</f>
         <v/>
       </c>
+      <c r="H85" s="9">
+        <f>IF('الفواتير'!$E85="يدوية",'الفواتير'!$D85,"")</f>
+        <v/>
+      </c>
+      <c r="I85" s="14">
+        <f>IF($H85="","",'الفواتير'!$F85)</f>
+        <v/>
+      </c>
+      <c r="J85" s="14">
+        <f>IF($H85="","",SUMIF($B$7:$B$606,$H85,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K85" s="15">
+        <f>IF($H85="","",IF($H85=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H85)=0,"🟡 ما انزلت بنودها",IF(ROUND($I85-$J85,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I85-$J85,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="86" ht="21" customHeight="1">
       <c r="A86" s="9">
@@ -6068,6 +7393,22 @@
         <f>IF(C86="","",N(D86)*N(E86))</f>
         <v/>
       </c>
+      <c r="H86" s="9">
+        <f>IF('الفواتير'!$E86="يدوية",'الفواتير'!$D86,"")</f>
+        <v/>
+      </c>
+      <c r="I86" s="14">
+        <f>IF($H86="","",'الفواتير'!$F86)</f>
+        <v/>
+      </c>
+      <c r="J86" s="14">
+        <f>IF($H86="","",SUMIF($B$7:$B$606,$H86,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K86" s="15">
+        <f>IF($H86="","",IF($H86=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H86)=0,"🟡 ما انزلت بنودها",IF(ROUND($I86-$J86,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I86-$J86,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="87" ht="21" customHeight="1">
       <c r="A87" s="9">
@@ -6082,6 +7423,22 @@
         <f>IF(C87="","",N(D87)*N(E87))</f>
         <v/>
       </c>
+      <c r="H87" s="9">
+        <f>IF('الفواتير'!$E87="يدوية",'الفواتير'!$D87,"")</f>
+        <v/>
+      </c>
+      <c r="I87" s="14">
+        <f>IF($H87="","",'الفواتير'!$F87)</f>
+        <v/>
+      </c>
+      <c r="J87" s="14">
+        <f>IF($H87="","",SUMIF($B$7:$B$606,$H87,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K87" s="15">
+        <f>IF($H87="","",IF($H87=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H87)=0,"🟡 ما انزلت بنودها",IF(ROUND($I87-$J87,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I87-$J87,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="88" ht="21" customHeight="1">
       <c r="A88" s="9">
@@ -6096,6 +7453,22 @@
         <f>IF(C88="","",N(D88)*N(E88))</f>
         <v/>
       </c>
+      <c r="H88" s="9">
+        <f>IF('الفواتير'!$E88="يدوية",'الفواتير'!$D88,"")</f>
+        <v/>
+      </c>
+      <c r="I88" s="14">
+        <f>IF($H88="","",'الفواتير'!$F88)</f>
+        <v/>
+      </c>
+      <c r="J88" s="14">
+        <f>IF($H88="","",SUMIF($B$7:$B$606,$H88,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K88" s="15">
+        <f>IF($H88="","",IF($H88=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H88)=0,"🟡 ما انزلت بنودها",IF(ROUND($I88-$J88,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I88-$J88,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="89" ht="21" customHeight="1">
       <c r="A89" s="9">
@@ -6110,6 +7483,22 @@
         <f>IF(C89="","",N(D89)*N(E89))</f>
         <v/>
       </c>
+      <c r="H89" s="9">
+        <f>IF('الفواتير'!$E89="يدوية",'الفواتير'!$D89,"")</f>
+        <v/>
+      </c>
+      <c r="I89" s="14">
+        <f>IF($H89="","",'الفواتير'!$F89)</f>
+        <v/>
+      </c>
+      <c r="J89" s="14">
+        <f>IF($H89="","",SUMIF($B$7:$B$606,$H89,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K89" s="15">
+        <f>IF($H89="","",IF($H89=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H89)=0,"🟡 ما انزلت بنودها",IF(ROUND($I89-$J89,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I89-$J89,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="90" ht="21" customHeight="1">
       <c r="A90" s="9">
@@ -6124,6 +7513,22 @@
         <f>IF(C90="","",N(D90)*N(E90))</f>
         <v/>
       </c>
+      <c r="H90" s="9">
+        <f>IF('الفواتير'!$E90="يدوية",'الفواتير'!$D90,"")</f>
+        <v/>
+      </c>
+      <c r="I90" s="14">
+        <f>IF($H90="","",'الفواتير'!$F90)</f>
+        <v/>
+      </c>
+      <c r="J90" s="14">
+        <f>IF($H90="","",SUMIF($B$7:$B$606,$H90,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K90" s="15">
+        <f>IF($H90="","",IF($H90=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H90)=0,"🟡 ما انزلت بنودها",IF(ROUND($I90-$J90,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I90-$J90,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="91" ht="21" customHeight="1">
       <c r="A91" s="9">
@@ -6138,6 +7543,22 @@
         <f>IF(C91="","",N(D91)*N(E91))</f>
         <v/>
       </c>
+      <c r="H91" s="9">
+        <f>IF('الفواتير'!$E91="يدوية",'الفواتير'!$D91,"")</f>
+        <v/>
+      </c>
+      <c r="I91" s="14">
+        <f>IF($H91="","",'الفواتير'!$F91)</f>
+        <v/>
+      </c>
+      <c r="J91" s="14">
+        <f>IF($H91="","",SUMIF($B$7:$B$606,$H91,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K91" s="15">
+        <f>IF($H91="","",IF($H91=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H91)=0,"🟡 ما انزلت بنودها",IF(ROUND($I91-$J91,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I91-$J91,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="92" ht="21" customHeight="1">
       <c r="A92" s="9">
@@ -6152,6 +7573,22 @@
         <f>IF(C92="","",N(D92)*N(E92))</f>
         <v/>
       </c>
+      <c r="H92" s="9">
+        <f>IF('الفواتير'!$E92="يدوية",'الفواتير'!$D92,"")</f>
+        <v/>
+      </c>
+      <c r="I92" s="14">
+        <f>IF($H92="","",'الفواتير'!$F92)</f>
+        <v/>
+      </c>
+      <c r="J92" s="14">
+        <f>IF($H92="","",SUMIF($B$7:$B$606,$H92,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K92" s="15">
+        <f>IF($H92="","",IF($H92=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H92)=0,"🟡 ما انزلت بنودها",IF(ROUND($I92-$J92,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I92-$J92,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="93" ht="21" customHeight="1">
       <c r="A93" s="9">
@@ -6166,6 +7603,22 @@
         <f>IF(C93="","",N(D93)*N(E93))</f>
         <v/>
       </c>
+      <c r="H93" s="9">
+        <f>IF('الفواتير'!$E93="يدوية",'الفواتير'!$D93,"")</f>
+        <v/>
+      </c>
+      <c r="I93" s="14">
+        <f>IF($H93="","",'الفواتير'!$F93)</f>
+        <v/>
+      </c>
+      <c r="J93" s="14">
+        <f>IF($H93="","",SUMIF($B$7:$B$606,$H93,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K93" s="15">
+        <f>IF($H93="","",IF($H93=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H93)=0,"🟡 ما انزلت بنودها",IF(ROUND($I93-$J93,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I93-$J93,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="94" ht="21" customHeight="1">
       <c r="A94" s="9">
@@ -6180,6 +7633,22 @@
         <f>IF(C94="","",N(D94)*N(E94))</f>
         <v/>
       </c>
+      <c r="H94" s="9">
+        <f>IF('الفواتير'!$E94="يدوية",'الفواتير'!$D94,"")</f>
+        <v/>
+      </c>
+      <c r="I94" s="14">
+        <f>IF($H94="","",'الفواتير'!$F94)</f>
+        <v/>
+      </c>
+      <c r="J94" s="14">
+        <f>IF($H94="","",SUMIF($B$7:$B$606,$H94,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K94" s="15">
+        <f>IF($H94="","",IF($H94=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H94)=0,"🟡 ما انزلت بنودها",IF(ROUND($I94-$J94,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I94-$J94,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="95" ht="21" customHeight="1">
       <c r="A95" s="9">
@@ -6194,6 +7663,22 @@
         <f>IF(C95="","",N(D95)*N(E95))</f>
         <v/>
       </c>
+      <c r="H95" s="9">
+        <f>IF('الفواتير'!$E95="يدوية",'الفواتير'!$D95,"")</f>
+        <v/>
+      </c>
+      <c r="I95" s="14">
+        <f>IF($H95="","",'الفواتير'!$F95)</f>
+        <v/>
+      </c>
+      <c r="J95" s="14">
+        <f>IF($H95="","",SUMIF($B$7:$B$606,$H95,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K95" s="15">
+        <f>IF($H95="","",IF($H95=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H95)=0,"🟡 ما انزلت بنودها",IF(ROUND($I95-$J95,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I95-$J95,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="96" ht="21" customHeight="1">
       <c r="A96" s="9">
@@ -6208,6 +7693,22 @@
         <f>IF(C96="","",N(D96)*N(E96))</f>
         <v/>
       </c>
+      <c r="H96" s="9">
+        <f>IF('الفواتير'!$E96="يدوية",'الفواتير'!$D96,"")</f>
+        <v/>
+      </c>
+      <c r="I96" s="14">
+        <f>IF($H96="","",'الفواتير'!$F96)</f>
+        <v/>
+      </c>
+      <c r="J96" s="14">
+        <f>IF($H96="","",SUMIF($B$7:$B$606,$H96,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K96" s="15">
+        <f>IF($H96="","",IF($H96=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H96)=0,"🟡 ما انزلت بنودها",IF(ROUND($I96-$J96,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I96-$J96,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="97" ht="21" customHeight="1">
       <c r="A97" s="9">
@@ -6222,6 +7723,22 @@
         <f>IF(C97="","",N(D97)*N(E97))</f>
         <v/>
       </c>
+      <c r="H97" s="9">
+        <f>IF('الفواتير'!$E97="يدوية",'الفواتير'!$D97,"")</f>
+        <v/>
+      </c>
+      <c r="I97" s="14">
+        <f>IF($H97="","",'الفواتير'!$F97)</f>
+        <v/>
+      </c>
+      <c r="J97" s="14">
+        <f>IF($H97="","",SUMIF($B$7:$B$606,$H97,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K97" s="15">
+        <f>IF($H97="","",IF($H97=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H97)=0,"🟡 ما انزلت بنودها",IF(ROUND($I97-$J97,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I97-$J97,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="98" ht="21" customHeight="1">
       <c r="A98" s="9">
@@ -6236,6 +7753,22 @@
         <f>IF(C98="","",N(D98)*N(E98))</f>
         <v/>
       </c>
+      <c r="H98" s="9">
+        <f>IF('الفواتير'!$E98="يدوية",'الفواتير'!$D98,"")</f>
+        <v/>
+      </c>
+      <c r="I98" s="14">
+        <f>IF($H98="","",'الفواتير'!$F98)</f>
+        <v/>
+      </c>
+      <c r="J98" s="14">
+        <f>IF($H98="","",SUMIF($B$7:$B$606,$H98,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K98" s="15">
+        <f>IF($H98="","",IF($H98=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H98)=0,"🟡 ما انزلت بنودها",IF(ROUND($I98-$J98,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I98-$J98,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="99" ht="21" customHeight="1">
       <c r="A99" s="9">
@@ -6250,6 +7783,22 @@
         <f>IF(C99="","",N(D99)*N(E99))</f>
         <v/>
       </c>
+      <c r="H99" s="9">
+        <f>IF('الفواتير'!$E99="يدوية",'الفواتير'!$D99,"")</f>
+        <v/>
+      </c>
+      <c r="I99" s="14">
+        <f>IF($H99="","",'الفواتير'!$F99)</f>
+        <v/>
+      </c>
+      <c r="J99" s="14">
+        <f>IF($H99="","",SUMIF($B$7:$B$606,$H99,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K99" s="15">
+        <f>IF($H99="","",IF($H99=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H99)=0,"🟡 ما انزلت بنودها",IF(ROUND($I99-$J99,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I99-$J99,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="100" ht="21" customHeight="1">
       <c r="A100" s="9">
@@ -6264,6 +7813,22 @@
         <f>IF(C100="","",N(D100)*N(E100))</f>
         <v/>
       </c>
+      <c r="H100" s="9">
+        <f>IF('الفواتير'!$E100="يدوية",'الفواتير'!$D100,"")</f>
+        <v/>
+      </c>
+      <c r="I100" s="14">
+        <f>IF($H100="","",'الفواتير'!$F100)</f>
+        <v/>
+      </c>
+      <c r="J100" s="14">
+        <f>IF($H100="","",SUMIF($B$7:$B$606,$H100,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K100" s="15">
+        <f>IF($H100="","",IF($H100=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H100)=0,"🟡 ما انزلت بنودها",IF(ROUND($I100-$J100,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I100-$J100,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="101" ht="21" customHeight="1">
       <c r="A101" s="9">
@@ -6278,6 +7843,22 @@
         <f>IF(C101="","",N(D101)*N(E101))</f>
         <v/>
       </c>
+      <c r="H101" s="9">
+        <f>IF('الفواتير'!$E101="يدوية",'الفواتير'!$D101,"")</f>
+        <v/>
+      </c>
+      <c r="I101" s="14">
+        <f>IF($H101="","",'الفواتير'!$F101)</f>
+        <v/>
+      </c>
+      <c r="J101" s="14">
+        <f>IF($H101="","",SUMIF($B$7:$B$606,$H101,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K101" s="15">
+        <f>IF($H101="","",IF($H101=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H101)=0,"🟡 ما انزلت بنودها",IF(ROUND($I101-$J101,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I101-$J101,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="102" ht="21" customHeight="1">
       <c r="A102" s="9">
@@ -6292,6 +7873,22 @@
         <f>IF(C102="","",N(D102)*N(E102))</f>
         <v/>
       </c>
+      <c r="H102" s="9">
+        <f>IF('الفواتير'!$E102="يدوية",'الفواتير'!$D102,"")</f>
+        <v/>
+      </c>
+      <c r="I102" s="14">
+        <f>IF($H102="","",'الفواتير'!$F102)</f>
+        <v/>
+      </c>
+      <c r="J102" s="14">
+        <f>IF($H102="","",SUMIF($B$7:$B$606,$H102,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K102" s="15">
+        <f>IF($H102="","",IF($H102=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H102)=0,"🟡 ما انزلت بنودها",IF(ROUND($I102-$J102,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I102-$J102,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="103" ht="21" customHeight="1">
       <c r="A103" s="9">
@@ -6306,6 +7903,22 @@
         <f>IF(C103="","",N(D103)*N(E103))</f>
         <v/>
       </c>
+      <c r="H103" s="9">
+        <f>IF('الفواتير'!$E103="يدوية",'الفواتير'!$D103,"")</f>
+        <v/>
+      </c>
+      <c r="I103" s="14">
+        <f>IF($H103="","",'الفواتير'!$F103)</f>
+        <v/>
+      </c>
+      <c r="J103" s="14">
+        <f>IF($H103="","",SUMIF($B$7:$B$606,$H103,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K103" s="15">
+        <f>IF($H103="","",IF($H103=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H103)=0,"🟡 ما انزلت بنودها",IF(ROUND($I103-$J103,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I103-$J103,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="104" ht="21" customHeight="1">
       <c r="A104" s="9">
@@ -6320,6 +7933,22 @@
         <f>IF(C104="","",N(D104)*N(E104))</f>
         <v/>
       </c>
+      <c r="H104" s="9">
+        <f>IF('الفواتير'!$E104="يدوية",'الفواتير'!$D104,"")</f>
+        <v/>
+      </c>
+      <c r="I104" s="14">
+        <f>IF($H104="","",'الفواتير'!$F104)</f>
+        <v/>
+      </c>
+      <c r="J104" s="14">
+        <f>IF($H104="","",SUMIF($B$7:$B$606,$H104,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K104" s="15">
+        <f>IF($H104="","",IF($H104=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H104)=0,"🟡 ما انزلت بنودها",IF(ROUND($I104-$J104,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I104-$J104,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="105" ht="21" customHeight="1">
       <c r="A105" s="9">
@@ -6334,6 +7963,22 @@
         <f>IF(C105="","",N(D105)*N(E105))</f>
         <v/>
       </c>
+      <c r="H105" s="9">
+        <f>IF('الفواتير'!$E105="يدوية",'الفواتير'!$D105,"")</f>
+        <v/>
+      </c>
+      <c r="I105" s="14">
+        <f>IF($H105="","",'الفواتير'!$F105)</f>
+        <v/>
+      </c>
+      <c r="J105" s="14">
+        <f>IF($H105="","",SUMIF($B$7:$B$606,$H105,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K105" s="15">
+        <f>IF($H105="","",IF($H105=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H105)=0,"🟡 ما انزلت بنودها",IF(ROUND($I105-$J105,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I105-$J105,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="106" ht="21" customHeight="1">
       <c r="A106" s="9">
@@ -6348,6 +7993,22 @@
         <f>IF(C106="","",N(D106)*N(E106))</f>
         <v/>
       </c>
+      <c r="H106" s="9">
+        <f>IF('الفواتير'!$E106="يدوية",'الفواتير'!$D106,"")</f>
+        <v/>
+      </c>
+      <c r="I106" s="14">
+        <f>IF($H106="","",'الفواتير'!$F106)</f>
+        <v/>
+      </c>
+      <c r="J106" s="14">
+        <f>IF($H106="","",SUMIF($B$7:$B$606,$H106,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K106" s="15">
+        <f>IF($H106="","",IF($H106=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H106)=0,"🟡 ما انزلت بنودها",IF(ROUND($I106-$J106,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I106-$J106,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="107" ht="21" customHeight="1">
       <c r="A107" s="9">
@@ -6362,6 +8023,22 @@
         <f>IF(C107="","",N(D107)*N(E107))</f>
         <v/>
       </c>
+      <c r="H107" s="9">
+        <f>IF('الفواتير'!$E107="يدوية",'الفواتير'!$D107,"")</f>
+        <v/>
+      </c>
+      <c r="I107" s="14">
+        <f>IF($H107="","",'الفواتير'!$F107)</f>
+        <v/>
+      </c>
+      <c r="J107" s="14">
+        <f>IF($H107="","",SUMIF($B$7:$B$606,$H107,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K107" s="15">
+        <f>IF($H107="","",IF($H107=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H107)=0,"🟡 ما انزلت بنودها",IF(ROUND($I107-$J107,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I107-$J107,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="108" ht="21" customHeight="1">
       <c r="A108" s="9">
@@ -6376,6 +8053,22 @@
         <f>IF(C108="","",N(D108)*N(E108))</f>
         <v/>
       </c>
+      <c r="H108" s="9">
+        <f>IF('الفواتير'!$E108="يدوية",'الفواتير'!$D108,"")</f>
+        <v/>
+      </c>
+      <c r="I108" s="14">
+        <f>IF($H108="","",'الفواتير'!$F108)</f>
+        <v/>
+      </c>
+      <c r="J108" s="14">
+        <f>IF($H108="","",SUMIF($B$7:$B$606,$H108,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K108" s="15">
+        <f>IF($H108="","",IF($H108=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H108)=0,"🟡 ما انزلت بنودها",IF(ROUND($I108-$J108,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I108-$J108,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="109" ht="21" customHeight="1">
       <c r="A109" s="9">
@@ -6390,6 +8083,22 @@
         <f>IF(C109="","",N(D109)*N(E109))</f>
         <v/>
       </c>
+      <c r="H109" s="9">
+        <f>IF('الفواتير'!$E109="يدوية",'الفواتير'!$D109,"")</f>
+        <v/>
+      </c>
+      <c r="I109" s="14">
+        <f>IF($H109="","",'الفواتير'!$F109)</f>
+        <v/>
+      </c>
+      <c r="J109" s="14">
+        <f>IF($H109="","",SUMIF($B$7:$B$606,$H109,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K109" s="15">
+        <f>IF($H109="","",IF($H109=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H109)=0,"🟡 ما انزلت بنودها",IF(ROUND($I109-$J109,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I109-$J109,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="110" ht="21" customHeight="1">
       <c r="A110" s="9">
@@ -6404,6 +8113,22 @@
         <f>IF(C110="","",N(D110)*N(E110))</f>
         <v/>
       </c>
+      <c r="H110" s="9">
+        <f>IF('الفواتير'!$E110="يدوية",'الفواتير'!$D110,"")</f>
+        <v/>
+      </c>
+      <c r="I110" s="14">
+        <f>IF($H110="","",'الفواتير'!$F110)</f>
+        <v/>
+      </c>
+      <c r="J110" s="14">
+        <f>IF($H110="","",SUMIF($B$7:$B$606,$H110,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K110" s="15">
+        <f>IF($H110="","",IF($H110=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H110)=0,"🟡 ما انزلت بنودها",IF(ROUND($I110-$J110,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I110-$J110,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="111" ht="21" customHeight="1">
       <c r="A111" s="9">
@@ -6418,6 +8143,22 @@
         <f>IF(C111="","",N(D111)*N(E111))</f>
         <v/>
       </c>
+      <c r="H111" s="9">
+        <f>IF('الفواتير'!$E111="يدوية",'الفواتير'!$D111,"")</f>
+        <v/>
+      </c>
+      <c r="I111" s="14">
+        <f>IF($H111="","",'الفواتير'!$F111)</f>
+        <v/>
+      </c>
+      <c r="J111" s="14">
+        <f>IF($H111="","",SUMIF($B$7:$B$606,$H111,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K111" s="15">
+        <f>IF($H111="","",IF($H111=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H111)=0,"🟡 ما انزلت بنودها",IF(ROUND($I111-$J111,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I111-$J111,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="112" ht="21" customHeight="1">
       <c r="A112" s="9">
@@ -6432,6 +8173,22 @@
         <f>IF(C112="","",N(D112)*N(E112))</f>
         <v/>
       </c>
+      <c r="H112" s="9">
+        <f>IF('الفواتير'!$E112="يدوية",'الفواتير'!$D112,"")</f>
+        <v/>
+      </c>
+      <c r="I112" s="14">
+        <f>IF($H112="","",'الفواتير'!$F112)</f>
+        <v/>
+      </c>
+      <c r="J112" s="14">
+        <f>IF($H112="","",SUMIF($B$7:$B$606,$H112,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K112" s="15">
+        <f>IF($H112="","",IF($H112=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H112)=0,"🟡 ما انزلت بنودها",IF(ROUND($I112-$J112,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I112-$J112,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="113" ht="21" customHeight="1">
       <c r="A113" s="9">
@@ -6446,6 +8203,22 @@
         <f>IF(C113="","",N(D113)*N(E113))</f>
         <v/>
       </c>
+      <c r="H113" s="9">
+        <f>IF('الفواتير'!$E113="يدوية",'الفواتير'!$D113,"")</f>
+        <v/>
+      </c>
+      <c r="I113" s="14">
+        <f>IF($H113="","",'الفواتير'!$F113)</f>
+        <v/>
+      </c>
+      <c r="J113" s="14">
+        <f>IF($H113="","",SUMIF($B$7:$B$606,$H113,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K113" s="15">
+        <f>IF($H113="","",IF($H113=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H113)=0,"🟡 ما انزلت بنودها",IF(ROUND($I113-$J113,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I113-$J113,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="114" ht="21" customHeight="1">
       <c r="A114" s="9">
@@ -6460,6 +8233,22 @@
         <f>IF(C114="","",N(D114)*N(E114))</f>
         <v/>
       </c>
+      <c r="H114" s="9">
+        <f>IF('الفواتير'!$E114="يدوية",'الفواتير'!$D114,"")</f>
+        <v/>
+      </c>
+      <c r="I114" s="14">
+        <f>IF($H114="","",'الفواتير'!$F114)</f>
+        <v/>
+      </c>
+      <c r="J114" s="14">
+        <f>IF($H114="","",SUMIF($B$7:$B$606,$H114,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K114" s="15">
+        <f>IF($H114="","",IF($H114=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H114)=0,"🟡 ما انزلت بنودها",IF(ROUND($I114-$J114,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I114-$J114,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="115" ht="21" customHeight="1">
       <c r="A115" s="9">
@@ -6474,6 +8263,22 @@
         <f>IF(C115="","",N(D115)*N(E115))</f>
         <v/>
       </c>
+      <c r="H115" s="9">
+        <f>IF('الفواتير'!$E115="يدوية",'الفواتير'!$D115,"")</f>
+        <v/>
+      </c>
+      <c r="I115" s="14">
+        <f>IF($H115="","",'الفواتير'!$F115)</f>
+        <v/>
+      </c>
+      <c r="J115" s="14">
+        <f>IF($H115="","",SUMIF($B$7:$B$606,$H115,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K115" s="15">
+        <f>IF($H115="","",IF($H115=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H115)=0,"🟡 ما انزلت بنودها",IF(ROUND($I115-$J115,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I115-$J115,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="116" ht="21" customHeight="1">
       <c r="A116" s="9">
@@ -6488,6 +8293,22 @@
         <f>IF(C116="","",N(D116)*N(E116))</f>
         <v/>
       </c>
+      <c r="H116" s="9">
+        <f>IF('الفواتير'!$E116="يدوية",'الفواتير'!$D116,"")</f>
+        <v/>
+      </c>
+      <c r="I116" s="14">
+        <f>IF($H116="","",'الفواتير'!$F116)</f>
+        <v/>
+      </c>
+      <c r="J116" s="14">
+        <f>IF($H116="","",SUMIF($B$7:$B$606,$H116,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K116" s="15">
+        <f>IF($H116="","",IF($H116=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H116)=0,"🟡 ما انزلت بنودها",IF(ROUND($I116-$J116,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I116-$J116,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="117" ht="21" customHeight="1">
       <c r="A117" s="9">
@@ -6502,6 +8323,22 @@
         <f>IF(C117="","",N(D117)*N(E117))</f>
         <v/>
       </c>
+      <c r="H117" s="9">
+        <f>IF('الفواتير'!$E117="يدوية",'الفواتير'!$D117,"")</f>
+        <v/>
+      </c>
+      <c r="I117" s="14">
+        <f>IF($H117="","",'الفواتير'!$F117)</f>
+        <v/>
+      </c>
+      <c r="J117" s="14">
+        <f>IF($H117="","",SUMIF($B$7:$B$606,$H117,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K117" s="15">
+        <f>IF($H117="","",IF($H117=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H117)=0,"🟡 ما انزلت بنودها",IF(ROUND($I117-$J117,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I117-$J117,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="118" ht="21" customHeight="1">
       <c r="A118" s="9">
@@ -6516,6 +8353,22 @@
         <f>IF(C118="","",N(D118)*N(E118))</f>
         <v/>
       </c>
+      <c r="H118" s="9">
+        <f>IF('الفواتير'!$E118="يدوية",'الفواتير'!$D118,"")</f>
+        <v/>
+      </c>
+      <c r="I118" s="14">
+        <f>IF($H118="","",'الفواتير'!$F118)</f>
+        <v/>
+      </c>
+      <c r="J118" s="14">
+        <f>IF($H118="","",SUMIF($B$7:$B$606,$H118,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K118" s="15">
+        <f>IF($H118="","",IF($H118=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H118)=0,"🟡 ما انزلت بنودها",IF(ROUND($I118-$J118,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I118-$J118,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="119" ht="21" customHeight="1">
       <c r="A119" s="9">
@@ -6530,6 +8383,22 @@
         <f>IF(C119="","",N(D119)*N(E119))</f>
         <v/>
       </c>
+      <c r="H119" s="9">
+        <f>IF('الفواتير'!$E119="يدوية",'الفواتير'!$D119,"")</f>
+        <v/>
+      </c>
+      <c r="I119" s="14">
+        <f>IF($H119="","",'الفواتير'!$F119)</f>
+        <v/>
+      </c>
+      <c r="J119" s="14">
+        <f>IF($H119="","",SUMIF($B$7:$B$606,$H119,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K119" s="15">
+        <f>IF($H119="","",IF($H119=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H119)=0,"🟡 ما انزلت بنودها",IF(ROUND($I119-$J119,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I119-$J119,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="120" ht="21" customHeight="1">
       <c r="A120" s="9">
@@ -6544,6 +8413,22 @@
         <f>IF(C120="","",N(D120)*N(E120))</f>
         <v/>
       </c>
+      <c r="H120" s="9">
+        <f>IF('الفواتير'!$E120="يدوية",'الفواتير'!$D120,"")</f>
+        <v/>
+      </c>
+      <c r="I120" s="14">
+        <f>IF($H120="","",'الفواتير'!$F120)</f>
+        <v/>
+      </c>
+      <c r="J120" s="14">
+        <f>IF($H120="","",SUMIF($B$7:$B$606,$H120,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K120" s="15">
+        <f>IF($H120="","",IF($H120=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H120)=0,"🟡 ما انزلت بنودها",IF(ROUND($I120-$J120,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I120-$J120,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="121" ht="21" customHeight="1">
       <c r="A121" s="9">
@@ -6558,6 +8443,22 @@
         <f>IF(C121="","",N(D121)*N(E121))</f>
         <v/>
       </c>
+      <c r="H121" s="9">
+        <f>IF('الفواتير'!$E121="يدوية",'الفواتير'!$D121,"")</f>
+        <v/>
+      </c>
+      <c r="I121" s="14">
+        <f>IF($H121="","",'الفواتير'!$F121)</f>
+        <v/>
+      </c>
+      <c r="J121" s="14">
+        <f>IF($H121="","",SUMIF($B$7:$B$606,$H121,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K121" s="15">
+        <f>IF($H121="","",IF($H121=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H121)=0,"🟡 ما انزلت بنودها",IF(ROUND($I121-$J121,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I121-$J121,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="122" ht="21" customHeight="1">
       <c r="A122" s="9">
@@ -6572,6 +8473,22 @@
         <f>IF(C122="","",N(D122)*N(E122))</f>
         <v/>
       </c>
+      <c r="H122" s="9">
+        <f>IF('الفواتير'!$E122="يدوية",'الفواتير'!$D122,"")</f>
+        <v/>
+      </c>
+      <c r="I122" s="14">
+        <f>IF($H122="","",'الفواتير'!$F122)</f>
+        <v/>
+      </c>
+      <c r="J122" s="14">
+        <f>IF($H122="","",SUMIF($B$7:$B$606,$H122,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K122" s="15">
+        <f>IF($H122="","",IF($H122=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H122)=0,"🟡 ما انزلت بنودها",IF(ROUND($I122-$J122,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I122-$J122,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="123" ht="21" customHeight="1">
       <c r="A123" s="9">
@@ -6586,6 +8503,22 @@
         <f>IF(C123="","",N(D123)*N(E123))</f>
         <v/>
       </c>
+      <c r="H123" s="9">
+        <f>IF('الفواتير'!$E123="يدوية",'الفواتير'!$D123,"")</f>
+        <v/>
+      </c>
+      <c r="I123" s="14">
+        <f>IF($H123="","",'الفواتير'!$F123)</f>
+        <v/>
+      </c>
+      <c r="J123" s="14">
+        <f>IF($H123="","",SUMIF($B$7:$B$606,$H123,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K123" s="15">
+        <f>IF($H123="","",IF($H123=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H123)=0,"🟡 ما انزلت بنودها",IF(ROUND($I123-$J123,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I123-$J123,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="124" ht="21" customHeight="1">
       <c r="A124" s="9">
@@ -6600,6 +8533,22 @@
         <f>IF(C124="","",N(D124)*N(E124))</f>
         <v/>
       </c>
+      <c r="H124" s="9">
+        <f>IF('الفواتير'!$E124="يدوية",'الفواتير'!$D124,"")</f>
+        <v/>
+      </c>
+      <c r="I124" s="14">
+        <f>IF($H124="","",'الفواتير'!$F124)</f>
+        <v/>
+      </c>
+      <c r="J124" s="14">
+        <f>IF($H124="","",SUMIF($B$7:$B$606,$H124,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K124" s="15">
+        <f>IF($H124="","",IF($H124=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H124)=0,"🟡 ما انزلت بنودها",IF(ROUND($I124-$J124,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I124-$J124,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="125" ht="21" customHeight="1">
       <c r="A125" s="9">
@@ -6614,6 +8563,22 @@
         <f>IF(C125="","",N(D125)*N(E125))</f>
         <v/>
       </c>
+      <c r="H125" s="9">
+        <f>IF('الفواتير'!$E125="يدوية",'الفواتير'!$D125,"")</f>
+        <v/>
+      </c>
+      <c r="I125" s="14">
+        <f>IF($H125="","",'الفواتير'!$F125)</f>
+        <v/>
+      </c>
+      <c r="J125" s="14">
+        <f>IF($H125="","",SUMIF($B$7:$B$606,$H125,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K125" s="15">
+        <f>IF($H125="","",IF($H125=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H125)=0,"🟡 ما انزلت بنودها",IF(ROUND($I125-$J125,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I125-$J125,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="126" ht="21" customHeight="1">
       <c r="A126" s="9">
@@ -6628,6 +8593,22 @@
         <f>IF(C126="","",N(D126)*N(E126))</f>
         <v/>
       </c>
+      <c r="H126" s="9">
+        <f>IF('الفواتير'!$E126="يدوية",'الفواتير'!$D126,"")</f>
+        <v/>
+      </c>
+      <c r="I126" s="14">
+        <f>IF($H126="","",'الفواتير'!$F126)</f>
+        <v/>
+      </c>
+      <c r="J126" s="14">
+        <f>IF($H126="","",SUMIF($B$7:$B$606,$H126,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K126" s="15">
+        <f>IF($H126="","",IF($H126=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H126)=0,"🟡 ما انزلت بنودها",IF(ROUND($I126-$J126,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I126-$J126,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="127" ht="21" customHeight="1">
       <c r="A127" s="9">
@@ -6642,6 +8623,22 @@
         <f>IF(C127="","",N(D127)*N(E127))</f>
         <v/>
       </c>
+      <c r="H127" s="9">
+        <f>IF('الفواتير'!$E127="يدوية",'الفواتير'!$D127,"")</f>
+        <v/>
+      </c>
+      <c r="I127" s="14">
+        <f>IF($H127="","",'الفواتير'!$F127)</f>
+        <v/>
+      </c>
+      <c r="J127" s="14">
+        <f>IF($H127="","",SUMIF($B$7:$B$606,$H127,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K127" s="15">
+        <f>IF($H127="","",IF($H127=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H127)=0,"🟡 ما انزلت بنودها",IF(ROUND($I127-$J127,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I127-$J127,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="128" ht="21" customHeight="1">
       <c r="A128" s="9">
@@ -6656,6 +8653,22 @@
         <f>IF(C128="","",N(D128)*N(E128))</f>
         <v/>
       </c>
+      <c r="H128" s="9">
+        <f>IF('الفواتير'!$E128="يدوية",'الفواتير'!$D128,"")</f>
+        <v/>
+      </c>
+      <c r="I128" s="14">
+        <f>IF($H128="","",'الفواتير'!$F128)</f>
+        <v/>
+      </c>
+      <c r="J128" s="14">
+        <f>IF($H128="","",SUMIF($B$7:$B$606,$H128,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K128" s="15">
+        <f>IF($H128="","",IF($H128=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H128)=0,"🟡 ما انزلت بنودها",IF(ROUND($I128-$J128,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I128-$J128,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="129" ht="21" customHeight="1">
       <c r="A129" s="9">
@@ -6670,6 +8683,22 @@
         <f>IF(C129="","",N(D129)*N(E129))</f>
         <v/>
       </c>
+      <c r="H129" s="9">
+        <f>IF('الفواتير'!$E129="يدوية",'الفواتير'!$D129,"")</f>
+        <v/>
+      </c>
+      <c r="I129" s="14">
+        <f>IF($H129="","",'الفواتير'!$F129)</f>
+        <v/>
+      </c>
+      <c r="J129" s="14">
+        <f>IF($H129="","",SUMIF($B$7:$B$606,$H129,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K129" s="15">
+        <f>IF($H129="","",IF($H129=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H129)=0,"🟡 ما انزلت بنودها",IF(ROUND($I129-$J129,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I129-$J129,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="130" ht="21" customHeight="1">
       <c r="A130" s="9">
@@ -6684,6 +8713,22 @@
         <f>IF(C130="","",N(D130)*N(E130))</f>
         <v/>
       </c>
+      <c r="H130" s="9">
+        <f>IF('الفواتير'!$E130="يدوية",'الفواتير'!$D130,"")</f>
+        <v/>
+      </c>
+      <c r="I130" s="14">
+        <f>IF($H130="","",'الفواتير'!$F130)</f>
+        <v/>
+      </c>
+      <c r="J130" s="14">
+        <f>IF($H130="","",SUMIF($B$7:$B$606,$H130,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K130" s="15">
+        <f>IF($H130="","",IF($H130=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H130)=0,"🟡 ما انزلت بنودها",IF(ROUND($I130-$J130,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I130-$J130,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="131" ht="21" customHeight="1">
       <c r="A131" s="9">
@@ -6698,6 +8743,22 @@
         <f>IF(C131="","",N(D131)*N(E131))</f>
         <v/>
       </c>
+      <c r="H131" s="9">
+        <f>IF('الفواتير'!$E131="يدوية",'الفواتير'!$D131,"")</f>
+        <v/>
+      </c>
+      <c r="I131" s="14">
+        <f>IF($H131="","",'الفواتير'!$F131)</f>
+        <v/>
+      </c>
+      <c r="J131" s="14">
+        <f>IF($H131="","",SUMIF($B$7:$B$606,$H131,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K131" s="15">
+        <f>IF($H131="","",IF($H131=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H131)=0,"🟡 ما انزلت بنودها",IF(ROUND($I131-$J131,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I131-$J131,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="132" ht="21" customHeight="1">
       <c r="A132" s="9">
@@ -6712,6 +8773,22 @@
         <f>IF(C132="","",N(D132)*N(E132))</f>
         <v/>
       </c>
+      <c r="H132" s="9">
+        <f>IF('الفواتير'!$E132="يدوية",'الفواتير'!$D132,"")</f>
+        <v/>
+      </c>
+      <c r="I132" s="14">
+        <f>IF($H132="","",'الفواتير'!$F132)</f>
+        <v/>
+      </c>
+      <c r="J132" s="14">
+        <f>IF($H132="","",SUMIF($B$7:$B$606,$H132,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K132" s="15">
+        <f>IF($H132="","",IF($H132=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H132)=0,"🟡 ما انزلت بنودها",IF(ROUND($I132-$J132,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I132-$J132,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="133" ht="21" customHeight="1">
       <c r="A133" s="9">
@@ -6726,6 +8803,22 @@
         <f>IF(C133="","",N(D133)*N(E133))</f>
         <v/>
       </c>
+      <c r="H133" s="9">
+        <f>IF('الفواتير'!$E133="يدوية",'الفواتير'!$D133,"")</f>
+        <v/>
+      </c>
+      <c r="I133" s="14">
+        <f>IF($H133="","",'الفواتير'!$F133)</f>
+        <v/>
+      </c>
+      <c r="J133" s="14">
+        <f>IF($H133="","",SUMIF($B$7:$B$606,$H133,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K133" s="15">
+        <f>IF($H133="","",IF($H133=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H133)=0,"🟡 ما انزلت بنودها",IF(ROUND($I133-$J133,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I133-$J133,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="134" ht="21" customHeight="1">
       <c r="A134" s="9">
@@ -6740,6 +8833,22 @@
         <f>IF(C134="","",N(D134)*N(E134))</f>
         <v/>
       </c>
+      <c r="H134" s="9">
+        <f>IF('الفواتير'!$E134="يدوية",'الفواتير'!$D134,"")</f>
+        <v/>
+      </c>
+      <c r="I134" s="14">
+        <f>IF($H134="","",'الفواتير'!$F134)</f>
+        <v/>
+      </c>
+      <c r="J134" s="14">
+        <f>IF($H134="","",SUMIF($B$7:$B$606,$H134,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K134" s="15">
+        <f>IF($H134="","",IF($H134=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H134)=0,"🟡 ما انزلت بنودها",IF(ROUND($I134-$J134,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I134-$J134,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="135" ht="21" customHeight="1">
       <c r="A135" s="9">
@@ -6754,6 +8863,22 @@
         <f>IF(C135="","",N(D135)*N(E135))</f>
         <v/>
       </c>
+      <c r="H135" s="9">
+        <f>IF('الفواتير'!$E135="يدوية",'الفواتير'!$D135,"")</f>
+        <v/>
+      </c>
+      <c r="I135" s="14">
+        <f>IF($H135="","",'الفواتير'!$F135)</f>
+        <v/>
+      </c>
+      <c r="J135" s="14">
+        <f>IF($H135="","",SUMIF($B$7:$B$606,$H135,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K135" s="15">
+        <f>IF($H135="","",IF($H135=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H135)=0,"🟡 ما انزلت بنودها",IF(ROUND($I135-$J135,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I135-$J135,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="136" ht="21" customHeight="1">
       <c r="A136" s="9">
@@ -6768,6 +8893,22 @@
         <f>IF(C136="","",N(D136)*N(E136))</f>
         <v/>
       </c>
+      <c r="H136" s="9">
+        <f>IF('الفواتير'!$E136="يدوية",'الفواتير'!$D136,"")</f>
+        <v/>
+      </c>
+      <c r="I136" s="14">
+        <f>IF($H136="","",'الفواتير'!$F136)</f>
+        <v/>
+      </c>
+      <c r="J136" s="14">
+        <f>IF($H136="","",SUMIF($B$7:$B$606,$H136,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K136" s="15">
+        <f>IF($H136="","",IF($H136=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H136)=0,"🟡 ما انزلت بنودها",IF(ROUND($I136-$J136,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I136-$J136,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="137" ht="21" customHeight="1">
       <c r="A137" s="9">
@@ -6782,6 +8923,22 @@
         <f>IF(C137="","",N(D137)*N(E137))</f>
         <v/>
       </c>
+      <c r="H137" s="9">
+        <f>IF('الفواتير'!$E137="يدوية",'الفواتير'!$D137,"")</f>
+        <v/>
+      </c>
+      <c r="I137" s="14">
+        <f>IF($H137="","",'الفواتير'!$F137)</f>
+        <v/>
+      </c>
+      <c r="J137" s="14">
+        <f>IF($H137="","",SUMIF($B$7:$B$606,$H137,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K137" s="15">
+        <f>IF($H137="","",IF($H137=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H137)=0,"🟡 ما انزلت بنودها",IF(ROUND($I137-$J137,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I137-$J137,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="138" ht="21" customHeight="1">
       <c r="A138" s="9">
@@ -6796,6 +8953,22 @@
         <f>IF(C138="","",N(D138)*N(E138))</f>
         <v/>
       </c>
+      <c r="H138" s="9">
+        <f>IF('الفواتير'!$E138="يدوية",'الفواتير'!$D138,"")</f>
+        <v/>
+      </c>
+      <c r="I138" s="14">
+        <f>IF($H138="","",'الفواتير'!$F138)</f>
+        <v/>
+      </c>
+      <c r="J138" s="14">
+        <f>IF($H138="","",SUMIF($B$7:$B$606,$H138,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K138" s="15">
+        <f>IF($H138="","",IF($H138=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H138)=0,"🟡 ما انزلت بنودها",IF(ROUND($I138-$J138,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I138-$J138,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="139" ht="21" customHeight="1">
       <c r="A139" s="9">
@@ -6810,6 +8983,22 @@
         <f>IF(C139="","",N(D139)*N(E139))</f>
         <v/>
       </c>
+      <c r="H139" s="9">
+        <f>IF('الفواتير'!$E139="يدوية",'الفواتير'!$D139,"")</f>
+        <v/>
+      </c>
+      <c r="I139" s="14">
+        <f>IF($H139="","",'الفواتير'!$F139)</f>
+        <v/>
+      </c>
+      <c r="J139" s="14">
+        <f>IF($H139="","",SUMIF($B$7:$B$606,$H139,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K139" s="15">
+        <f>IF($H139="","",IF($H139=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H139)=0,"🟡 ما انزلت بنودها",IF(ROUND($I139-$J139,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I139-$J139,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="140" ht="21" customHeight="1">
       <c r="A140" s="9">
@@ -6824,6 +9013,22 @@
         <f>IF(C140="","",N(D140)*N(E140))</f>
         <v/>
       </c>
+      <c r="H140" s="9">
+        <f>IF('الفواتير'!$E140="يدوية",'الفواتير'!$D140,"")</f>
+        <v/>
+      </c>
+      <c r="I140" s="14">
+        <f>IF($H140="","",'الفواتير'!$F140)</f>
+        <v/>
+      </c>
+      <c r="J140" s="14">
+        <f>IF($H140="","",SUMIF($B$7:$B$606,$H140,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K140" s="15">
+        <f>IF($H140="","",IF($H140=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H140)=0,"🟡 ما انزلت بنودها",IF(ROUND($I140-$J140,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I140-$J140,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="141" ht="21" customHeight="1">
       <c r="A141" s="9">
@@ -6838,6 +9043,22 @@
         <f>IF(C141="","",N(D141)*N(E141))</f>
         <v/>
       </c>
+      <c r="H141" s="9">
+        <f>IF('الفواتير'!$E141="يدوية",'الفواتير'!$D141,"")</f>
+        <v/>
+      </c>
+      <c r="I141" s="14">
+        <f>IF($H141="","",'الفواتير'!$F141)</f>
+        <v/>
+      </c>
+      <c r="J141" s="14">
+        <f>IF($H141="","",SUMIF($B$7:$B$606,$H141,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K141" s="15">
+        <f>IF($H141="","",IF($H141=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H141)=0,"🟡 ما انزلت بنودها",IF(ROUND($I141-$J141,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I141-$J141,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="142" ht="21" customHeight="1">
       <c r="A142" s="9">
@@ -6852,6 +9073,22 @@
         <f>IF(C142="","",N(D142)*N(E142))</f>
         <v/>
       </c>
+      <c r="H142" s="9">
+        <f>IF('الفواتير'!$E142="يدوية",'الفواتير'!$D142,"")</f>
+        <v/>
+      </c>
+      <c r="I142" s="14">
+        <f>IF($H142="","",'الفواتير'!$F142)</f>
+        <v/>
+      </c>
+      <c r="J142" s="14">
+        <f>IF($H142="","",SUMIF($B$7:$B$606,$H142,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K142" s="15">
+        <f>IF($H142="","",IF($H142=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H142)=0,"🟡 ما انزلت بنودها",IF(ROUND($I142-$J142,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I142-$J142,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="143" ht="21" customHeight="1">
       <c r="A143" s="9">
@@ -6866,6 +9103,22 @@
         <f>IF(C143="","",N(D143)*N(E143))</f>
         <v/>
       </c>
+      <c r="H143" s="9">
+        <f>IF('الفواتير'!$E143="يدوية",'الفواتير'!$D143,"")</f>
+        <v/>
+      </c>
+      <c r="I143" s="14">
+        <f>IF($H143="","",'الفواتير'!$F143)</f>
+        <v/>
+      </c>
+      <c r="J143" s="14">
+        <f>IF($H143="","",SUMIF($B$7:$B$606,$H143,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K143" s="15">
+        <f>IF($H143="","",IF($H143=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H143)=0,"🟡 ما انزلت بنودها",IF(ROUND($I143-$J143,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I143-$J143,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="144" ht="21" customHeight="1">
       <c r="A144" s="9">
@@ -6880,6 +9133,22 @@
         <f>IF(C144="","",N(D144)*N(E144))</f>
         <v/>
       </c>
+      <c r="H144" s="9">
+        <f>IF('الفواتير'!$E144="يدوية",'الفواتير'!$D144,"")</f>
+        <v/>
+      </c>
+      <c r="I144" s="14">
+        <f>IF($H144="","",'الفواتير'!$F144)</f>
+        <v/>
+      </c>
+      <c r="J144" s="14">
+        <f>IF($H144="","",SUMIF($B$7:$B$606,$H144,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K144" s="15">
+        <f>IF($H144="","",IF($H144=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H144)=0,"🟡 ما انزلت بنودها",IF(ROUND($I144-$J144,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I144-$J144,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="145" ht="21" customHeight="1">
       <c r="A145" s="9">
@@ -6894,6 +9163,22 @@
         <f>IF(C145="","",N(D145)*N(E145))</f>
         <v/>
       </c>
+      <c r="H145" s="9">
+        <f>IF('الفواتير'!$E145="يدوية",'الفواتير'!$D145,"")</f>
+        <v/>
+      </c>
+      <c r="I145" s="14">
+        <f>IF($H145="","",'الفواتير'!$F145)</f>
+        <v/>
+      </c>
+      <c r="J145" s="14">
+        <f>IF($H145="","",SUMIF($B$7:$B$606,$H145,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K145" s="15">
+        <f>IF($H145="","",IF($H145=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H145)=0,"🟡 ما انزلت بنودها",IF(ROUND($I145-$J145,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I145-$J145,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="146" ht="21" customHeight="1">
       <c r="A146" s="9">
@@ -6908,6 +9193,22 @@
         <f>IF(C146="","",N(D146)*N(E146))</f>
         <v/>
       </c>
+      <c r="H146" s="9">
+        <f>IF('الفواتير'!$E146="يدوية",'الفواتير'!$D146,"")</f>
+        <v/>
+      </c>
+      <c r="I146" s="14">
+        <f>IF($H146="","",'الفواتير'!$F146)</f>
+        <v/>
+      </c>
+      <c r="J146" s="14">
+        <f>IF($H146="","",SUMIF($B$7:$B$606,$H146,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K146" s="15">
+        <f>IF($H146="","",IF($H146=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H146)=0,"🟡 ما انزلت بنودها",IF(ROUND($I146-$J146,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I146-$J146,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="147" ht="21" customHeight="1">
       <c r="A147" s="9">
@@ -6922,6 +9223,22 @@
         <f>IF(C147="","",N(D147)*N(E147))</f>
         <v/>
       </c>
+      <c r="H147" s="9">
+        <f>IF('الفواتير'!$E147="يدوية",'الفواتير'!$D147,"")</f>
+        <v/>
+      </c>
+      <c r="I147" s="14">
+        <f>IF($H147="","",'الفواتير'!$F147)</f>
+        <v/>
+      </c>
+      <c r="J147" s="14">
+        <f>IF($H147="","",SUMIF($B$7:$B$606,$H147,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K147" s="15">
+        <f>IF($H147="","",IF($H147=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H147)=0,"🟡 ما انزلت بنودها",IF(ROUND($I147-$J147,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I147-$J147,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="148" ht="21" customHeight="1">
       <c r="A148" s="9">
@@ -6936,6 +9253,22 @@
         <f>IF(C148="","",N(D148)*N(E148))</f>
         <v/>
       </c>
+      <c r="H148" s="9">
+        <f>IF('الفواتير'!$E148="يدوية",'الفواتير'!$D148,"")</f>
+        <v/>
+      </c>
+      <c r="I148" s="14">
+        <f>IF($H148="","",'الفواتير'!$F148)</f>
+        <v/>
+      </c>
+      <c r="J148" s="14">
+        <f>IF($H148="","",SUMIF($B$7:$B$606,$H148,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K148" s="15">
+        <f>IF($H148="","",IF($H148=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H148)=0,"🟡 ما انزلت بنودها",IF(ROUND($I148-$J148,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I148-$J148,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="149" ht="21" customHeight="1">
       <c r="A149" s="9">
@@ -6950,6 +9283,22 @@
         <f>IF(C149="","",N(D149)*N(E149))</f>
         <v/>
       </c>
+      <c r="H149" s="9">
+        <f>IF('الفواتير'!$E149="يدوية",'الفواتير'!$D149,"")</f>
+        <v/>
+      </c>
+      <c r="I149" s="14">
+        <f>IF($H149="","",'الفواتير'!$F149)</f>
+        <v/>
+      </c>
+      <c r="J149" s="14">
+        <f>IF($H149="","",SUMIF($B$7:$B$606,$H149,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K149" s="15">
+        <f>IF($H149="","",IF($H149=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H149)=0,"🟡 ما انزلت بنودها",IF(ROUND($I149-$J149,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I149-$J149,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="150" ht="21" customHeight="1">
       <c r="A150" s="9">
@@ -6964,6 +9313,22 @@
         <f>IF(C150="","",N(D150)*N(E150))</f>
         <v/>
       </c>
+      <c r="H150" s="9">
+        <f>IF('الفواتير'!$E150="يدوية",'الفواتير'!$D150,"")</f>
+        <v/>
+      </c>
+      <c r="I150" s="14">
+        <f>IF($H150="","",'الفواتير'!$F150)</f>
+        <v/>
+      </c>
+      <c r="J150" s="14">
+        <f>IF($H150="","",SUMIF($B$7:$B$606,$H150,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K150" s="15">
+        <f>IF($H150="","",IF($H150=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H150)=0,"🟡 ما انزلت بنودها",IF(ROUND($I150-$J150,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I150-$J150,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="151" ht="21" customHeight="1">
       <c r="A151" s="9">
@@ -6978,6 +9343,22 @@
         <f>IF(C151="","",N(D151)*N(E151))</f>
         <v/>
       </c>
+      <c r="H151" s="9">
+        <f>IF('الفواتير'!$E151="يدوية",'الفواتير'!$D151,"")</f>
+        <v/>
+      </c>
+      <c r="I151" s="14">
+        <f>IF($H151="","",'الفواتير'!$F151)</f>
+        <v/>
+      </c>
+      <c r="J151" s="14">
+        <f>IF($H151="","",SUMIF($B$7:$B$606,$H151,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K151" s="15">
+        <f>IF($H151="","",IF($H151=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H151)=0,"🟡 ما انزلت بنودها",IF(ROUND($I151-$J151,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I151-$J151,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="152" ht="21" customHeight="1">
       <c r="A152" s="9">
@@ -6992,6 +9373,22 @@
         <f>IF(C152="","",N(D152)*N(E152))</f>
         <v/>
       </c>
+      <c r="H152" s="9">
+        <f>IF('الفواتير'!$E152="يدوية",'الفواتير'!$D152,"")</f>
+        <v/>
+      </c>
+      <c r="I152" s="14">
+        <f>IF($H152="","",'الفواتير'!$F152)</f>
+        <v/>
+      </c>
+      <c r="J152" s="14">
+        <f>IF($H152="","",SUMIF($B$7:$B$606,$H152,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K152" s="15">
+        <f>IF($H152="","",IF($H152=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H152)=0,"🟡 ما انزلت بنودها",IF(ROUND($I152-$J152,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I152-$J152,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="153" ht="21" customHeight="1">
       <c r="A153" s="9">
@@ -7006,6 +9403,22 @@
         <f>IF(C153="","",N(D153)*N(E153))</f>
         <v/>
       </c>
+      <c r="H153" s="9">
+        <f>IF('الفواتير'!$E153="يدوية",'الفواتير'!$D153,"")</f>
+        <v/>
+      </c>
+      <c r="I153" s="14">
+        <f>IF($H153="","",'الفواتير'!$F153)</f>
+        <v/>
+      </c>
+      <c r="J153" s="14">
+        <f>IF($H153="","",SUMIF($B$7:$B$606,$H153,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K153" s="15">
+        <f>IF($H153="","",IF($H153=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H153)=0,"🟡 ما انزلت بنودها",IF(ROUND($I153-$J153,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I153-$J153,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="154" ht="21" customHeight="1">
       <c r="A154" s="9">
@@ -7020,6 +9433,22 @@
         <f>IF(C154="","",N(D154)*N(E154))</f>
         <v/>
       </c>
+      <c r="H154" s="9">
+        <f>IF('الفواتير'!$E154="يدوية",'الفواتير'!$D154,"")</f>
+        <v/>
+      </c>
+      <c r="I154" s="14">
+        <f>IF($H154="","",'الفواتير'!$F154)</f>
+        <v/>
+      </c>
+      <c r="J154" s="14">
+        <f>IF($H154="","",SUMIF($B$7:$B$606,$H154,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K154" s="15">
+        <f>IF($H154="","",IF($H154=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H154)=0,"🟡 ما انزلت بنودها",IF(ROUND($I154-$J154,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I154-$J154,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="155" ht="21" customHeight="1">
       <c r="A155" s="9">
@@ -7034,6 +9463,22 @@
         <f>IF(C155="","",N(D155)*N(E155))</f>
         <v/>
       </c>
+      <c r="H155" s="9">
+        <f>IF('الفواتير'!$E155="يدوية",'الفواتير'!$D155,"")</f>
+        <v/>
+      </c>
+      <c r="I155" s="14">
+        <f>IF($H155="","",'الفواتير'!$F155)</f>
+        <v/>
+      </c>
+      <c r="J155" s="14">
+        <f>IF($H155="","",SUMIF($B$7:$B$606,$H155,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K155" s="15">
+        <f>IF($H155="","",IF($H155=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H155)=0,"🟡 ما انزلت بنودها",IF(ROUND($I155-$J155,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I155-$J155,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="156" ht="21" customHeight="1">
       <c r="A156" s="9">
@@ -7048,6 +9493,22 @@
         <f>IF(C156="","",N(D156)*N(E156))</f>
         <v/>
       </c>
+      <c r="H156" s="9">
+        <f>IF('الفواتير'!$E156="يدوية",'الفواتير'!$D156,"")</f>
+        <v/>
+      </c>
+      <c r="I156" s="14">
+        <f>IF($H156="","",'الفواتير'!$F156)</f>
+        <v/>
+      </c>
+      <c r="J156" s="14">
+        <f>IF($H156="","",SUMIF($B$7:$B$606,$H156,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K156" s="15">
+        <f>IF($H156="","",IF($H156=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H156)=0,"🟡 ما انزلت بنودها",IF(ROUND($I156-$J156,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I156-$J156,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="157" ht="21" customHeight="1">
       <c r="A157" s="9">
@@ -7062,6 +9523,22 @@
         <f>IF(C157="","",N(D157)*N(E157))</f>
         <v/>
       </c>
+      <c r="H157" s="9">
+        <f>IF('الفواتير'!$E157="يدوية",'الفواتير'!$D157,"")</f>
+        <v/>
+      </c>
+      <c r="I157" s="14">
+        <f>IF($H157="","",'الفواتير'!$F157)</f>
+        <v/>
+      </c>
+      <c r="J157" s="14">
+        <f>IF($H157="","",SUMIF($B$7:$B$606,$H157,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K157" s="15">
+        <f>IF($H157="","",IF($H157=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H157)=0,"🟡 ما انزلت بنودها",IF(ROUND($I157-$J157,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I157-$J157,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="158" ht="21" customHeight="1">
       <c r="A158" s="9">
@@ -7076,6 +9553,22 @@
         <f>IF(C158="","",N(D158)*N(E158))</f>
         <v/>
       </c>
+      <c r="H158" s="9">
+        <f>IF('الفواتير'!$E158="يدوية",'الفواتير'!$D158,"")</f>
+        <v/>
+      </c>
+      <c r="I158" s="14">
+        <f>IF($H158="","",'الفواتير'!$F158)</f>
+        <v/>
+      </c>
+      <c r="J158" s="14">
+        <f>IF($H158="","",SUMIF($B$7:$B$606,$H158,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K158" s="15">
+        <f>IF($H158="","",IF($H158=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H158)=0,"🟡 ما انزلت بنودها",IF(ROUND($I158-$J158,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I158-$J158,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="159" ht="21" customHeight="1">
       <c r="A159" s="9">
@@ -7090,6 +9583,22 @@
         <f>IF(C159="","",N(D159)*N(E159))</f>
         <v/>
       </c>
+      <c r="H159" s="9">
+        <f>IF('الفواتير'!$E159="يدوية",'الفواتير'!$D159,"")</f>
+        <v/>
+      </c>
+      <c r="I159" s="14">
+        <f>IF($H159="","",'الفواتير'!$F159)</f>
+        <v/>
+      </c>
+      <c r="J159" s="14">
+        <f>IF($H159="","",SUMIF($B$7:$B$606,$H159,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K159" s="15">
+        <f>IF($H159="","",IF($H159=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H159)=0,"🟡 ما انزلت بنودها",IF(ROUND($I159-$J159,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I159-$J159,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="160" ht="21" customHeight="1">
       <c r="A160" s="9">
@@ -7104,6 +9613,22 @@
         <f>IF(C160="","",N(D160)*N(E160))</f>
         <v/>
       </c>
+      <c r="H160" s="9">
+        <f>IF('الفواتير'!$E160="يدوية",'الفواتير'!$D160,"")</f>
+        <v/>
+      </c>
+      <c r="I160" s="14">
+        <f>IF($H160="","",'الفواتير'!$F160)</f>
+        <v/>
+      </c>
+      <c r="J160" s="14">
+        <f>IF($H160="","",SUMIF($B$7:$B$606,$H160,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K160" s="15">
+        <f>IF($H160="","",IF($H160=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H160)=0,"🟡 ما انزلت بنودها",IF(ROUND($I160-$J160,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I160-$J160,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="161" ht="21" customHeight="1">
       <c r="A161" s="9">
@@ -7118,6 +9643,22 @@
         <f>IF(C161="","",N(D161)*N(E161))</f>
         <v/>
       </c>
+      <c r="H161" s="9">
+        <f>IF('الفواتير'!$E161="يدوية",'الفواتير'!$D161,"")</f>
+        <v/>
+      </c>
+      <c r="I161" s="14">
+        <f>IF($H161="","",'الفواتير'!$F161)</f>
+        <v/>
+      </c>
+      <c r="J161" s="14">
+        <f>IF($H161="","",SUMIF($B$7:$B$606,$H161,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K161" s="15">
+        <f>IF($H161="","",IF($H161=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H161)=0,"🟡 ما انزلت بنودها",IF(ROUND($I161-$J161,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I161-$J161,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="162" ht="21" customHeight="1">
       <c r="A162" s="9">
@@ -7132,6 +9673,22 @@
         <f>IF(C162="","",N(D162)*N(E162))</f>
         <v/>
       </c>
+      <c r="H162" s="9">
+        <f>IF('الفواتير'!$E162="يدوية",'الفواتير'!$D162,"")</f>
+        <v/>
+      </c>
+      <c r="I162" s="14">
+        <f>IF($H162="","",'الفواتير'!$F162)</f>
+        <v/>
+      </c>
+      <c r="J162" s="14">
+        <f>IF($H162="","",SUMIF($B$7:$B$606,$H162,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K162" s="15">
+        <f>IF($H162="","",IF($H162=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H162)=0,"🟡 ما انزلت بنودها",IF(ROUND($I162-$J162,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I162-$J162,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="163" ht="21" customHeight="1">
       <c r="A163" s="9">
@@ -7146,6 +9703,22 @@
         <f>IF(C163="","",N(D163)*N(E163))</f>
         <v/>
       </c>
+      <c r="H163" s="9">
+        <f>IF('الفواتير'!$E163="يدوية",'الفواتير'!$D163,"")</f>
+        <v/>
+      </c>
+      <c r="I163" s="14">
+        <f>IF($H163="","",'الفواتير'!$F163)</f>
+        <v/>
+      </c>
+      <c r="J163" s="14">
+        <f>IF($H163="","",SUMIF($B$7:$B$606,$H163,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K163" s="15">
+        <f>IF($H163="","",IF($H163=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H163)=0,"🟡 ما انزلت بنودها",IF(ROUND($I163-$J163,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I163-$J163,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="164" ht="21" customHeight="1">
       <c r="A164" s="9">
@@ -7160,6 +9733,22 @@
         <f>IF(C164="","",N(D164)*N(E164))</f>
         <v/>
       </c>
+      <c r="H164" s="9">
+        <f>IF('الفواتير'!$E164="يدوية",'الفواتير'!$D164,"")</f>
+        <v/>
+      </c>
+      <c r="I164" s="14">
+        <f>IF($H164="","",'الفواتير'!$F164)</f>
+        <v/>
+      </c>
+      <c r="J164" s="14">
+        <f>IF($H164="","",SUMIF($B$7:$B$606,$H164,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K164" s="15">
+        <f>IF($H164="","",IF($H164=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H164)=0,"🟡 ما انزلت بنودها",IF(ROUND($I164-$J164,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I164-$J164,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="165" ht="21" customHeight="1">
       <c r="A165" s="9">
@@ -7174,6 +9763,22 @@
         <f>IF(C165="","",N(D165)*N(E165))</f>
         <v/>
       </c>
+      <c r="H165" s="9">
+        <f>IF('الفواتير'!$E165="يدوية",'الفواتير'!$D165,"")</f>
+        <v/>
+      </c>
+      <c r="I165" s="14">
+        <f>IF($H165="","",'الفواتير'!$F165)</f>
+        <v/>
+      </c>
+      <c r="J165" s="14">
+        <f>IF($H165="","",SUMIF($B$7:$B$606,$H165,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K165" s="15">
+        <f>IF($H165="","",IF($H165=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H165)=0,"🟡 ما انزلت بنودها",IF(ROUND($I165-$J165,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I165-$J165,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="166" ht="21" customHeight="1">
       <c r="A166" s="9">
@@ -7188,6 +9793,22 @@
         <f>IF(C166="","",N(D166)*N(E166))</f>
         <v/>
       </c>
+      <c r="H166" s="9">
+        <f>IF('الفواتير'!$E166="يدوية",'الفواتير'!$D166,"")</f>
+        <v/>
+      </c>
+      <c r="I166" s="14">
+        <f>IF($H166="","",'الفواتير'!$F166)</f>
+        <v/>
+      </c>
+      <c r="J166" s="14">
+        <f>IF($H166="","",SUMIF($B$7:$B$606,$H166,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K166" s="15">
+        <f>IF($H166="","",IF($H166=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H166)=0,"🟡 ما انزلت بنودها",IF(ROUND($I166-$J166,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I166-$J166,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="167" ht="21" customHeight="1">
       <c r="A167" s="9">
@@ -7202,6 +9823,22 @@
         <f>IF(C167="","",N(D167)*N(E167))</f>
         <v/>
       </c>
+      <c r="H167" s="9">
+        <f>IF('الفواتير'!$E167="يدوية",'الفواتير'!$D167,"")</f>
+        <v/>
+      </c>
+      <c r="I167" s="14">
+        <f>IF($H167="","",'الفواتير'!$F167)</f>
+        <v/>
+      </c>
+      <c r="J167" s="14">
+        <f>IF($H167="","",SUMIF($B$7:$B$606,$H167,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K167" s="15">
+        <f>IF($H167="","",IF($H167=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H167)=0,"🟡 ما انزلت بنودها",IF(ROUND($I167-$J167,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I167-$J167,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="168" ht="21" customHeight="1">
       <c r="A168" s="9">
@@ -7216,6 +9853,22 @@
         <f>IF(C168="","",N(D168)*N(E168))</f>
         <v/>
       </c>
+      <c r="H168" s="9">
+        <f>IF('الفواتير'!$E168="يدوية",'الفواتير'!$D168,"")</f>
+        <v/>
+      </c>
+      <c r="I168" s="14">
+        <f>IF($H168="","",'الفواتير'!$F168)</f>
+        <v/>
+      </c>
+      <c r="J168" s="14">
+        <f>IF($H168="","",SUMIF($B$7:$B$606,$H168,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K168" s="15">
+        <f>IF($H168="","",IF($H168=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H168)=0,"🟡 ما انزلت بنودها",IF(ROUND($I168-$J168,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I168-$J168,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="169" ht="21" customHeight="1">
       <c r="A169" s="9">
@@ -7230,6 +9883,22 @@
         <f>IF(C169="","",N(D169)*N(E169))</f>
         <v/>
       </c>
+      <c r="H169" s="9">
+        <f>IF('الفواتير'!$E169="يدوية",'الفواتير'!$D169,"")</f>
+        <v/>
+      </c>
+      <c r="I169" s="14">
+        <f>IF($H169="","",'الفواتير'!$F169)</f>
+        <v/>
+      </c>
+      <c r="J169" s="14">
+        <f>IF($H169="","",SUMIF($B$7:$B$606,$H169,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K169" s="15">
+        <f>IF($H169="","",IF($H169=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H169)=0,"🟡 ما انزلت بنودها",IF(ROUND($I169-$J169,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I169-$J169,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="170" ht="21" customHeight="1">
       <c r="A170" s="9">
@@ -7244,6 +9913,22 @@
         <f>IF(C170="","",N(D170)*N(E170))</f>
         <v/>
       </c>
+      <c r="H170" s="9">
+        <f>IF('الفواتير'!$E170="يدوية",'الفواتير'!$D170,"")</f>
+        <v/>
+      </c>
+      <c r="I170" s="14">
+        <f>IF($H170="","",'الفواتير'!$F170)</f>
+        <v/>
+      </c>
+      <c r="J170" s="14">
+        <f>IF($H170="","",SUMIF($B$7:$B$606,$H170,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K170" s="15">
+        <f>IF($H170="","",IF($H170=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H170)=0,"🟡 ما انزلت بنودها",IF(ROUND($I170-$J170,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I170-$J170,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="171" ht="21" customHeight="1">
       <c r="A171" s="9">
@@ -7258,6 +9943,22 @@
         <f>IF(C171="","",N(D171)*N(E171))</f>
         <v/>
       </c>
+      <c r="H171" s="9">
+        <f>IF('الفواتير'!$E171="يدوية",'الفواتير'!$D171,"")</f>
+        <v/>
+      </c>
+      <c r="I171" s="14">
+        <f>IF($H171="","",'الفواتير'!$F171)</f>
+        <v/>
+      </c>
+      <c r="J171" s="14">
+        <f>IF($H171="","",SUMIF($B$7:$B$606,$H171,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K171" s="15">
+        <f>IF($H171="","",IF($H171=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H171)=0,"🟡 ما انزلت بنودها",IF(ROUND($I171-$J171,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I171-$J171,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="172" ht="21" customHeight="1">
       <c r="A172" s="9">
@@ -7272,6 +9973,22 @@
         <f>IF(C172="","",N(D172)*N(E172))</f>
         <v/>
       </c>
+      <c r="H172" s="9">
+        <f>IF('الفواتير'!$E172="يدوية",'الفواتير'!$D172,"")</f>
+        <v/>
+      </c>
+      <c r="I172" s="14">
+        <f>IF($H172="","",'الفواتير'!$F172)</f>
+        <v/>
+      </c>
+      <c r="J172" s="14">
+        <f>IF($H172="","",SUMIF($B$7:$B$606,$H172,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K172" s="15">
+        <f>IF($H172="","",IF($H172=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H172)=0,"🟡 ما انزلت بنودها",IF(ROUND($I172-$J172,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I172-$J172,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="173" ht="21" customHeight="1">
       <c r="A173" s="9">
@@ -7286,6 +10003,22 @@
         <f>IF(C173="","",N(D173)*N(E173))</f>
         <v/>
       </c>
+      <c r="H173" s="9">
+        <f>IF('الفواتير'!$E173="يدوية",'الفواتير'!$D173,"")</f>
+        <v/>
+      </c>
+      <c r="I173" s="14">
+        <f>IF($H173="","",'الفواتير'!$F173)</f>
+        <v/>
+      </c>
+      <c r="J173" s="14">
+        <f>IF($H173="","",SUMIF($B$7:$B$606,$H173,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K173" s="15">
+        <f>IF($H173="","",IF($H173=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H173)=0,"🟡 ما انزلت بنودها",IF(ROUND($I173-$J173,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I173-$J173,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="174" ht="21" customHeight="1">
       <c r="A174" s="9">
@@ -7300,6 +10033,22 @@
         <f>IF(C174="","",N(D174)*N(E174))</f>
         <v/>
       </c>
+      <c r="H174" s="9">
+        <f>IF('الفواتير'!$E174="يدوية",'الفواتير'!$D174,"")</f>
+        <v/>
+      </c>
+      <c r="I174" s="14">
+        <f>IF($H174="","",'الفواتير'!$F174)</f>
+        <v/>
+      </c>
+      <c r="J174" s="14">
+        <f>IF($H174="","",SUMIF($B$7:$B$606,$H174,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K174" s="15">
+        <f>IF($H174="","",IF($H174=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H174)=0,"🟡 ما انزلت بنودها",IF(ROUND($I174-$J174,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I174-$J174,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="175" ht="21" customHeight="1">
       <c r="A175" s="9">
@@ -7314,6 +10063,22 @@
         <f>IF(C175="","",N(D175)*N(E175))</f>
         <v/>
       </c>
+      <c r="H175" s="9">
+        <f>IF('الفواتير'!$E175="يدوية",'الفواتير'!$D175,"")</f>
+        <v/>
+      </c>
+      <c r="I175" s="14">
+        <f>IF($H175="","",'الفواتير'!$F175)</f>
+        <v/>
+      </c>
+      <c r="J175" s="14">
+        <f>IF($H175="","",SUMIF($B$7:$B$606,$H175,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K175" s="15">
+        <f>IF($H175="","",IF($H175=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H175)=0,"🟡 ما انزلت بنودها",IF(ROUND($I175-$J175,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I175-$J175,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="176" ht="21" customHeight="1">
       <c r="A176" s="9">
@@ -7328,6 +10093,22 @@
         <f>IF(C176="","",N(D176)*N(E176))</f>
         <v/>
       </c>
+      <c r="H176" s="9">
+        <f>IF('الفواتير'!$E176="يدوية",'الفواتير'!$D176,"")</f>
+        <v/>
+      </c>
+      <c r="I176" s="14">
+        <f>IF($H176="","",'الفواتير'!$F176)</f>
+        <v/>
+      </c>
+      <c r="J176" s="14">
+        <f>IF($H176="","",SUMIF($B$7:$B$606,$H176,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K176" s="15">
+        <f>IF($H176="","",IF($H176=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H176)=0,"🟡 ما انزلت بنودها",IF(ROUND($I176-$J176,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I176-$J176,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="177" ht="21" customHeight="1">
       <c r="A177" s="9">
@@ -7342,6 +10123,22 @@
         <f>IF(C177="","",N(D177)*N(E177))</f>
         <v/>
       </c>
+      <c r="H177" s="9">
+        <f>IF('الفواتير'!$E177="يدوية",'الفواتير'!$D177,"")</f>
+        <v/>
+      </c>
+      <c r="I177" s="14">
+        <f>IF($H177="","",'الفواتير'!$F177)</f>
+        <v/>
+      </c>
+      <c r="J177" s="14">
+        <f>IF($H177="","",SUMIF($B$7:$B$606,$H177,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K177" s="15">
+        <f>IF($H177="","",IF($H177=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H177)=0,"🟡 ما انزلت بنودها",IF(ROUND($I177-$J177,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I177-$J177,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="178" ht="21" customHeight="1">
       <c r="A178" s="9">
@@ -7356,6 +10153,22 @@
         <f>IF(C178="","",N(D178)*N(E178))</f>
         <v/>
       </c>
+      <c r="H178" s="9">
+        <f>IF('الفواتير'!$E178="يدوية",'الفواتير'!$D178,"")</f>
+        <v/>
+      </c>
+      <c r="I178" s="14">
+        <f>IF($H178="","",'الفواتير'!$F178)</f>
+        <v/>
+      </c>
+      <c r="J178" s="14">
+        <f>IF($H178="","",SUMIF($B$7:$B$606,$H178,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K178" s="15">
+        <f>IF($H178="","",IF($H178=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H178)=0,"🟡 ما انزلت بنودها",IF(ROUND($I178-$J178,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I178-$J178,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="179" ht="21" customHeight="1">
       <c r="A179" s="9">
@@ -7370,6 +10183,22 @@
         <f>IF(C179="","",N(D179)*N(E179))</f>
         <v/>
       </c>
+      <c r="H179" s="9">
+        <f>IF('الفواتير'!$E179="يدوية",'الفواتير'!$D179,"")</f>
+        <v/>
+      </c>
+      <c r="I179" s="14">
+        <f>IF($H179="","",'الفواتير'!$F179)</f>
+        <v/>
+      </c>
+      <c r="J179" s="14">
+        <f>IF($H179="","",SUMIF($B$7:$B$606,$H179,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K179" s="15">
+        <f>IF($H179="","",IF($H179=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H179)=0,"🟡 ما انزلت بنودها",IF(ROUND($I179-$J179,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I179-$J179,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="180" ht="21" customHeight="1">
       <c r="A180" s="9">
@@ -7384,6 +10213,22 @@
         <f>IF(C180="","",N(D180)*N(E180))</f>
         <v/>
       </c>
+      <c r="H180" s="9">
+        <f>IF('الفواتير'!$E180="يدوية",'الفواتير'!$D180,"")</f>
+        <v/>
+      </c>
+      <c r="I180" s="14">
+        <f>IF($H180="","",'الفواتير'!$F180)</f>
+        <v/>
+      </c>
+      <c r="J180" s="14">
+        <f>IF($H180="","",SUMIF($B$7:$B$606,$H180,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K180" s="15">
+        <f>IF($H180="","",IF($H180=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H180)=0,"🟡 ما انزلت بنودها",IF(ROUND($I180-$J180,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I180-$J180,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="181" ht="21" customHeight="1">
       <c r="A181" s="9">
@@ -7398,6 +10243,22 @@
         <f>IF(C181="","",N(D181)*N(E181))</f>
         <v/>
       </c>
+      <c r="H181" s="9">
+        <f>IF('الفواتير'!$E181="يدوية",'الفواتير'!$D181,"")</f>
+        <v/>
+      </c>
+      <c r="I181" s="14">
+        <f>IF($H181="","",'الفواتير'!$F181)</f>
+        <v/>
+      </c>
+      <c r="J181" s="14">
+        <f>IF($H181="","",SUMIF($B$7:$B$606,$H181,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K181" s="15">
+        <f>IF($H181="","",IF($H181=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H181)=0,"🟡 ما انزلت بنودها",IF(ROUND($I181-$J181,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I181-$J181,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="182" ht="21" customHeight="1">
       <c r="A182" s="9">
@@ -7412,6 +10273,22 @@
         <f>IF(C182="","",N(D182)*N(E182))</f>
         <v/>
       </c>
+      <c r="H182" s="9">
+        <f>IF('الفواتير'!$E182="يدوية",'الفواتير'!$D182,"")</f>
+        <v/>
+      </c>
+      <c r="I182" s="14">
+        <f>IF($H182="","",'الفواتير'!$F182)</f>
+        <v/>
+      </c>
+      <c r="J182" s="14">
+        <f>IF($H182="","",SUMIF($B$7:$B$606,$H182,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K182" s="15">
+        <f>IF($H182="","",IF($H182=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H182)=0,"🟡 ما انزلت بنودها",IF(ROUND($I182-$J182,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I182-$J182,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="183" ht="21" customHeight="1">
       <c r="A183" s="9">
@@ -7426,6 +10303,22 @@
         <f>IF(C183="","",N(D183)*N(E183))</f>
         <v/>
       </c>
+      <c r="H183" s="9">
+        <f>IF('الفواتير'!$E183="يدوية",'الفواتير'!$D183,"")</f>
+        <v/>
+      </c>
+      <c r="I183" s="14">
+        <f>IF($H183="","",'الفواتير'!$F183)</f>
+        <v/>
+      </c>
+      <c r="J183" s="14">
+        <f>IF($H183="","",SUMIF($B$7:$B$606,$H183,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K183" s="15">
+        <f>IF($H183="","",IF($H183=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H183)=0,"🟡 ما انزلت بنودها",IF(ROUND($I183-$J183,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I183-$J183,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="184" ht="21" customHeight="1">
       <c r="A184" s="9">
@@ -7440,6 +10333,22 @@
         <f>IF(C184="","",N(D184)*N(E184))</f>
         <v/>
       </c>
+      <c r="H184" s="9">
+        <f>IF('الفواتير'!$E184="يدوية",'الفواتير'!$D184,"")</f>
+        <v/>
+      </c>
+      <c r="I184" s="14">
+        <f>IF($H184="","",'الفواتير'!$F184)</f>
+        <v/>
+      </c>
+      <c r="J184" s="14">
+        <f>IF($H184="","",SUMIF($B$7:$B$606,$H184,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K184" s="15">
+        <f>IF($H184="","",IF($H184=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H184)=0,"🟡 ما انزلت بنودها",IF(ROUND($I184-$J184,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I184-$J184,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="185" ht="21" customHeight="1">
       <c r="A185" s="9">
@@ -7454,6 +10363,22 @@
         <f>IF(C185="","",N(D185)*N(E185))</f>
         <v/>
       </c>
+      <c r="H185" s="9">
+        <f>IF('الفواتير'!$E185="يدوية",'الفواتير'!$D185,"")</f>
+        <v/>
+      </c>
+      <c r="I185" s="14">
+        <f>IF($H185="","",'الفواتير'!$F185)</f>
+        <v/>
+      </c>
+      <c r="J185" s="14">
+        <f>IF($H185="","",SUMIF($B$7:$B$606,$H185,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K185" s="15">
+        <f>IF($H185="","",IF($H185=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H185)=0,"🟡 ما انزلت بنودها",IF(ROUND($I185-$J185,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I185-$J185,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="186" ht="21" customHeight="1">
       <c r="A186" s="9">
@@ -7468,6 +10393,22 @@
         <f>IF(C186="","",N(D186)*N(E186))</f>
         <v/>
       </c>
+      <c r="H186" s="9">
+        <f>IF('الفواتير'!$E186="يدوية",'الفواتير'!$D186,"")</f>
+        <v/>
+      </c>
+      <c r="I186" s="14">
+        <f>IF($H186="","",'الفواتير'!$F186)</f>
+        <v/>
+      </c>
+      <c r="J186" s="14">
+        <f>IF($H186="","",SUMIF($B$7:$B$606,$H186,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K186" s="15">
+        <f>IF($H186="","",IF($H186=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H186)=0,"🟡 ما انزلت بنودها",IF(ROUND($I186-$J186,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I186-$J186,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="187" ht="21" customHeight="1">
       <c r="A187" s="9">
@@ -7482,6 +10423,22 @@
         <f>IF(C187="","",N(D187)*N(E187))</f>
         <v/>
       </c>
+      <c r="H187" s="9">
+        <f>IF('الفواتير'!$E187="يدوية",'الفواتير'!$D187,"")</f>
+        <v/>
+      </c>
+      <c r="I187" s="14">
+        <f>IF($H187="","",'الفواتير'!$F187)</f>
+        <v/>
+      </c>
+      <c r="J187" s="14">
+        <f>IF($H187="","",SUMIF($B$7:$B$606,$H187,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K187" s="15">
+        <f>IF($H187="","",IF($H187=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H187)=0,"🟡 ما انزلت بنودها",IF(ROUND($I187-$J187,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I187-$J187,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="188" ht="21" customHeight="1">
       <c r="A188" s="9">
@@ -7496,6 +10453,22 @@
         <f>IF(C188="","",N(D188)*N(E188))</f>
         <v/>
       </c>
+      <c r="H188" s="9">
+        <f>IF('الفواتير'!$E188="يدوية",'الفواتير'!$D188,"")</f>
+        <v/>
+      </c>
+      <c r="I188" s="14">
+        <f>IF($H188="","",'الفواتير'!$F188)</f>
+        <v/>
+      </c>
+      <c r="J188" s="14">
+        <f>IF($H188="","",SUMIF($B$7:$B$606,$H188,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K188" s="15">
+        <f>IF($H188="","",IF($H188=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H188)=0,"🟡 ما انزلت بنودها",IF(ROUND($I188-$J188,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I188-$J188,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="189" ht="21" customHeight="1">
       <c r="A189" s="9">
@@ -7510,6 +10483,22 @@
         <f>IF(C189="","",N(D189)*N(E189))</f>
         <v/>
       </c>
+      <c r="H189" s="9">
+        <f>IF('الفواتير'!$E189="يدوية",'الفواتير'!$D189,"")</f>
+        <v/>
+      </c>
+      <c r="I189" s="14">
+        <f>IF($H189="","",'الفواتير'!$F189)</f>
+        <v/>
+      </c>
+      <c r="J189" s="14">
+        <f>IF($H189="","",SUMIF($B$7:$B$606,$H189,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K189" s="15">
+        <f>IF($H189="","",IF($H189=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H189)=0,"🟡 ما انزلت بنودها",IF(ROUND($I189-$J189,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I189-$J189,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="190" ht="21" customHeight="1">
       <c r="A190" s="9">
@@ -7524,6 +10513,22 @@
         <f>IF(C190="","",N(D190)*N(E190))</f>
         <v/>
       </c>
+      <c r="H190" s="9">
+        <f>IF('الفواتير'!$E190="يدوية",'الفواتير'!$D190,"")</f>
+        <v/>
+      </c>
+      <c r="I190" s="14">
+        <f>IF($H190="","",'الفواتير'!$F190)</f>
+        <v/>
+      </c>
+      <c r="J190" s="14">
+        <f>IF($H190="","",SUMIF($B$7:$B$606,$H190,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K190" s="15">
+        <f>IF($H190="","",IF($H190=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H190)=0,"🟡 ما انزلت بنودها",IF(ROUND($I190-$J190,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I190-$J190,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="191" ht="21" customHeight="1">
       <c r="A191" s="9">
@@ -7538,6 +10543,22 @@
         <f>IF(C191="","",N(D191)*N(E191))</f>
         <v/>
       </c>
+      <c r="H191" s="9">
+        <f>IF('الفواتير'!$E191="يدوية",'الفواتير'!$D191,"")</f>
+        <v/>
+      </c>
+      <c r="I191" s="14">
+        <f>IF($H191="","",'الفواتير'!$F191)</f>
+        <v/>
+      </c>
+      <c r="J191" s="14">
+        <f>IF($H191="","",SUMIF($B$7:$B$606,$H191,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K191" s="15">
+        <f>IF($H191="","",IF($H191=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H191)=0,"🟡 ما انزلت بنودها",IF(ROUND($I191-$J191,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I191-$J191,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="192" ht="21" customHeight="1">
       <c r="A192" s="9">
@@ -7552,6 +10573,22 @@
         <f>IF(C192="","",N(D192)*N(E192))</f>
         <v/>
       </c>
+      <c r="H192" s="9">
+        <f>IF('الفواتير'!$E192="يدوية",'الفواتير'!$D192,"")</f>
+        <v/>
+      </c>
+      <c r="I192" s="14">
+        <f>IF($H192="","",'الفواتير'!$F192)</f>
+        <v/>
+      </c>
+      <c r="J192" s="14">
+        <f>IF($H192="","",SUMIF($B$7:$B$606,$H192,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K192" s="15">
+        <f>IF($H192="","",IF($H192=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H192)=0,"🟡 ما انزلت بنودها",IF(ROUND($I192-$J192,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I192-$J192,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="193" ht="21" customHeight="1">
       <c r="A193" s="9">
@@ -7566,6 +10603,22 @@
         <f>IF(C193="","",N(D193)*N(E193))</f>
         <v/>
       </c>
+      <c r="H193" s="9">
+        <f>IF('الفواتير'!$E193="يدوية",'الفواتير'!$D193,"")</f>
+        <v/>
+      </c>
+      <c r="I193" s="14">
+        <f>IF($H193="","",'الفواتير'!$F193)</f>
+        <v/>
+      </c>
+      <c r="J193" s="14">
+        <f>IF($H193="","",SUMIF($B$7:$B$606,$H193,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K193" s="15">
+        <f>IF($H193="","",IF($H193=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H193)=0,"🟡 ما انزلت بنودها",IF(ROUND($I193-$J193,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I193-$J193,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="194" ht="21" customHeight="1">
       <c r="A194" s="9">
@@ -7580,6 +10633,22 @@
         <f>IF(C194="","",N(D194)*N(E194))</f>
         <v/>
       </c>
+      <c r="H194" s="9">
+        <f>IF('الفواتير'!$E194="يدوية",'الفواتير'!$D194,"")</f>
+        <v/>
+      </c>
+      <c r="I194" s="14">
+        <f>IF($H194="","",'الفواتير'!$F194)</f>
+        <v/>
+      </c>
+      <c r="J194" s="14">
+        <f>IF($H194="","",SUMIF($B$7:$B$606,$H194,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K194" s="15">
+        <f>IF($H194="","",IF($H194=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H194)=0,"🟡 ما انزلت بنودها",IF(ROUND($I194-$J194,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I194-$J194,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="195" ht="21" customHeight="1">
       <c r="A195" s="9">
@@ -7594,6 +10663,22 @@
         <f>IF(C195="","",N(D195)*N(E195))</f>
         <v/>
       </c>
+      <c r="H195" s="9">
+        <f>IF('الفواتير'!$E195="يدوية",'الفواتير'!$D195,"")</f>
+        <v/>
+      </c>
+      <c r="I195" s="14">
+        <f>IF($H195="","",'الفواتير'!$F195)</f>
+        <v/>
+      </c>
+      <c r="J195" s="14">
+        <f>IF($H195="","",SUMIF($B$7:$B$606,$H195,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K195" s="15">
+        <f>IF($H195="","",IF($H195=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H195)=0,"🟡 ما انزلت بنودها",IF(ROUND($I195-$J195,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I195-$J195,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="196" ht="21" customHeight="1">
       <c r="A196" s="9">
@@ -7608,6 +10693,22 @@
         <f>IF(C196="","",N(D196)*N(E196))</f>
         <v/>
       </c>
+      <c r="H196" s="9">
+        <f>IF('الفواتير'!$E196="يدوية",'الفواتير'!$D196,"")</f>
+        <v/>
+      </c>
+      <c r="I196" s="14">
+        <f>IF($H196="","",'الفواتير'!$F196)</f>
+        <v/>
+      </c>
+      <c r="J196" s="14">
+        <f>IF($H196="","",SUMIF($B$7:$B$606,$H196,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K196" s="15">
+        <f>IF($H196="","",IF($H196=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H196)=0,"🟡 ما انزلت بنودها",IF(ROUND($I196-$J196,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I196-$J196,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="197" ht="21" customHeight="1">
       <c r="A197" s="9">
@@ -7622,6 +10723,22 @@
         <f>IF(C197="","",N(D197)*N(E197))</f>
         <v/>
       </c>
+      <c r="H197" s="9">
+        <f>IF('الفواتير'!$E197="يدوية",'الفواتير'!$D197,"")</f>
+        <v/>
+      </c>
+      <c r="I197" s="14">
+        <f>IF($H197="","",'الفواتير'!$F197)</f>
+        <v/>
+      </c>
+      <c r="J197" s="14">
+        <f>IF($H197="","",SUMIF($B$7:$B$606,$H197,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K197" s="15">
+        <f>IF($H197="","",IF($H197=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H197)=0,"🟡 ما انزلت بنودها",IF(ROUND($I197-$J197,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I197-$J197,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="198" ht="21" customHeight="1">
       <c r="A198" s="9">
@@ -7636,6 +10753,22 @@
         <f>IF(C198="","",N(D198)*N(E198))</f>
         <v/>
       </c>
+      <c r="H198" s="9">
+        <f>IF('الفواتير'!$E198="يدوية",'الفواتير'!$D198,"")</f>
+        <v/>
+      </c>
+      <c r="I198" s="14">
+        <f>IF($H198="","",'الفواتير'!$F198)</f>
+        <v/>
+      </c>
+      <c r="J198" s="14">
+        <f>IF($H198="","",SUMIF($B$7:$B$606,$H198,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K198" s="15">
+        <f>IF($H198="","",IF($H198=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H198)=0,"🟡 ما انزلت بنودها",IF(ROUND($I198-$J198,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I198-$J198,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="199" ht="21" customHeight="1">
       <c r="A199" s="9">
@@ -7650,6 +10783,22 @@
         <f>IF(C199="","",N(D199)*N(E199))</f>
         <v/>
       </c>
+      <c r="H199" s="9">
+        <f>IF('الفواتير'!$E199="يدوية",'الفواتير'!$D199,"")</f>
+        <v/>
+      </c>
+      <c r="I199" s="14">
+        <f>IF($H199="","",'الفواتير'!$F199)</f>
+        <v/>
+      </c>
+      <c r="J199" s="14">
+        <f>IF($H199="","",SUMIF($B$7:$B$606,$H199,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K199" s="15">
+        <f>IF($H199="","",IF($H199=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H199)=0,"🟡 ما انزلت بنودها",IF(ROUND($I199-$J199,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I199-$J199,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="200" ht="21" customHeight="1">
       <c r="A200" s="9">
@@ -7664,6 +10813,22 @@
         <f>IF(C200="","",N(D200)*N(E200))</f>
         <v/>
       </c>
+      <c r="H200" s="9">
+        <f>IF('الفواتير'!$E200="يدوية",'الفواتير'!$D200,"")</f>
+        <v/>
+      </c>
+      <c r="I200" s="14">
+        <f>IF($H200="","",'الفواتير'!$F200)</f>
+        <v/>
+      </c>
+      <c r="J200" s="14">
+        <f>IF($H200="","",SUMIF($B$7:$B$606,$H200,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K200" s="15">
+        <f>IF($H200="","",IF($H200=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H200)=0,"🟡 ما انزلت بنودها",IF(ROUND($I200-$J200,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I200-$J200,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="201" ht="21" customHeight="1">
       <c r="A201" s="9">
@@ -7678,6 +10843,22 @@
         <f>IF(C201="","",N(D201)*N(E201))</f>
         <v/>
       </c>
+      <c r="H201" s="9">
+        <f>IF('الفواتير'!$E201="يدوية",'الفواتير'!$D201,"")</f>
+        <v/>
+      </c>
+      <c r="I201" s="14">
+        <f>IF($H201="","",'الفواتير'!$F201)</f>
+        <v/>
+      </c>
+      <c r="J201" s="14">
+        <f>IF($H201="","",SUMIF($B$7:$B$606,$H201,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K201" s="15">
+        <f>IF($H201="","",IF($H201=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H201)=0,"🟡 ما انزلت بنودها",IF(ROUND($I201-$J201,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I201-$J201,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="202" ht="21" customHeight="1">
       <c r="A202" s="9">
@@ -7692,6 +10873,22 @@
         <f>IF(C202="","",N(D202)*N(E202))</f>
         <v/>
       </c>
+      <c r="H202" s="9">
+        <f>IF('الفواتير'!$E202="يدوية",'الفواتير'!$D202,"")</f>
+        <v/>
+      </c>
+      <c r="I202" s="14">
+        <f>IF($H202="","",'الفواتير'!$F202)</f>
+        <v/>
+      </c>
+      <c r="J202" s="14">
+        <f>IF($H202="","",SUMIF($B$7:$B$606,$H202,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K202" s="15">
+        <f>IF($H202="","",IF($H202=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H202)=0,"🟡 ما انزلت بنودها",IF(ROUND($I202-$J202,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I202-$J202,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="203" ht="21" customHeight="1">
       <c r="A203" s="9">
@@ -7706,6 +10903,22 @@
         <f>IF(C203="","",N(D203)*N(E203))</f>
         <v/>
       </c>
+      <c r="H203" s="9">
+        <f>IF('الفواتير'!$E203="يدوية",'الفواتير'!$D203,"")</f>
+        <v/>
+      </c>
+      <c r="I203" s="14">
+        <f>IF($H203="","",'الفواتير'!$F203)</f>
+        <v/>
+      </c>
+      <c r="J203" s="14">
+        <f>IF($H203="","",SUMIF($B$7:$B$606,$H203,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K203" s="15">
+        <f>IF($H203="","",IF($H203=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H203)=0,"🟡 ما انزلت بنودها",IF(ROUND($I203-$J203,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I203-$J203,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="204" ht="21" customHeight="1">
       <c r="A204" s="9">
@@ -7720,6 +10933,22 @@
         <f>IF(C204="","",N(D204)*N(E204))</f>
         <v/>
       </c>
+      <c r="H204" s="9">
+        <f>IF('الفواتير'!$E204="يدوية",'الفواتير'!$D204,"")</f>
+        <v/>
+      </c>
+      <c r="I204" s="14">
+        <f>IF($H204="","",'الفواتير'!$F204)</f>
+        <v/>
+      </c>
+      <c r="J204" s="14">
+        <f>IF($H204="","",SUMIF($B$7:$B$606,$H204,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K204" s="15">
+        <f>IF($H204="","",IF($H204=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H204)=0,"🟡 ما انزلت بنودها",IF(ROUND($I204-$J204,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I204-$J204,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="205" ht="21" customHeight="1">
       <c r="A205" s="9">
@@ -7734,6 +10963,22 @@
         <f>IF(C205="","",N(D205)*N(E205))</f>
         <v/>
       </c>
+      <c r="H205" s="9">
+        <f>IF('الفواتير'!$E205="يدوية",'الفواتير'!$D205,"")</f>
+        <v/>
+      </c>
+      <c r="I205" s="14">
+        <f>IF($H205="","",'الفواتير'!$F205)</f>
+        <v/>
+      </c>
+      <c r="J205" s="14">
+        <f>IF($H205="","",SUMIF($B$7:$B$606,$H205,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K205" s="15">
+        <f>IF($H205="","",IF($H205=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H205)=0,"🟡 ما انزلت بنودها",IF(ROUND($I205-$J205,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I205-$J205,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="206" ht="21" customHeight="1">
       <c r="A206" s="9">
@@ -7748,6 +10993,22 @@
         <f>IF(C206="","",N(D206)*N(E206))</f>
         <v/>
       </c>
+      <c r="H206" s="9">
+        <f>IF('الفواتير'!$E206="يدوية",'الفواتير'!$D206,"")</f>
+        <v/>
+      </c>
+      <c r="I206" s="14">
+        <f>IF($H206="","",'الفواتير'!$F206)</f>
+        <v/>
+      </c>
+      <c r="J206" s="14">
+        <f>IF($H206="","",SUMIF($B$7:$B$606,$H206,$F$7:$F$606))</f>
+        <v/>
+      </c>
+      <c r="K206" s="15">
+        <f>IF($H206="","",IF($H206=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H206)=0,"🟡 ما انزلت بنودها",IF(ROUND($I206-$J206,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I206-$J206,"0.000")))))</f>
+        <v/>
+      </c>
     </row>
     <row r="207" ht="21" customHeight="1">
       <c r="A207" s="9">
@@ -13351,7 +16612,7 @@
     </row>
     <row r="607"/>
     <row r="608" ht="22" customHeight="1">
-      <c r="A608" s="20" t="inlineStr">
+      <c r="A608" s="21" t="inlineStr">
         <is>
           <t>رقم الفاتورة لازم يكون نفسه المكتوب بورقة «الفواتير» — وإلا بيطلع ⛔ بعمود #</t>
         </is>
@@ -13359,40 +16620,62 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="0" formatRows="1" sort="1"/>
-  <mergeCells count="4">
+  <mergeCells count="5">
+    <mergeCell ref="H4:K4"/>
+    <mergeCell ref="E4:F4"/>
     <mergeCell ref="B2:F2"/>
-    <mergeCell ref="E4:F4"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A608:F608"/>
   </mergeCells>
+  <conditionalFormatting sqref="K7:K206">
+    <cfRule type="expression" priority="1" dxfId="3">
+      <formula>LEFT($K7,1)="✅"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2" dxfId="2">
+      <formula>LEFT($K7,1)="⛔"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="3" dxfId="7">
+      <formula>LEFT($K7,1)="🟡"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H4">
+    <cfRule type="expression" priority="4" dxfId="0">
+      <formula>AND(COUNTIF($K$7:$K$206,"✅*")&gt;0,COUNTIF($K$7:$K$206,"✅*")=COUNTIF('الفواتير'!$E$7:$E$206,"يدوية"))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="E4">
-    <cfRule type="expression" priority="1" dxfId="0">
+    <cfRule type="expression" priority="5" dxfId="0">
       <formula>LEFT(E4,1)="✅"</formula>
     </cfRule>
-    <cfRule type="expression" priority="2" dxfId="1">
+    <cfRule type="expression" priority="6" dxfId="1">
       <formula>LEFT(E4,1)="⛔"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A7:F606">
-    <cfRule type="expression" priority="3" dxfId="5">
+    <cfRule type="expression" priority="7" dxfId="6">
       <formula>$A7="⛔"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B7:B606">
-    <cfRule type="expression" priority="4" dxfId="5">
+    <cfRule type="expression" priority="8" dxfId="6">
       <formula>AND($C7&lt;&gt;"",$B7="")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D7:D606">
-    <cfRule type="expression" priority="5" dxfId="5">
+    <cfRule type="expression" priority="9" dxfId="6">
       <formula>AND($C7&lt;&gt;"",$D7="")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E7:E606">
-    <cfRule type="expression" priority="6" dxfId="5">
+    <cfRule type="expression" priority="10" dxfId="6">
       <formula>AND($C7&lt;&gt;"",$E7="")</formula>
     </cfRule>
   </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="B7:B606" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>='الفواتير'!$D$7:$D$206</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
@@ -13404,7 +16687,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B24"/>
+  <dimension ref="A1:B29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -13419,248 +16702,304 @@
       </c>
     </row>
     <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="21" t="inlineStr">
+      <c r="A3" s="22" t="inlineStr">
         <is>
           <t>القاعدة الأساسية</t>
         </is>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="22" t="inlineStr">
+      <c r="A4" s="23" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B4" s="23" t="inlineStr">
+      <c r="B4" s="24" t="inlineStr">
         <is>
           <t>ملف واحد لكل شهر. بتفرّغ فيه فواتير شراء البضاعة يوم بيوم — مش آخر الشهر.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="22" t="inlineStr">
+      <c r="A5" s="23" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B5" s="23" t="inlineStr">
+      <c r="B5" s="24" t="inlineStr">
         <is>
           <t>اكتب الشهر مرة وحدة فوق بورقة «الفواتير» وبس. ورقة «البنود» بتاخده لحالها.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="21" t="inlineStr">
+      <c r="A6" s="22" t="inlineStr">
         <is>
           <t>ورقة «الفواتير» — سطر لكل فاتورة</t>
         </is>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="22" t="inlineStr">
+      <c r="A7" s="23" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B7" s="23" t="inlineStr">
+      <c r="B7" s="24" t="inlineStr">
         <is>
           <t>المورد: اكتب الاسم نفسه بالضبط كل مرة. «كتانة» و«سليم كتانة» بينحسبوا موردين اثنين.</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" s="22" t="inlineStr">
+    <row r="8" ht="45" customHeight="1">
+      <c r="A8" s="23" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B8" s="23" t="inlineStr">
+      <c r="B8" s="24" t="inlineStr">
+        <is>
+          <t>التاريخ: اكتبه أرقام ورا بعض بلا شرطات — 24092026 والخانة بتعرضه 24/09/2026 لحالها. إذا صار برتقالي يعني التاريخ غلط (يوم أكبر من 31 أو شهر أكبر من 12).</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" s="23" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B9" s="24" t="inlineStr">
         <is>
           <t>النوع: من القائمة — مطبوعة أو يدوية. هاي بتحدّد شو بعدها.</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="22" t="inlineStr">
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="23" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
-      <c r="B9" s="23" t="inlineStr">
+      <c r="B10" s="24" t="inlineStr">
         <is>
           <t>مطبوعة ← المورد + التاريخ + رقم الفاتورة + المجموع وبس. ما بدنا بنودها، بس ابعث صورتها مع الملف.</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="22" t="inlineStr">
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="23" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
-      <c r="B10" s="23" t="inlineStr">
+      <c r="B11" s="24" t="inlineStr">
         <is>
           <t>يدوية ← نفس الأربعة، وكمان بنودها بورقة «البنود». السبب: الخط اليدوي ما بينقرأ، والبنود لازم تنكتب عشان تنزل على النظام.</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="22" t="inlineStr">
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="23" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
-      <c r="B11" s="23" t="inlineStr">
+      <c r="B12" s="24" t="inlineStr">
         <is>
           <t>الخصم: إذا في خصم على الفاتورة كلها اكتبه، وإلا اتركه فاضي. الصافي بيتحسب لحاله (المجموع − الخصم).</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="22" t="inlineStr">
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="23" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
-      <c r="B12" s="23" t="inlineStr">
+      <c r="B13" s="24" t="inlineStr">
         <is>
           <t>رقم الفاتورة اللي بيصير برتقالي = مكرر بنفس الملف. غيّره، وإلا بنودها بتختلط.</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="24" customHeight="1">
-      <c r="A13" s="21" t="inlineStr">
+    <row r="14" ht="24" customHeight="1">
+      <c r="A14" s="22" t="inlineStr">
         <is>
           <t>ورقة «البنود» — للفواتير اليدوية فقط</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" s="22" t="inlineStr">
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" s="23" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
-      <c r="B14" s="23" t="inlineStr">
+      <c r="B15" s="24" t="inlineStr">
         <is>
           <t>كل بند بسطر: رقم الفاتورة + البند + الكمية + الإفرادي. الإجمالي بيتحسب لحاله.</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="22" t="inlineStr">
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="23" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
-      <c r="B15" s="23" t="inlineStr">
+      <c r="B16" s="24" t="inlineStr">
         <is>
           <t>رقم الفاتورة لازم يكون نفسه المكتوب بورقة «الفواتير». إذا طلع ⛔ مكان الرقم التسلسلي ← يعني الرقم مش موجود بورقة الفواتير.</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" s="22" t="inlineStr">
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" s="23" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
-      <c r="B16" s="23" t="inlineStr">
+      <c r="B17" s="24" t="inlineStr">
         <is>
           <t>اكتب البند زي ما هو مكتوب بالفاتورة. مش لازم يطابق الكتالوج — أنا بطابقه.</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="24" customHeight="1">
-      <c r="A17" s="21" t="inlineStr">
+    <row r="18" ht="24" customHeight="1">
+      <c r="A18" s="22" t="inlineStr">
+        <is>
+          <t>لوحة المتابعة — يمين ورقة «البنود»</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="30" customHeight="1">
+      <c r="A19" s="23" t="inlineStr">
+        <is>
+          <t>◆</t>
+        </is>
+      </c>
+      <c r="B19" s="24" t="inlineStr">
+        <is>
+          <t>أرقام الفواتير اليدوية بتطلع فيها لحالها — ما بتكتب إشي. جنب كل رقم: مجموع الفاتورة · مجموع بنودها اللي أدخلتها · وعمود «خلصت؟».</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="23" t="inlineStr">
+        <is>
+          <t>◆</t>
+        </is>
+      </c>
+      <c r="B20" s="24" t="inlineStr">
+        <is>
+          <t>🟡 ما انزلت بنودها = لسا ما بلّشت فيها · ⛔ فرق 0.500 = المجموعان مش متطابقين · ✅ خلصت = المجموعان تطابقا وخلصت هاي الفاتورة.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="23" t="inlineStr">
+        <is>
+          <t>◆</t>
+        </is>
+      </c>
+      <c r="B21" s="24" t="inlineStr">
+        <is>
+          <t>فوق اللوحة بيطلع «3 مكتملة من 5 فواتير يدوية» — لما يصير أخضر يعني كلهن خلصوا.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="24" customHeight="1">
+      <c r="A22" s="22" t="inlineStr">
         <is>
           <t>التدقيق — شغل الإكسل مش شغلك</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="22" t="inlineStr">
+    <row r="23" ht="30" customHeight="1">
+      <c r="A23" s="23" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
-      <c r="B18" s="23" t="inlineStr">
+      <c r="B23" s="24" t="inlineStr">
         <is>
           <t>عمود «الحالة» بيقارن مجموع البنود مع مجموع الفاتورة لحاله: ✅ البنود مطابقة يعني تمام · ⛔ فرق 0.500 يعني ناقص أو زايد 500 فلس.</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="22" t="inlineStr">
+    <row r="24" ht="30" customHeight="1">
+      <c r="A24" s="23" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
-      <c r="B19" s="23" t="inlineStr">
+      <c r="B24" s="24" t="inlineStr">
         <is>
           <t>العدّاد فوق ما بيصير أخضر إلا لما كل فاتورة تكون سليمة. لا تبعث الملف وهو أحمر.</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="24" customHeight="1">
-      <c r="A20" s="21" t="inlineStr">
+    <row r="25" ht="24" customHeight="1">
+      <c r="A25" s="22" t="inlineStr">
         <is>
           <t>الإرسال</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" s="22" t="inlineStr">
+    <row r="26" ht="15" customHeight="1">
+      <c r="A26" s="23" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
-      <c r="B21" s="23" t="inlineStr">
+      <c r="B26" s="24" t="inlineStr">
         <is>
           <t>كل يوم: ابعث الملف + صور الفواتير المطبوعة اللي دخّلتها اليوم.</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="30" customHeight="1">
-      <c r="A22" s="22" t="inlineStr">
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="23" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
-      <c r="B22" s="23" t="inlineStr">
+      <c r="B27" s="24" t="inlineStr">
         <is>
           <t>الفواتير بتنزل على أودو يوم بيوم — مش آخر الشهر. كل يوم بيمرّ بلا تنزيل = يوم بتشتغل فيه على أرقام مش صحيحة.</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="24" customHeight="1">
-      <c r="A23" s="21" t="inlineStr">
+    <row r="28" ht="24" customHeight="1">
+      <c r="A28" s="22" t="inlineStr">
         <is>
           <t>الفكرة باختصار</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="30" customHeight="1">
-      <c r="A24" s="22" t="inlineStr">
+    <row r="29" ht="30" customHeight="1">
+      <c r="A29" s="23" t="inlineStr">
         <is>
           <t>◆</t>
         </is>
       </c>
-      <c r="B24" s="23" t="inlineStr">
+      <c r="B29" s="24" t="inlineStr">
         <is>
           <t>المطبوعة إلها صورة بتغني عن كتابة بنودها. اليدوية ما إلها — فبنكتب بنودها مرة وحدة هون، وبتضل مقروءة للأبد.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A13:B13"/>
+  <mergeCells count="8">
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A14:B14"/>
     <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A22:B22"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" fitToWidth="1"/>

--- a/العون/نموذج_مشتريات_شهري.xlsx
+++ b/العون/نموذج_مشتريات_شهري.xlsx
@@ -12,6 +12,7 @@
     <sheet name="التعليمات" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
+    <definedName name="فواتير_مفتوحة">OFFSET('البنود'!$N$7,0,0,MAX(1,SUMPRODUCT(--('البنود'!$N$7:$N$206&lt;&gt;""))),1)</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'الفواتير'!$1:$6</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'الفواتير'!$A$1:$I$208</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'البنود'!$1:$6</definedName>
@@ -4890,7 +4891,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K608"/>
+  <dimension ref="A1:N608"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -4904,6 +4905,9 @@
     <col width="13" customWidth="1" min="9" max="9"/>
     <col width="13" customWidth="1" min="10" max="10"/>
     <col width="26" customWidth="1" min="11" max="11"/>
+    <col hidden="1" width="14" customWidth="1" min="12" max="12"/>
+    <col hidden="1" width="14" customWidth="1" min="13" max="13"/>
+    <col hidden="1" width="14" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -5009,6 +5013,16 @@
           <t>خلصت؟</t>
         </is>
       </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>ترتيب</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>المفتوحة</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="21" customHeight="1">
       <c r="A7" s="9">
@@ -5039,6 +5053,14 @@
         <f>IF($H7="","",IF($H7=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H7)=0,"🟡 ما انزلت بنودها",IF(ROUND($I7-$J7,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I7-$J7,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M7">
+        <f>IF(AND($H7&lt;&gt;"",$H7&lt;&gt;0,LEFT($K7,1)&lt;&gt;"✅"),COUNT($M$6:M6)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N7">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="8" ht="21" customHeight="1">
       <c r="A8" s="9">
@@ -5069,6 +5091,14 @@
         <f>IF($H8="","",IF($H8=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H8)=0,"🟡 ما انزلت بنودها",IF(ROUND($I8-$J8,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I8-$J8,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M8">
+        <f>IF(AND($H8&lt;&gt;"",$H8&lt;&gt;0,LEFT($K8,1)&lt;&gt;"✅"),COUNT($M$6:M7)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N8">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="9" ht="21" customHeight="1">
       <c r="A9" s="9">
@@ -5099,6 +5129,14 @@
         <f>IF($H9="","",IF($H9=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H9)=0,"🟡 ما انزلت بنودها",IF(ROUND($I9-$J9,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I9-$J9,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M9">
+        <f>IF(AND($H9&lt;&gt;"",$H9&lt;&gt;0,LEFT($K9,1)&lt;&gt;"✅"),COUNT($M$6:M8)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N9">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="10" ht="21" customHeight="1">
       <c r="A10" s="9">
@@ -5129,6 +5167,14 @@
         <f>IF($H10="","",IF($H10=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H10)=0,"🟡 ما انزلت بنودها",IF(ROUND($I10-$J10,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I10-$J10,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M10">
+        <f>IF(AND($H10&lt;&gt;"",$H10&lt;&gt;0,LEFT($K10,1)&lt;&gt;"✅"),COUNT($M$6:M9)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N10">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="11" ht="21" customHeight="1">
       <c r="A11" s="9">
@@ -5159,6 +5205,14 @@
         <f>IF($H11="","",IF($H11=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H11)=0,"🟡 ما انزلت بنودها",IF(ROUND($I11-$J11,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I11-$J11,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M11">
+        <f>IF(AND($H11&lt;&gt;"",$H11&lt;&gt;0,LEFT($K11,1)&lt;&gt;"✅"),COUNT($M$6:M10)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N11">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="12" ht="21" customHeight="1">
       <c r="A12" s="9">
@@ -5189,6 +5243,14 @@
         <f>IF($H12="","",IF($H12=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H12)=0,"🟡 ما انزلت بنودها",IF(ROUND($I12-$J12,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I12-$J12,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M12">
+        <f>IF(AND($H12&lt;&gt;"",$H12&lt;&gt;0,LEFT($K12,1)&lt;&gt;"✅"),COUNT($M$6:M11)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N12">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="13" ht="21" customHeight="1">
       <c r="A13" s="9">
@@ -5219,6 +5281,14 @@
         <f>IF($H13="","",IF($H13=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H13)=0,"🟡 ما انزلت بنودها",IF(ROUND($I13-$J13,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I13-$J13,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M13">
+        <f>IF(AND($H13&lt;&gt;"",$H13&lt;&gt;0,LEFT($K13,1)&lt;&gt;"✅"),COUNT($M$6:M12)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N13">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="14" ht="21" customHeight="1">
       <c r="A14" s="9">
@@ -5249,6 +5319,14 @@
         <f>IF($H14="","",IF($H14=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H14)=0,"🟡 ما انزلت بنودها",IF(ROUND($I14-$J14,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I14-$J14,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M14">
+        <f>IF(AND($H14&lt;&gt;"",$H14&lt;&gt;0,LEFT($K14,1)&lt;&gt;"✅"),COUNT($M$6:M13)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N14">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="15" ht="21" customHeight="1">
       <c r="A15" s="9">
@@ -5279,6 +5357,14 @@
         <f>IF($H15="","",IF($H15=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H15)=0,"🟡 ما انزلت بنودها",IF(ROUND($I15-$J15,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I15-$J15,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M15">
+        <f>IF(AND($H15&lt;&gt;"",$H15&lt;&gt;0,LEFT($K15,1)&lt;&gt;"✅"),COUNT($M$6:M14)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N15">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="16" ht="21" customHeight="1">
       <c r="A16" s="9">
@@ -5309,6 +5395,14 @@
         <f>IF($H16="","",IF($H16=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H16)=0,"🟡 ما انزلت بنودها",IF(ROUND($I16-$J16,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I16-$J16,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M16">
+        <f>IF(AND($H16&lt;&gt;"",$H16&lt;&gt;0,LEFT($K16,1)&lt;&gt;"✅"),COUNT($M$6:M15)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N16">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="17" ht="21" customHeight="1">
       <c r="A17" s="9">
@@ -5339,6 +5433,14 @@
         <f>IF($H17="","",IF($H17=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H17)=0,"🟡 ما انزلت بنودها",IF(ROUND($I17-$J17,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I17-$J17,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M17">
+        <f>IF(AND($H17&lt;&gt;"",$H17&lt;&gt;0,LEFT($K17,1)&lt;&gt;"✅"),COUNT($M$6:M16)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N17">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="18" ht="21" customHeight="1">
       <c r="A18" s="9">
@@ -5369,6 +5471,14 @@
         <f>IF($H18="","",IF($H18=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H18)=0,"🟡 ما انزلت بنودها",IF(ROUND($I18-$J18,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I18-$J18,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M18">
+        <f>IF(AND($H18&lt;&gt;"",$H18&lt;&gt;0,LEFT($K18,1)&lt;&gt;"✅"),COUNT($M$6:M17)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N18">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="19" ht="21" customHeight="1">
       <c r="A19" s="9">
@@ -5399,6 +5509,14 @@
         <f>IF($H19="","",IF($H19=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H19)=0,"🟡 ما انزلت بنودها",IF(ROUND($I19-$J19,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I19-$J19,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M19">
+        <f>IF(AND($H19&lt;&gt;"",$H19&lt;&gt;0,LEFT($K19,1)&lt;&gt;"✅"),COUNT($M$6:M18)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N19">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="20" ht="21" customHeight="1">
       <c r="A20" s="9">
@@ -5429,6 +5547,14 @@
         <f>IF($H20="","",IF($H20=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H20)=0,"🟡 ما انزلت بنودها",IF(ROUND($I20-$J20,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I20-$J20,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M20">
+        <f>IF(AND($H20&lt;&gt;"",$H20&lt;&gt;0,LEFT($K20,1)&lt;&gt;"✅"),COUNT($M$6:M19)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N20">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="21" ht="21" customHeight="1">
       <c r="A21" s="9">
@@ -5459,6 +5585,14 @@
         <f>IF($H21="","",IF($H21=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H21)=0,"🟡 ما انزلت بنودها",IF(ROUND($I21-$J21,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I21-$J21,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M21">
+        <f>IF(AND($H21&lt;&gt;"",$H21&lt;&gt;0,LEFT($K21,1)&lt;&gt;"✅"),COUNT($M$6:M20)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N21">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="22" ht="21" customHeight="1">
       <c r="A22" s="9">
@@ -5489,6 +5623,14 @@
         <f>IF($H22="","",IF($H22=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H22)=0,"🟡 ما انزلت بنودها",IF(ROUND($I22-$J22,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I22-$J22,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M22">
+        <f>IF(AND($H22&lt;&gt;"",$H22&lt;&gt;0,LEFT($K22,1)&lt;&gt;"✅"),COUNT($M$6:M21)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N22">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="23" ht="21" customHeight="1">
       <c r="A23" s="9">
@@ -5519,6 +5661,14 @@
         <f>IF($H23="","",IF($H23=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H23)=0,"🟡 ما انزلت بنودها",IF(ROUND($I23-$J23,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I23-$J23,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M23">
+        <f>IF(AND($H23&lt;&gt;"",$H23&lt;&gt;0,LEFT($K23,1)&lt;&gt;"✅"),COUNT($M$6:M22)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N23">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="24" ht="21" customHeight="1">
       <c r="A24" s="9">
@@ -5549,6 +5699,14 @@
         <f>IF($H24="","",IF($H24=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H24)=0,"🟡 ما انزلت بنودها",IF(ROUND($I24-$J24,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I24-$J24,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M24">
+        <f>IF(AND($H24&lt;&gt;"",$H24&lt;&gt;0,LEFT($K24,1)&lt;&gt;"✅"),COUNT($M$6:M23)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N24">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="25" ht="21" customHeight="1">
       <c r="A25" s="9">
@@ -5579,6 +5737,14 @@
         <f>IF($H25="","",IF($H25=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H25)=0,"🟡 ما انزلت بنودها",IF(ROUND($I25-$J25,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I25-$J25,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M25">
+        <f>IF(AND($H25&lt;&gt;"",$H25&lt;&gt;0,LEFT($K25,1)&lt;&gt;"✅"),COUNT($M$6:M24)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N25">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="26" ht="21" customHeight="1">
       <c r="A26" s="9">
@@ -5609,6 +5775,14 @@
         <f>IF($H26="","",IF($H26=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H26)=0,"🟡 ما انزلت بنودها",IF(ROUND($I26-$J26,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I26-$J26,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M26">
+        <f>IF(AND($H26&lt;&gt;"",$H26&lt;&gt;0,LEFT($K26,1)&lt;&gt;"✅"),COUNT($M$6:M25)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N26">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="27" ht="21" customHeight="1">
       <c r="A27" s="9">
@@ -5639,6 +5813,14 @@
         <f>IF($H27="","",IF($H27=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H27)=0,"🟡 ما انزلت بنودها",IF(ROUND($I27-$J27,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I27-$J27,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M27">
+        <f>IF(AND($H27&lt;&gt;"",$H27&lt;&gt;0,LEFT($K27,1)&lt;&gt;"✅"),COUNT($M$6:M26)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N27">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="28" ht="21" customHeight="1">
       <c r="A28" s="9">
@@ -5669,6 +5851,14 @@
         <f>IF($H28="","",IF($H28=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H28)=0,"🟡 ما انزلت بنودها",IF(ROUND($I28-$J28,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I28-$J28,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M28">
+        <f>IF(AND($H28&lt;&gt;"",$H28&lt;&gt;0,LEFT($K28,1)&lt;&gt;"✅"),COUNT($M$6:M27)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N28">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="29" ht="21" customHeight="1">
       <c r="A29" s="9">
@@ -5699,6 +5889,14 @@
         <f>IF($H29="","",IF($H29=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H29)=0,"🟡 ما انزلت بنودها",IF(ROUND($I29-$J29,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I29-$J29,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M29">
+        <f>IF(AND($H29&lt;&gt;"",$H29&lt;&gt;0,LEFT($K29,1)&lt;&gt;"✅"),COUNT($M$6:M28)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N29">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="30" ht="21" customHeight="1">
       <c r="A30" s="9">
@@ -5729,6 +5927,14 @@
         <f>IF($H30="","",IF($H30=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H30)=0,"🟡 ما انزلت بنودها",IF(ROUND($I30-$J30,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I30-$J30,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M30">
+        <f>IF(AND($H30&lt;&gt;"",$H30&lt;&gt;0,LEFT($K30,1)&lt;&gt;"✅"),COUNT($M$6:M29)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N30">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="31" ht="21" customHeight="1">
       <c r="A31" s="9">
@@ -5759,6 +5965,14 @@
         <f>IF($H31="","",IF($H31=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H31)=0,"🟡 ما انزلت بنودها",IF(ROUND($I31-$J31,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I31-$J31,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M31">
+        <f>IF(AND($H31&lt;&gt;"",$H31&lt;&gt;0,LEFT($K31,1)&lt;&gt;"✅"),COUNT($M$6:M30)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N31">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="32" ht="21" customHeight="1">
       <c r="A32" s="9">
@@ -5789,6 +6003,14 @@
         <f>IF($H32="","",IF($H32=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H32)=0,"🟡 ما انزلت بنودها",IF(ROUND($I32-$J32,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I32-$J32,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M32">
+        <f>IF(AND($H32&lt;&gt;"",$H32&lt;&gt;0,LEFT($K32,1)&lt;&gt;"✅"),COUNT($M$6:M31)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N32">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="33" ht="21" customHeight="1">
       <c r="A33" s="9">
@@ -5819,6 +6041,14 @@
         <f>IF($H33="","",IF($H33=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H33)=0,"🟡 ما انزلت بنودها",IF(ROUND($I33-$J33,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I33-$J33,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M33">
+        <f>IF(AND($H33&lt;&gt;"",$H33&lt;&gt;0,LEFT($K33,1)&lt;&gt;"✅"),COUNT($M$6:M32)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N33">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="34" ht="21" customHeight="1">
       <c r="A34" s="9">
@@ -5849,6 +6079,14 @@
         <f>IF($H34="","",IF($H34=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H34)=0,"🟡 ما انزلت بنودها",IF(ROUND($I34-$J34,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I34-$J34,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M34">
+        <f>IF(AND($H34&lt;&gt;"",$H34&lt;&gt;0,LEFT($K34,1)&lt;&gt;"✅"),COUNT($M$6:M33)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N34">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="35" ht="21" customHeight="1">
       <c r="A35" s="9">
@@ -5879,6 +6117,14 @@
         <f>IF($H35="","",IF($H35=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H35)=0,"🟡 ما انزلت بنودها",IF(ROUND($I35-$J35,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I35-$J35,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M35">
+        <f>IF(AND($H35&lt;&gt;"",$H35&lt;&gt;0,LEFT($K35,1)&lt;&gt;"✅"),COUNT($M$6:M34)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N35">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="36" ht="21" customHeight="1">
       <c r="A36" s="9">
@@ -5909,6 +6155,14 @@
         <f>IF($H36="","",IF($H36=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H36)=0,"🟡 ما انزلت بنودها",IF(ROUND($I36-$J36,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I36-$J36,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M36">
+        <f>IF(AND($H36&lt;&gt;"",$H36&lt;&gt;0,LEFT($K36,1)&lt;&gt;"✅"),COUNT($M$6:M35)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N36">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="37" ht="21" customHeight="1">
       <c r="A37" s="9">
@@ -5939,6 +6193,14 @@
         <f>IF($H37="","",IF($H37=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H37)=0,"🟡 ما انزلت بنودها",IF(ROUND($I37-$J37,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I37-$J37,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M37">
+        <f>IF(AND($H37&lt;&gt;"",$H37&lt;&gt;0,LEFT($K37,1)&lt;&gt;"✅"),COUNT($M$6:M36)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N37">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="38" ht="21" customHeight="1">
       <c r="A38" s="9">
@@ -5969,6 +6231,14 @@
         <f>IF($H38="","",IF($H38=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H38)=0,"🟡 ما انزلت بنودها",IF(ROUND($I38-$J38,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I38-$J38,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M38">
+        <f>IF(AND($H38&lt;&gt;"",$H38&lt;&gt;0,LEFT($K38,1)&lt;&gt;"✅"),COUNT($M$6:M37)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N38">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="39" ht="21" customHeight="1">
       <c r="A39" s="9">
@@ -5999,6 +6269,14 @@
         <f>IF($H39="","",IF($H39=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H39)=0,"🟡 ما انزلت بنودها",IF(ROUND($I39-$J39,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I39-$J39,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M39">
+        <f>IF(AND($H39&lt;&gt;"",$H39&lt;&gt;0,LEFT($K39,1)&lt;&gt;"✅"),COUNT($M$6:M38)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N39">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="40" ht="21" customHeight="1">
       <c r="A40" s="9">
@@ -6029,6 +6307,14 @@
         <f>IF($H40="","",IF($H40=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H40)=0,"🟡 ما انزلت بنودها",IF(ROUND($I40-$J40,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I40-$J40,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M40">
+        <f>IF(AND($H40&lt;&gt;"",$H40&lt;&gt;0,LEFT($K40,1)&lt;&gt;"✅"),COUNT($M$6:M39)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N40">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="41" ht="21" customHeight="1">
       <c r="A41" s="9">
@@ -6059,6 +6345,14 @@
         <f>IF($H41="","",IF($H41=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H41)=0,"🟡 ما انزلت بنودها",IF(ROUND($I41-$J41,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I41-$J41,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M41">
+        <f>IF(AND($H41&lt;&gt;"",$H41&lt;&gt;0,LEFT($K41,1)&lt;&gt;"✅"),COUNT($M$6:M40)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N41">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="42" ht="21" customHeight="1">
       <c r="A42" s="9">
@@ -6089,6 +6383,14 @@
         <f>IF($H42="","",IF($H42=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H42)=0,"🟡 ما انزلت بنودها",IF(ROUND($I42-$J42,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I42-$J42,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M42">
+        <f>IF(AND($H42&lt;&gt;"",$H42&lt;&gt;0,LEFT($K42,1)&lt;&gt;"✅"),COUNT($M$6:M41)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N42">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="43" ht="21" customHeight="1">
       <c r="A43" s="9">
@@ -6119,6 +6421,14 @@
         <f>IF($H43="","",IF($H43=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H43)=0,"🟡 ما انزلت بنودها",IF(ROUND($I43-$J43,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I43-$J43,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M43">
+        <f>IF(AND($H43&lt;&gt;"",$H43&lt;&gt;0,LEFT($K43,1)&lt;&gt;"✅"),COUNT($M$6:M42)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N43">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="44" ht="21" customHeight="1">
       <c r="A44" s="9">
@@ -6149,6 +6459,14 @@
         <f>IF($H44="","",IF($H44=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H44)=0,"🟡 ما انزلت بنودها",IF(ROUND($I44-$J44,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I44-$J44,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M44">
+        <f>IF(AND($H44&lt;&gt;"",$H44&lt;&gt;0,LEFT($K44,1)&lt;&gt;"✅"),COUNT($M$6:M43)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N44">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="45" ht="21" customHeight="1">
       <c r="A45" s="9">
@@ -6179,6 +6497,14 @@
         <f>IF($H45="","",IF($H45=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H45)=0,"🟡 ما انزلت بنودها",IF(ROUND($I45-$J45,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I45-$J45,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M45">
+        <f>IF(AND($H45&lt;&gt;"",$H45&lt;&gt;0,LEFT($K45,1)&lt;&gt;"✅"),COUNT($M$6:M44)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N45">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="46" ht="21" customHeight="1">
       <c r="A46" s="9">
@@ -6209,6 +6535,14 @@
         <f>IF($H46="","",IF($H46=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H46)=0,"🟡 ما انزلت بنودها",IF(ROUND($I46-$J46,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I46-$J46,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M46">
+        <f>IF(AND($H46&lt;&gt;"",$H46&lt;&gt;0,LEFT($K46,1)&lt;&gt;"✅"),COUNT($M$6:M45)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N46">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="47" ht="21" customHeight="1">
       <c r="A47" s="9">
@@ -6239,6 +6573,14 @@
         <f>IF($H47="","",IF($H47=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H47)=0,"🟡 ما انزلت بنودها",IF(ROUND($I47-$J47,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I47-$J47,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M47">
+        <f>IF(AND($H47&lt;&gt;"",$H47&lt;&gt;0,LEFT($K47,1)&lt;&gt;"✅"),COUNT($M$6:M46)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N47">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="48" ht="21" customHeight="1">
       <c r="A48" s="9">
@@ -6269,6 +6611,14 @@
         <f>IF($H48="","",IF($H48=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H48)=0,"🟡 ما انزلت بنودها",IF(ROUND($I48-$J48,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I48-$J48,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M48">
+        <f>IF(AND($H48&lt;&gt;"",$H48&lt;&gt;0,LEFT($K48,1)&lt;&gt;"✅"),COUNT($M$6:M47)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N48">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="49" ht="21" customHeight="1">
       <c r="A49" s="9">
@@ -6299,6 +6649,14 @@
         <f>IF($H49="","",IF($H49=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H49)=0,"🟡 ما انزلت بنودها",IF(ROUND($I49-$J49,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I49-$J49,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M49">
+        <f>IF(AND($H49&lt;&gt;"",$H49&lt;&gt;0,LEFT($K49,1)&lt;&gt;"✅"),COUNT($M$6:M48)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N49">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="50" ht="21" customHeight="1">
       <c r="A50" s="9">
@@ -6329,6 +6687,14 @@
         <f>IF($H50="","",IF($H50=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H50)=0,"🟡 ما انزلت بنودها",IF(ROUND($I50-$J50,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I50-$J50,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M50">
+        <f>IF(AND($H50&lt;&gt;"",$H50&lt;&gt;0,LEFT($K50,1)&lt;&gt;"✅"),COUNT($M$6:M49)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N50">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="51" ht="21" customHeight="1">
       <c r="A51" s="9">
@@ -6359,6 +6725,14 @@
         <f>IF($H51="","",IF($H51=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H51)=0,"🟡 ما انزلت بنودها",IF(ROUND($I51-$J51,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I51-$J51,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M51">
+        <f>IF(AND($H51&lt;&gt;"",$H51&lt;&gt;0,LEFT($K51,1)&lt;&gt;"✅"),COUNT($M$6:M50)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N51">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="52" ht="21" customHeight="1">
       <c r="A52" s="9">
@@ -6389,6 +6763,14 @@
         <f>IF($H52="","",IF($H52=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H52)=0,"🟡 ما انزلت بنودها",IF(ROUND($I52-$J52,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I52-$J52,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M52">
+        <f>IF(AND($H52&lt;&gt;"",$H52&lt;&gt;0,LEFT($K52,1)&lt;&gt;"✅"),COUNT($M$6:M51)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N52">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="53" ht="21" customHeight="1">
       <c r="A53" s="9">
@@ -6419,6 +6801,14 @@
         <f>IF($H53="","",IF($H53=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H53)=0,"🟡 ما انزلت بنودها",IF(ROUND($I53-$J53,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I53-$J53,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M53">
+        <f>IF(AND($H53&lt;&gt;"",$H53&lt;&gt;0,LEFT($K53,1)&lt;&gt;"✅"),COUNT($M$6:M52)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N53">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="54" ht="21" customHeight="1">
       <c r="A54" s="9">
@@ -6449,6 +6839,14 @@
         <f>IF($H54="","",IF($H54=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H54)=0,"🟡 ما انزلت بنودها",IF(ROUND($I54-$J54,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I54-$J54,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M54">
+        <f>IF(AND($H54&lt;&gt;"",$H54&lt;&gt;0,LEFT($K54,1)&lt;&gt;"✅"),COUNT($M$6:M53)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N54">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="55" ht="21" customHeight="1">
       <c r="A55" s="9">
@@ -6479,6 +6877,14 @@
         <f>IF($H55="","",IF($H55=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H55)=0,"🟡 ما انزلت بنودها",IF(ROUND($I55-$J55,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I55-$J55,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M55">
+        <f>IF(AND($H55&lt;&gt;"",$H55&lt;&gt;0,LEFT($K55,1)&lt;&gt;"✅"),COUNT($M$6:M54)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N55">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="56" ht="21" customHeight="1">
       <c r="A56" s="9">
@@ -6509,6 +6915,14 @@
         <f>IF($H56="","",IF($H56=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H56)=0,"🟡 ما انزلت بنودها",IF(ROUND($I56-$J56,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I56-$J56,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M56">
+        <f>IF(AND($H56&lt;&gt;"",$H56&lt;&gt;0,LEFT($K56,1)&lt;&gt;"✅"),COUNT($M$6:M55)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N56">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="57" ht="21" customHeight="1">
       <c r="A57" s="9">
@@ -6539,6 +6953,14 @@
         <f>IF($H57="","",IF($H57=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H57)=0,"🟡 ما انزلت بنودها",IF(ROUND($I57-$J57,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I57-$J57,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M57">
+        <f>IF(AND($H57&lt;&gt;"",$H57&lt;&gt;0,LEFT($K57,1)&lt;&gt;"✅"),COUNT($M$6:M56)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N57">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="58" ht="21" customHeight="1">
       <c r="A58" s="9">
@@ -6569,6 +6991,14 @@
         <f>IF($H58="","",IF($H58=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H58)=0,"🟡 ما انزلت بنودها",IF(ROUND($I58-$J58,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I58-$J58,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M58">
+        <f>IF(AND($H58&lt;&gt;"",$H58&lt;&gt;0,LEFT($K58,1)&lt;&gt;"✅"),COUNT($M$6:M57)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N58">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="59" ht="21" customHeight="1">
       <c r="A59" s="9">
@@ -6599,6 +7029,14 @@
         <f>IF($H59="","",IF($H59=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H59)=0,"🟡 ما انزلت بنودها",IF(ROUND($I59-$J59,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I59-$J59,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M59">
+        <f>IF(AND($H59&lt;&gt;"",$H59&lt;&gt;0,LEFT($K59,1)&lt;&gt;"✅"),COUNT($M$6:M58)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N59">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="60" ht="21" customHeight="1">
       <c r="A60" s="9">
@@ -6629,6 +7067,14 @@
         <f>IF($H60="","",IF($H60=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H60)=0,"🟡 ما انزلت بنودها",IF(ROUND($I60-$J60,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I60-$J60,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M60">
+        <f>IF(AND($H60&lt;&gt;"",$H60&lt;&gt;0,LEFT($K60,1)&lt;&gt;"✅"),COUNT($M$6:M59)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N60">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="61" ht="21" customHeight="1">
       <c r="A61" s="9">
@@ -6659,6 +7105,14 @@
         <f>IF($H61="","",IF($H61=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H61)=0,"🟡 ما انزلت بنودها",IF(ROUND($I61-$J61,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I61-$J61,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M61">
+        <f>IF(AND($H61&lt;&gt;"",$H61&lt;&gt;0,LEFT($K61,1)&lt;&gt;"✅"),COUNT($M$6:M60)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N61">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="62" ht="21" customHeight="1">
       <c r="A62" s="9">
@@ -6689,6 +7143,14 @@
         <f>IF($H62="","",IF($H62=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H62)=0,"🟡 ما انزلت بنودها",IF(ROUND($I62-$J62,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I62-$J62,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M62">
+        <f>IF(AND($H62&lt;&gt;"",$H62&lt;&gt;0,LEFT($K62,1)&lt;&gt;"✅"),COUNT($M$6:M61)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N62">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="63" ht="21" customHeight="1">
       <c r="A63" s="9">
@@ -6719,6 +7181,14 @@
         <f>IF($H63="","",IF($H63=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H63)=0,"🟡 ما انزلت بنودها",IF(ROUND($I63-$J63,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I63-$J63,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M63">
+        <f>IF(AND($H63&lt;&gt;"",$H63&lt;&gt;0,LEFT($K63,1)&lt;&gt;"✅"),COUNT($M$6:M62)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N63">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="64" ht="21" customHeight="1">
       <c r="A64" s="9">
@@ -6749,6 +7219,14 @@
         <f>IF($H64="","",IF($H64=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H64)=0,"🟡 ما انزلت بنودها",IF(ROUND($I64-$J64,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I64-$J64,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M64">
+        <f>IF(AND($H64&lt;&gt;"",$H64&lt;&gt;0,LEFT($K64,1)&lt;&gt;"✅"),COUNT($M$6:M63)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N64">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="65" ht="21" customHeight="1">
       <c r="A65" s="9">
@@ -6779,6 +7257,14 @@
         <f>IF($H65="","",IF($H65=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H65)=0,"🟡 ما انزلت بنودها",IF(ROUND($I65-$J65,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I65-$J65,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M65">
+        <f>IF(AND($H65&lt;&gt;"",$H65&lt;&gt;0,LEFT($K65,1)&lt;&gt;"✅"),COUNT($M$6:M64)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N65">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="66" ht="21" customHeight="1">
       <c r="A66" s="9">
@@ -6809,6 +7295,14 @@
         <f>IF($H66="","",IF($H66=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H66)=0,"🟡 ما انزلت بنودها",IF(ROUND($I66-$J66,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I66-$J66,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M66">
+        <f>IF(AND($H66&lt;&gt;"",$H66&lt;&gt;0,LEFT($K66,1)&lt;&gt;"✅"),COUNT($M$6:M65)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N66">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="67" ht="21" customHeight="1">
       <c r="A67" s="9">
@@ -6839,6 +7333,14 @@
         <f>IF($H67="","",IF($H67=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H67)=0,"🟡 ما انزلت بنودها",IF(ROUND($I67-$J67,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I67-$J67,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M67">
+        <f>IF(AND($H67&lt;&gt;"",$H67&lt;&gt;0,LEFT($K67,1)&lt;&gt;"✅"),COUNT($M$6:M66)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N67">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="68" ht="21" customHeight="1">
       <c r="A68" s="9">
@@ -6869,6 +7371,14 @@
         <f>IF($H68="","",IF($H68=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H68)=0,"🟡 ما انزلت بنودها",IF(ROUND($I68-$J68,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I68-$J68,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M68">
+        <f>IF(AND($H68&lt;&gt;"",$H68&lt;&gt;0,LEFT($K68,1)&lt;&gt;"✅"),COUNT($M$6:M67)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N68">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="69" ht="21" customHeight="1">
       <c r="A69" s="9">
@@ -6899,6 +7409,14 @@
         <f>IF($H69="","",IF($H69=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H69)=0,"🟡 ما انزلت بنودها",IF(ROUND($I69-$J69,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I69-$J69,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M69">
+        <f>IF(AND($H69&lt;&gt;"",$H69&lt;&gt;0,LEFT($K69,1)&lt;&gt;"✅"),COUNT($M$6:M68)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N69">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="70" ht="21" customHeight="1">
       <c r="A70" s="9">
@@ -6929,6 +7447,14 @@
         <f>IF($H70="","",IF($H70=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H70)=0,"🟡 ما انزلت بنودها",IF(ROUND($I70-$J70,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I70-$J70,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M70">
+        <f>IF(AND($H70&lt;&gt;"",$H70&lt;&gt;0,LEFT($K70,1)&lt;&gt;"✅"),COUNT($M$6:M69)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N70">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="71" ht="21" customHeight="1">
       <c r="A71" s="9">
@@ -6959,6 +7485,14 @@
         <f>IF($H71="","",IF($H71=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H71)=0,"🟡 ما انزلت بنودها",IF(ROUND($I71-$J71,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I71-$J71,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M71">
+        <f>IF(AND($H71&lt;&gt;"",$H71&lt;&gt;0,LEFT($K71,1)&lt;&gt;"✅"),COUNT($M$6:M70)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N71">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="72" ht="21" customHeight="1">
       <c r="A72" s="9">
@@ -6989,6 +7523,14 @@
         <f>IF($H72="","",IF($H72=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H72)=0,"🟡 ما انزلت بنودها",IF(ROUND($I72-$J72,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I72-$J72,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M72">
+        <f>IF(AND($H72&lt;&gt;"",$H72&lt;&gt;0,LEFT($K72,1)&lt;&gt;"✅"),COUNT($M$6:M71)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N72">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="73" ht="21" customHeight="1">
       <c r="A73" s="9">
@@ -7019,6 +7561,14 @@
         <f>IF($H73="","",IF($H73=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H73)=0,"🟡 ما انزلت بنودها",IF(ROUND($I73-$J73,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I73-$J73,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M73">
+        <f>IF(AND($H73&lt;&gt;"",$H73&lt;&gt;0,LEFT($K73,1)&lt;&gt;"✅"),COUNT($M$6:M72)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N73">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="74" ht="21" customHeight="1">
       <c r="A74" s="9">
@@ -7049,6 +7599,14 @@
         <f>IF($H74="","",IF($H74=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H74)=0,"🟡 ما انزلت بنودها",IF(ROUND($I74-$J74,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I74-$J74,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M74">
+        <f>IF(AND($H74&lt;&gt;"",$H74&lt;&gt;0,LEFT($K74,1)&lt;&gt;"✅"),COUNT($M$6:M73)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N74">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="75" ht="21" customHeight="1">
       <c r="A75" s="9">
@@ -7079,6 +7637,14 @@
         <f>IF($H75="","",IF($H75=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H75)=0,"🟡 ما انزلت بنودها",IF(ROUND($I75-$J75,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I75-$J75,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M75">
+        <f>IF(AND($H75&lt;&gt;"",$H75&lt;&gt;0,LEFT($K75,1)&lt;&gt;"✅"),COUNT($M$6:M74)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N75">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="76" ht="21" customHeight="1">
       <c r="A76" s="9">
@@ -7109,6 +7675,14 @@
         <f>IF($H76="","",IF($H76=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H76)=0,"🟡 ما انزلت بنودها",IF(ROUND($I76-$J76,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I76-$J76,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M76">
+        <f>IF(AND($H76&lt;&gt;"",$H76&lt;&gt;0,LEFT($K76,1)&lt;&gt;"✅"),COUNT($M$6:M75)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N76">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="77" ht="21" customHeight="1">
       <c r="A77" s="9">
@@ -7139,6 +7713,14 @@
         <f>IF($H77="","",IF($H77=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H77)=0,"🟡 ما انزلت بنودها",IF(ROUND($I77-$J77,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I77-$J77,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M77">
+        <f>IF(AND($H77&lt;&gt;"",$H77&lt;&gt;0,LEFT($K77,1)&lt;&gt;"✅"),COUNT($M$6:M76)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N77">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="78" ht="21" customHeight="1">
       <c r="A78" s="9">
@@ -7169,6 +7751,14 @@
         <f>IF($H78="","",IF($H78=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H78)=0,"🟡 ما انزلت بنودها",IF(ROUND($I78-$J78,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I78-$J78,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M78">
+        <f>IF(AND($H78&lt;&gt;"",$H78&lt;&gt;0,LEFT($K78,1)&lt;&gt;"✅"),COUNT($M$6:M77)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N78">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="79" ht="21" customHeight="1">
       <c r="A79" s="9">
@@ -7199,6 +7789,14 @@
         <f>IF($H79="","",IF($H79=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H79)=0,"🟡 ما انزلت بنودها",IF(ROUND($I79-$J79,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I79-$J79,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M79">
+        <f>IF(AND($H79&lt;&gt;"",$H79&lt;&gt;0,LEFT($K79,1)&lt;&gt;"✅"),COUNT($M$6:M78)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N79">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="80" ht="21" customHeight="1">
       <c r="A80" s="9">
@@ -7229,6 +7827,14 @@
         <f>IF($H80="","",IF($H80=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H80)=0,"🟡 ما انزلت بنودها",IF(ROUND($I80-$J80,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I80-$J80,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M80">
+        <f>IF(AND($H80&lt;&gt;"",$H80&lt;&gt;0,LEFT($K80,1)&lt;&gt;"✅"),COUNT($M$6:M79)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N80">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="81" ht="21" customHeight="1">
       <c r="A81" s="9">
@@ -7259,6 +7865,14 @@
         <f>IF($H81="","",IF($H81=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H81)=0,"🟡 ما انزلت بنودها",IF(ROUND($I81-$J81,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I81-$J81,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M81">
+        <f>IF(AND($H81&lt;&gt;"",$H81&lt;&gt;0,LEFT($K81,1)&lt;&gt;"✅"),COUNT($M$6:M80)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N81">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="82" ht="21" customHeight="1">
       <c r="A82" s="9">
@@ -7289,6 +7903,14 @@
         <f>IF($H82="","",IF($H82=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H82)=0,"🟡 ما انزلت بنودها",IF(ROUND($I82-$J82,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I82-$J82,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M82">
+        <f>IF(AND($H82&lt;&gt;"",$H82&lt;&gt;0,LEFT($K82,1)&lt;&gt;"✅"),COUNT($M$6:M81)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N82">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="83" ht="21" customHeight="1">
       <c r="A83" s="9">
@@ -7319,6 +7941,14 @@
         <f>IF($H83="","",IF($H83=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H83)=0,"🟡 ما انزلت بنودها",IF(ROUND($I83-$J83,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I83-$J83,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M83">
+        <f>IF(AND($H83&lt;&gt;"",$H83&lt;&gt;0,LEFT($K83,1)&lt;&gt;"✅"),COUNT($M$6:M82)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N83">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="84" ht="21" customHeight="1">
       <c r="A84" s="9">
@@ -7349,6 +7979,14 @@
         <f>IF($H84="","",IF($H84=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H84)=0,"🟡 ما انزلت بنودها",IF(ROUND($I84-$J84,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I84-$J84,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M84">
+        <f>IF(AND($H84&lt;&gt;"",$H84&lt;&gt;0,LEFT($K84,1)&lt;&gt;"✅"),COUNT($M$6:M83)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N84">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="85" ht="21" customHeight="1">
       <c r="A85" s="9">
@@ -7379,6 +8017,14 @@
         <f>IF($H85="","",IF($H85=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H85)=0,"🟡 ما انزلت بنودها",IF(ROUND($I85-$J85,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I85-$J85,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M85">
+        <f>IF(AND($H85&lt;&gt;"",$H85&lt;&gt;0,LEFT($K85,1)&lt;&gt;"✅"),COUNT($M$6:M84)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N85">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="86" ht="21" customHeight="1">
       <c r="A86" s="9">
@@ -7409,6 +8055,14 @@
         <f>IF($H86="","",IF($H86=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H86)=0,"🟡 ما انزلت بنودها",IF(ROUND($I86-$J86,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I86-$J86,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M86">
+        <f>IF(AND($H86&lt;&gt;"",$H86&lt;&gt;0,LEFT($K86,1)&lt;&gt;"✅"),COUNT($M$6:M85)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N86">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="87" ht="21" customHeight="1">
       <c r="A87" s="9">
@@ -7439,6 +8093,14 @@
         <f>IF($H87="","",IF($H87=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H87)=0,"🟡 ما انزلت بنودها",IF(ROUND($I87-$J87,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I87-$J87,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M87">
+        <f>IF(AND($H87&lt;&gt;"",$H87&lt;&gt;0,LEFT($K87,1)&lt;&gt;"✅"),COUNT($M$6:M86)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N87">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="88" ht="21" customHeight="1">
       <c r="A88" s="9">
@@ -7469,6 +8131,14 @@
         <f>IF($H88="","",IF($H88=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H88)=0,"🟡 ما انزلت بنودها",IF(ROUND($I88-$J88,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I88-$J88,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M88">
+        <f>IF(AND($H88&lt;&gt;"",$H88&lt;&gt;0,LEFT($K88,1)&lt;&gt;"✅"),COUNT($M$6:M87)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N88">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="89" ht="21" customHeight="1">
       <c r="A89" s="9">
@@ -7499,6 +8169,14 @@
         <f>IF($H89="","",IF($H89=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H89)=0,"🟡 ما انزلت بنودها",IF(ROUND($I89-$J89,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I89-$J89,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M89">
+        <f>IF(AND($H89&lt;&gt;"",$H89&lt;&gt;0,LEFT($K89,1)&lt;&gt;"✅"),COUNT($M$6:M88)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N89">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="90" ht="21" customHeight="1">
       <c r="A90" s="9">
@@ -7529,6 +8207,14 @@
         <f>IF($H90="","",IF($H90=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H90)=0,"🟡 ما انزلت بنودها",IF(ROUND($I90-$J90,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I90-$J90,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M90">
+        <f>IF(AND($H90&lt;&gt;"",$H90&lt;&gt;0,LEFT($K90,1)&lt;&gt;"✅"),COUNT($M$6:M89)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N90">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="91" ht="21" customHeight="1">
       <c r="A91" s="9">
@@ -7559,6 +8245,14 @@
         <f>IF($H91="","",IF($H91=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H91)=0,"🟡 ما انزلت بنودها",IF(ROUND($I91-$J91,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I91-$J91,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M91">
+        <f>IF(AND($H91&lt;&gt;"",$H91&lt;&gt;0,LEFT($K91,1)&lt;&gt;"✅"),COUNT($M$6:M90)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N91">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="92" ht="21" customHeight="1">
       <c r="A92" s="9">
@@ -7589,6 +8283,14 @@
         <f>IF($H92="","",IF($H92=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H92)=0,"🟡 ما انزلت بنودها",IF(ROUND($I92-$J92,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I92-$J92,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M92">
+        <f>IF(AND($H92&lt;&gt;"",$H92&lt;&gt;0,LEFT($K92,1)&lt;&gt;"✅"),COUNT($M$6:M91)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N92">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="93" ht="21" customHeight="1">
       <c r="A93" s="9">
@@ -7619,6 +8321,14 @@
         <f>IF($H93="","",IF($H93=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H93)=0,"🟡 ما انزلت بنودها",IF(ROUND($I93-$J93,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I93-$J93,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M93">
+        <f>IF(AND($H93&lt;&gt;"",$H93&lt;&gt;0,LEFT($K93,1)&lt;&gt;"✅"),COUNT($M$6:M92)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N93">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="94" ht="21" customHeight="1">
       <c r="A94" s="9">
@@ -7649,6 +8359,14 @@
         <f>IF($H94="","",IF($H94=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H94)=0,"🟡 ما انزلت بنودها",IF(ROUND($I94-$J94,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I94-$J94,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M94">
+        <f>IF(AND($H94&lt;&gt;"",$H94&lt;&gt;0,LEFT($K94,1)&lt;&gt;"✅"),COUNT($M$6:M93)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N94">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="95" ht="21" customHeight="1">
       <c r="A95" s="9">
@@ -7679,6 +8397,14 @@
         <f>IF($H95="","",IF($H95=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H95)=0,"🟡 ما انزلت بنودها",IF(ROUND($I95-$J95,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I95-$J95,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M95">
+        <f>IF(AND($H95&lt;&gt;"",$H95&lt;&gt;0,LEFT($K95,1)&lt;&gt;"✅"),COUNT($M$6:M94)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N95">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="96" ht="21" customHeight="1">
       <c r="A96" s="9">
@@ -7709,6 +8435,14 @@
         <f>IF($H96="","",IF($H96=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H96)=0,"🟡 ما انزلت بنودها",IF(ROUND($I96-$J96,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I96-$J96,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M96">
+        <f>IF(AND($H96&lt;&gt;"",$H96&lt;&gt;0,LEFT($K96,1)&lt;&gt;"✅"),COUNT($M$6:M95)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N96">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="97" ht="21" customHeight="1">
       <c r="A97" s="9">
@@ -7739,6 +8473,14 @@
         <f>IF($H97="","",IF($H97=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H97)=0,"🟡 ما انزلت بنودها",IF(ROUND($I97-$J97,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I97-$J97,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M97">
+        <f>IF(AND($H97&lt;&gt;"",$H97&lt;&gt;0,LEFT($K97,1)&lt;&gt;"✅"),COUNT($M$6:M96)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N97">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="98" ht="21" customHeight="1">
       <c r="A98" s="9">
@@ -7769,6 +8511,14 @@
         <f>IF($H98="","",IF($H98=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H98)=0,"🟡 ما انزلت بنودها",IF(ROUND($I98-$J98,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I98-$J98,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M98">
+        <f>IF(AND($H98&lt;&gt;"",$H98&lt;&gt;0,LEFT($K98,1)&lt;&gt;"✅"),COUNT($M$6:M97)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N98">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="99" ht="21" customHeight="1">
       <c r="A99" s="9">
@@ -7799,6 +8549,14 @@
         <f>IF($H99="","",IF($H99=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H99)=0,"🟡 ما انزلت بنودها",IF(ROUND($I99-$J99,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I99-$J99,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M99">
+        <f>IF(AND($H99&lt;&gt;"",$H99&lt;&gt;0,LEFT($K99,1)&lt;&gt;"✅"),COUNT($M$6:M98)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N99">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="100" ht="21" customHeight="1">
       <c r="A100" s="9">
@@ -7829,6 +8587,14 @@
         <f>IF($H100="","",IF($H100=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H100)=0,"🟡 ما انزلت بنودها",IF(ROUND($I100-$J100,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I100-$J100,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M100">
+        <f>IF(AND($H100&lt;&gt;"",$H100&lt;&gt;0,LEFT($K100,1)&lt;&gt;"✅"),COUNT($M$6:M99)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N100">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="101" ht="21" customHeight="1">
       <c r="A101" s="9">
@@ -7859,6 +8625,14 @@
         <f>IF($H101="","",IF($H101=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H101)=0,"🟡 ما انزلت بنودها",IF(ROUND($I101-$J101,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I101-$J101,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M101">
+        <f>IF(AND($H101&lt;&gt;"",$H101&lt;&gt;0,LEFT($K101,1)&lt;&gt;"✅"),COUNT($M$6:M100)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N101">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="102" ht="21" customHeight="1">
       <c r="A102" s="9">
@@ -7889,6 +8663,14 @@
         <f>IF($H102="","",IF($H102=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H102)=0,"🟡 ما انزلت بنودها",IF(ROUND($I102-$J102,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I102-$J102,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M102">
+        <f>IF(AND($H102&lt;&gt;"",$H102&lt;&gt;0,LEFT($K102,1)&lt;&gt;"✅"),COUNT($M$6:M101)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N102">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="103" ht="21" customHeight="1">
       <c r="A103" s="9">
@@ -7919,6 +8701,14 @@
         <f>IF($H103="","",IF($H103=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H103)=0,"🟡 ما انزلت بنودها",IF(ROUND($I103-$J103,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I103-$J103,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M103">
+        <f>IF(AND($H103&lt;&gt;"",$H103&lt;&gt;0,LEFT($K103,1)&lt;&gt;"✅"),COUNT($M$6:M102)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N103">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="104" ht="21" customHeight="1">
       <c r="A104" s="9">
@@ -7949,6 +8739,14 @@
         <f>IF($H104="","",IF($H104=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H104)=0,"🟡 ما انزلت بنودها",IF(ROUND($I104-$J104,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I104-$J104,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M104">
+        <f>IF(AND($H104&lt;&gt;"",$H104&lt;&gt;0,LEFT($K104,1)&lt;&gt;"✅"),COUNT($M$6:M103)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N104">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="105" ht="21" customHeight="1">
       <c r="A105" s="9">
@@ -7979,6 +8777,14 @@
         <f>IF($H105="","",IF($H105=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H105)=0,"🟡 ما انزلت بنودها",IF(ROUND($I105-$J105,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I105-$J105,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M105">
+        <f>IF(AND($H105&lt;&gt;"",$H105&lt;&gt;0,LEFT($K105,1)&lt;&gt;"✅"),COUNT($M$6:M104)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N105">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="106" ht="21" customHeight="1">
       <c r="A106" s="9">
@@ -8009,6 +8815,14 @@
         <f>IF($H106="","",IF($H106=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H106)=0,"🟡 ما انزلت بنودها",IF(ROUND($I106-$J106,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I106-$J106,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M106">
+        <f>IF(AND($H106&lt;&gt;"",$H106&lt;&gt;0,LEFT($K106,1)&lt;&gt;"✅"),COUNT($M$6:M105)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N106">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="107" ht="21" customHeight="1">
       <c r="A107" s="9">
@@ -8039,6 +8853,14 @@
         <f>IF($H107="","",IF($H107=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H107)=0,"🟡 ما انزلت بنودها",IF(ROUND($I107-$J107,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I107-$J107,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M107">
+        <f>IF(AND($H107&lt;&gt;"",$H107&lt;&gt;0,LEFT($K107,1)&lt;&gt;"✅"),COUNT($M$6:M106)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N107">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="108" ht="21" customHeight="1">
       <c r="A108" s="9">
@@ -8069,6 +8891,14 @@
         <f>IF($H108="","",IF($H108=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H108)=0,"🟡 ما انزلت بنودها",IF(ROUND($I108-$J108,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I108-$J108,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M108">
+        <f>IF(AND($H108&lt;&gt;"",$H108&lt;&gt;0,LEFT($K108,1)&lt;&gt;"✅"),COUNT($M$6:M107)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N108">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="109" ht="21" customHeight="1">
       <c r="A109" s="9">
@@ -8099,6 +8929,14 @@
         <f>IF($H109="","",IF($H109=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H109)=0,"🟡 ما انزلت بنودها",IF(ROUND($I109-$J109,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I109-$J109,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M109">
+        <f>IF(AND($H109&lt;&gt;"",$H109&lt;&gt;0,LEFT($K109,1)&lt;&gt;"✅"),COUNT($M$6:M108)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N109">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="110" ht="21" customHeight="1">
       <c r="A110" s="9">
@@ -8129,6 +8967,14 @@
         <f>IF($H110="","",IF($H110=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H110)=0,"🟡 ما انزلت بنودها",IF(ROUND($I110-$J110,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I110-$J110,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M110">
+        <f>IF(AND($H110&lt;&gt;"",$H110&lt;&gt;0,LEFT($K110,1)&lt;&gt;"✅"),COUNT($M$6:M109)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N110">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="111" ht="21" customHeight="1">
       <c r="A111" s="9">
@@ -8159,6 +9005,14 @@
         <f>IF($H111="","",IF($H111=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H111)=0,"🟡 ما انزلت بنودها",IF(ROUND($I111-$J111,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I111-$J111,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M111">
+        <f>IF(AND($H111&lt;&gt;"",$H111&lt;&gt;0,LEFT($K111,1)&lt;&gt;"✅"),COUNT($M$6:M110)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N111">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="112" ht="21" customHeight="1">
       <c r="A112" s="9">
@@ -8189,6 +9043,14 @@
         <f>IF($H112="","",IF($H112=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H112)=0,"🟡 ما انزلت بنودها",IF(ROUND($I112-$J112,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I112-$J112,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M112">
+        <f>IF(AND($H112&lt;&gt;"",$H112&lt;&gt;0,LEFT($K112,1)&lt;&gt;"✅"),COUNT($M$6:M111)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N112">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="113" ht="21" customHeight="1">
       <c r="A113" s="9">
@@ -8219,6 +9081,14 @@
         <f>IF($H113="","",IF($H113=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H113)=0,"🟡 ما انزلت بنودها",IF(ROUND($I113-$J113,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I113-$J113,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M113">
+        <f>IF(AND($H113&lt;&gt;"",$H113&lt;&gt;0,LEFT($K113,1)&lt;&gt;"✅"),COUNT($M$6:M112)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N113">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="114" ht="21" customHeight="1">
       <c r="A114" s="9">
@@ -8249,6 +9119,14 @@
         <f>IF($H114="","",IF($H114=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H114)=0,"🟡 ما انزلت بنودها",IF(ROUND($I114-$J114,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I114-$J114,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M114">
+        <f>IF(AND($H114&lt;&gt;"",$H114&lt;&gt;0,LEFT($K114,1)&lt;&gt;"✅"),COUNT($M$6:M113)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N114">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="115" ht="21" customHeight="1">
       <c r="A115" s="9">
@@ -8279,6 +9157,14 @@
         <f>IF($H115="","",IF($H115=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H115)=0,"🟡 ما انزلت بنودها",IF(ROUND($I115-$J115,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I115-$J115,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M115">
+        <f>IF(AND($H115&lt;&gt;"",$H115&lt;&gt;0,LEFT($K115,1)&lt;&gt;"✅"),COUNT($M$6:M114)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N115">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="116" ht="21" customHeight="1">
       <c r="A116" s="9">
@@ -8309,6 +9195,14 @@
         <f>IF($H116="","",IF($H116=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H116)=0,"🟡 ما انزلت بنودها",IF(ROUND($I116-$J116,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I116-$J116,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M116">
+        <f>IF(AND($H116&lt;&gt;"",$H116&lt;&gt;0,LEFT($K116,1)&lt;&gt;"✅"),COUNT($M$6:M115)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N116">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="117" ht="21" customHeight="1">
       <c r="A117" s="9">
@@ -8339,6 +9233,14 @@
         <f>IF($H117="","",IF($H117=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H117)=0,"🟡 ما انزلت بنودها",IF(ROUND($I117-$J117,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I117-$J117,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M117">
+        <f>IF(AND($H117&lt;&gt;"",$H117&lt;&gt;0,LEFT($K117,1)&lt;&gt;"✅"),COUNT($M$6:M116)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N117">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="118" ht="21" customHeight="1">
       <c r="A118" s="9">
@@ -8369,6 +9271,14 @@
         <f>IF($H118="","",IF($H118=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H118)=0,"🟡 ما انزلت بنودها",IF(ROUND($I118-$J118,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I118-$J118,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M118">
+        <f>IF(AND($H118&lt;&gt;"",$H118&lt;&gt;0,LEFT($K118,1)&lt;&gt;"✅"),COUNT($M$6:M117)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N118">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="119" ht="21" customHeight="1">
       <c r="A119" s="9">
@@ -8399,6 +9309,14 @@
         <f>IF($H119="","",IF($H119=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H119)=0,"🟡 ما انزلت بنودها",IF(ROUND($I119-$J119,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I119-$J119,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M119">
+        <f>IF(AND($H119&lt;&gt;"",$H119&lt;&gt;0,LEFT($K119,1)&lt;&gt;"✅"),COUNT($M$6:M118)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N119">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="120" ht="21" customHeight="1">
       <c r="A120" s="9">
@@ -8429,6 +9347,14 @@
         <f>IF($H120="","",IF($H120=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H120)=0,"🟡 ما انزلت بنودها",IF(ROUND($I120-$J120,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I120-$J120,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M120">
+        <f>IF(AND($H120&lt;&gt;"",$H120&lt;&gt;0,LEFT($K120,1)&lt;&gt;"✅"),COUNT($M$6:M119)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N120">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="121" ht="21" customHeight="1">
       <c r="A121" s="9">
@@ -8459,6 +9385,14 @@
         <f>IF($H121="","",IF($H121=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H121)=0,"🟡 ما انزلت بنودها",IF(ROUND($I121-$J121,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I121-$J121,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M121">
+        <f>IF(AND($H121&lt;&gt;"",$H121&lt;&gt;0,LEFT($K121,1)&lt;&gt;"✅"),COUNT($M$6:M120)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N121">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="122" ht="21" customHeight="1">
       <c r="A122" s="9">
@@ -8489,6 +9423,14 @@
         <f>IF($H122="","",IF($H122=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H122)=0,"🟡 ما انزلت بنودها",IF(ROUND($I122-$J122,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I122-$J122,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M122">
+        <f>IF(AND($H122&lt;&gt;"",$H122&lt;&gt;0,LEFT($K122,1)&lt;&gt;"✅"),COUNT($M$6:M121)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N122">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="123" ht="21" customHeight="1">
       <c r="A123" s="9">
@@ -8519,6 +9461,14 @@
         <f>IF($H123="","",IF($H123=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H123)=0,"🟡 ما انزلت بنودها",IF(ROUND($I123-$J123,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I123-$J123,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M123">
+        <f>IF(AND($H123&lt;&gt;"",$H123&lt;&gt;0,LEFT($K123,1)&lt;&gt;"✅"),COUNT($M$6:M122)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N123">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="124" ht="21" customHeight="1">
       <c r="A124" s="9">
@@ -8549,6 +9499,14 @@
         <f>IF($H124="","",IF($H124=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H124)=0,"🟡 ما انزلت بنودها",IF(ROUND($I124-$J124,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I124-$J124,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M124">
+        <f>IF(AND($H124&lt;&gt;"",$H124&lt;&gt;0,LEFT($K124,1)&lt;&gt;"✅"),COUNT($M$6:M123)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N124">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="125" ht="21" customHeight="1">
       <c r="A125" s="9">
@@ -8579,6 +9537,14 @@
         <f>IF($H125="","",IF($H125=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H125)=0,"🟡 ما انزلت بنودها",IF(ROUND($I125-$J125,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I125-$J125,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M125">
+        <f>IF(AND($H125&lt;&gt;"",$H125&lt;&gt;0,LEFT($K125,1)&lt;&gt;"✅"),COUNT($M$6:M124)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N125">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="126" ht="21" customHeight="1">
       <c r="A126" s="9">
@@ -8609,6 +9575,14 @@
         <f>IF($H126="","",IF($H126=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H126)=0,"🟡 ما انزلت بنودها",IF(ROUND($I126-$J126,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I126-$J126,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M126">
+        <f>IF(AND($H126&lt;&gt;"",$H126&lt;&gt;0,LEFT($K126,1)&lt;&gt;"✅"),COUNT($M$6:M125)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N126">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="127" ht="21" customHeight="1">
       <c r="A127" s="9">
@@ -8639,6 +9613,14 @@
         <f>IF($H127="","",IF($H127=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H127)=0,"🟡 ما انزلت بنودها",IF(ROUND($I127-$J127,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I127-$J127,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M127">
+        <f>IF(AND($H127&lt;&gt;"",$H127&lt;&gt;0,LEFT($K127,1)&lt;&gt;"✅"),COUNT($M$6:M126)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N127">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="128" ht="21" customHeight="1">
       <c r="A128" s="9">
@@ -8669,6 +9651,14 @@
         <f>IF($H128="","",IF($H128=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H128)=0,"🟡 ما انزلت بنودها",IF(ROUND($I128-$J128,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I128-$J128,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M128">
+        <f>IF(AND($H128&lt;&gt;"",$H128&lt;&gt;0,LEFT($K128,1)&lt;&gt;"✅"),COUNT($M$6:M127)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N128">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="129" ht="21" customHeight="1">
       <c r="A129" s="9">
@@ -8699,6 +9689,14 @@
         <f>IF($H129="","",IF($H129=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H129)=0,"🟡 ما انزلت بنودها",IF(ROUND($I129-$J129,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I129-$J129,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M129">
+        <f>IF(AND($H129&lt;&gt;"",$H129&lt;&gt;0,LEFT($K129,1)&lt;&gt;"✅"),COUNT($M$6:M128)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N129">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="130" ht="21" customHeight="1">
       <c r="A130" s="9">
@@ -8729,6 +9727,14 @@
         <f>IF($H130="","",IF($H130=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H130)=0,"🟡 ما انزلت بنودها",IF(ROUND($I130-$J130,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I130-$J130,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M130">
+        <f>IF(AND($H130&lt;&gt;"",$H130&lt;&gt;0,LEFT($K130,1)&lt;&gt;"✅"),COUNT($M$6:M129)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N130">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="131" ht="21" customHeight="1">
       <c r="A131" s="9">
@@ -8759,6 +9765,14 @@
         <f>IF($H131="","",IF($H131=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H131)=0,"🟡 ما انزلت بنودها",IF(ROUND($I131-$J131,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I131-$J131,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M131">
+        <f>IF(AND($H131&lt;&gt;"",$H131&lt;&gt;0,LEFT($K131,1)&lt;&gt;"✅"),COUNT($M$6:M130)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N131">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="132" ht="21" customHeight="1">
       <c r="A132" s="9">
@@ -8789,6 +9803,14 @@
         <f>IF($H132="","",IF($H132=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H132)=0,"🟡 ما انزلت بنودها",IF(ROUND($I132-$J132,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I132-$J132,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M132">
+        <f>IF(AND($H132&lt;&gt;"",$H132&lt;&gt;0,LEFT($K132,1)&lt;&gt;"✅"),COUNT($M$6:M131)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N132">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="133" ht="21" customHeight="1">
       <c r="A133" s="9">
@@ -8819,6 +9841,14 @@
         <f>IF($H133="","",IF($H133=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H133)=0,"🟡 ما انزلت بنودها",IF(ROUND($I133-$J133,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I133-$J133,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M133">
+        <f>IF(AND($H133&lt;&gt;"",$H133&lt;&gt;0,LEFT($K133,1)&lt;&gt;"✅"),COUNT($M$6:M132)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N133">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="134" ht="21" customHeight="1">
       <c r="A134" s="9">
@@ -8849,6 +9879,14 @@
         <f>IF($H134="","",IF($H134=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H134)=0,"🟡 ما انزلت بنودها",IF(ROUND($I134-$J134,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I134-$J134,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M134">
+        <f>IF(AND($H134&lt;&gt;"",$H134&lt;&gt;0,LEFT($K134,1)&lt;&gt;"✅"),COUNT($M$6:M133)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N134">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="135" ht="21" customHeight="1">
       <c r="A135" s="9">
@@ -8879,6 +9917,14 @@
         <f>IF($H135="","",IF($H135=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H135)=0,"🟡 ما انزلت بنودها",IF(ROUND($I135-$J135,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I135-$J135,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M135">
+        <f>IF(AND($H135&lt;&gt;"",$H135&lt;&gt;0,LEFT($K135,1)&lt;&gt;"✅"),COUNT($M$6:M134)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N135">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="136" ht="21" customHeight="1">
       <c r="A136" s="9">
@@ -8909,6 +9955,14 @@
         <f>IF($H136="","",IF($H136=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H136)=0,"🟡 ما انزلت بنودها",IF(ROUND($I136-$J136,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I136-$J136,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M136">
+        <f>IF(AND($H136&lt;&gt;"",$H136&lt;&gt;0,LEFT($K136,1)&lt;&gt;"✅"),COUNT($M$6:M135)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N136">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="137" ht="21" customHeight="1">
       <c r="A137" s="9">
@@ -8939,6 +9993,14 @@
         <f>IF($H137="","",IF($H137=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H137)=0,"🟡 ما انزلت بنودها",IF(ROUND($I137-$J137,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I137-$J137,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M137">
+        <f>IF(AND($H137&lt;&gt;"",$H137&lt;&gt;0,LEFT($K137,1)&lt;&gt;"✅"),COUNT($M$6:M136)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N137">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="138" ht="21" customHeight="1">
       <c r="A138" s="9">
@@ -8969,6 +10031,14 @@
         <f>IF($H138="","",IF($H138=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H138)=0,"🟡 ما انزلت بنودها",IF(ROUND($I138-$J138,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I138-$J138,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M138">
+        <f>IF(AND($H138&lt;&gt;"",$H138&lt;&gt;0,LEFT($K138,1)&lt;&gt;"✅"),COUNT($M$6:M137)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N138">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="139" ht="21" customHeight="1">
       <c r="A139" s="9">
@@ -8999,6 +10069,14 @@
         <f>IF($H139="","",IF($H139=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H139)=0,"🟡 ما انزلت بنودها",IF(ROUND($I139-$J139,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I139-$J139,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M139">
+        <f>IF(AND($H139&lt;&gt;"",$H139&lt;&gt;0,LEFT($K139,1)&lt;&gt;"✅"),COUNT($M$6:M138)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N139">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="140" ht="21" customHeight="1">
       <c r="A140" s="9">
@@ -9029,6 +10107,14 @@
         <f>IF($H140="","",IF($H140=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H140)=0,"🟡 ما انزلت بنودها",IF(ROUND($I140-$J140,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I140-$J140,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M140">
+        <f>IF(AND($H140&lt;&gt;"",$H140&lt;&gt;0,LEFT($K140,1)&lt;&gt;"✅"),COUNT($M$6:M139)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N140">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="141" ht="21" customHeight="1">
       <c r="A141" s="9">
@@ -9059,6 +10145,14 @@
         <f>IF($H141="","",IF($H141=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H141)=0,"🟡 ما انزلت بنودها",IF(ROUND($I141-$J141,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I141-$J141,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M141">
+        <f>IF(AND($H141&lt;&gt;"",$H141&lt;&gt;0,LEFT($K141,1)&lt;&gt;"✅"),COUNT($M$6:M140)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N141">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="142" ht="21" customHeight="1">
       <c r="A142" s="9">
@@ -9089,6 +10183,14 @@
         <f>IF($H142="","",IF($H142=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H142)=0,"🟡 ما انزلت بنودها",IF(ROUND($I142-$J142,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I142-$J142,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M142">
+        <f>IF(AND($H142&lt;&gt;"",$H142&lt;&gt;0,LEFT($K142,1)&lt;&gt;"✅"),COUNT($M$6:M141)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N142">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="143" ht="21" customHeight="1">
       <c r="A143" s="9">
@@ -9119,6 +10221,14 @@
         <f>IF($H143="","",IF($H143=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H143)=0,"🟡 ما انزلت بنودها",IF(ROUND($I143-$J143,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I143-$J143,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M143">
+        <f>IF(AND($H143&lt;&gt;"",$H143&lt;&gt;0,LEFT($K143,1)&lt;&gt;"✅"),COUNT($M$6:M142)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N143">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="144" ht="21" customHeight="1">
       <c r="A144" s="9">
@@ -9149,6 +10259,14 @@
         <f>IF($H144="","",IF($H144=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H144)=0,"🟡 ما انزلت بنودها",IF(ROUND($I144-$J144,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I144-$J144,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M144">
+        <f>IF(AND($H144&lt;&gt;"",$H144&lt;&gt;0,LEFT($K144,1)&lt;&gt;"✅"),COUNT($M$6:M143)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N144">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="145" ht="21" customHeight="1">
       <c r="A145" s="9">
@@ -9179,6 +10297,14 @@
         <f>IF($H145="","",IF($H145=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H145)=0,"🟡 ما انزلت بنودها",IF(ROUND($I145-$J145,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I145-$J145,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M145">
+        <f>IF(AND($H145&lt;&gt;"",$H145&lt;&gt;0,LEFT($K145,1)&lt;&gt;"✅"),COUNT($M$6:M144)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N145">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="146" ht="21" customHeight="1">
       <c r="A146" s="9">
@@ -9209,6 +10335,14 @@
         <f>IF($H146="","",IF($H146=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H146)=0,"🟡 ما انزلت بنودها",IF(ROUND($I146-$J146,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I146-$J146,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M146">
+        <f>IF(AND($H146&lt;&gt;"",$H146&lt;&gt;0,LEFT($K146,1)&lt;&gt;"✅"),COUNT($M$6:M145)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N146">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="147" ht="21" customHeight="1">
       <c r="A147" s="9">
@@ -9239,6 +10373,14 @@
         <f>IF($H147="","",IF($H147=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H147)=0,"🟡 ما انزلت بنودها",IF(ROUND($I147-$J147,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I147-$J147,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M147">
+        <f>IF(AND($H147&lt;&gt;"",$H147&lt;&gt;0,LEFT($K147,1)&lt;&gt;"✅"),COUNT($M$6:M146)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N147">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="148" ht="21" customHeight="1">
       <c r="A148" s="9">
@@ -9269,6 +10411,14 @@
         <f>IF($H148="","",IF($H148=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H148)=0,"🟡 ما انزلت بنودها",IF(ROUND($I148-$J148,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I148-$J148,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M148">
+        <f>IF(AND($H148&lt;&gt;"",$H148&lt;&gt;0,LEFT($K148,1)&lt;&gt;"✅"),COUNT($M$6:M147)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N148">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="149" ht="21" customHeight="1">
       <c r="A149" s="9">
@@ -9299,6 +10449,14 @@
         <f>IF($H149="","",IF($H149=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H149)=0,"🟡 ما انزلت بنودها",IF(ROUND($I149-$J149,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I149-$J149,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M149">
+        <f>IF(AND($H149&lt;&gt;"",$H149&lt;&gt;0,LEFT($K149,1)&lt;&gt;"✅"),COUNT($M$6:M148)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N149">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="150" ht="21" customHeight="1">
       <c r="A150" s="9">
@@ -9329,6 +10487,14 @@
         <f>IF($H150="","",IF($H150=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H150)=0,"🟡 ما انزلت بنودها",IF(ROUND($I150-$J150,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I150-$J150,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M150">
+        <f>IF(AND($H150&lt;&gt;"",$H150&lt;&gt;0,LEFT($K150,1)&lt;&gt;"✅"),COUNT($M$6:M149)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N150">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="151" ht="21" customHeight="1">
       <c r="A151" s="9">
@@ -9359,6 +10525,14 @@
         <f>IF($H151="","",IF($H151=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H151)=0,"🟡 ما انزلت بنودها",IF(ROUND($I151-$J151,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I151-$J151,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M151">
+        <f>IF(AND($H151&lt;&gt;"",$H151&lt;&gt;0,LEFT($K151,1)&lt;&gt;"✅"),COUNT($M$6:M150)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N151">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="152" ht="21" customHeight="1">
       <c r="A152" s="9">
@@ -9389,6 +10563,14 @@
         <f>IF($H152="","",IF($H152=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H152)=0,"🟡 ما انزلت بنودها",IF(ROUND($I152-$J152,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I152-$J152,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M152">
+        <f>IF(AND($H152&lt;&gt;"",$H152&lt;&gt;0,LEFT($K152,1)&lt;&gt;"✅"),COUNT($M$6:M151)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N152">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="153" ht="21" customHeight="1">
       <c r="A153" s="9">
@@ -9419,6 +10601,14 @@
         <f>IF($H153="","",IF($H153=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H153)=0,"🟡 ما انزلت بنودها",IF(ROUND($I153-$J153,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I153-$J153,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M153">
+        <f>IF(AND($H153&lt;&gt;"",$H153&lt;&gt;0,LEFT($K153,1)&lt;&gt;"✅"),COUNT($M$6:M152)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N153">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="154" ht="21" customHeight="1">
       <c r="A154" s="9">
@@ -9449,6 +10639,14 @@
         <f>IF($H154="","",IF($H154=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H154)=0,"🟡 ما انزلت بنودها",IF(ROUND($I154-$J154,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I154-$J154,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M154">
+        <f>IF(AND($H154&lt;&gt;"",$H154&lt;&gt;0,LEFT($K154,1)&lt;&gt;"✅"),COUNT($M$6:M153)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N154">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="155" ht="21" customHeight="1">
       <c r="A155" s="9">
@@ -9479,6 +10677,14 @@
         <f>IF($H155="","",IF($H155=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H155)=0,"🟡 ما انزلت بنودها",IF(ROUND($I155-$J155,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I155-$J155,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M155">
+        <f>IF(AND($H155&lt;&gt;"",$H155&lt;&gt;0,LEFT($K155,1)&lt;&gt;"✅"),COUNT($M$6:M154)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N155">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="156" ht="21" customHeight="1">
       <c r="A156" s="9">
@@ -9509,6 +10715,14 @@
         <f>IF($H156="","",IF($H156=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H156)=0,"🟡 ما انزلت بنودها",IF(ROUND($I156-$J156,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I156-$J156,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M156">
+        <f>IF(AND($H156&lt;&gt;"",$H156&lt;&gt;0,LEFT($K156,1)&lt;&gt;"✅"),COUNT($M$6:M155)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N156">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="157" ht="21" customHeight="1">
       <c r="A157" s="9">
@@ -9539,6 +10753,14 @@
         <f>IF($H157="","",IF($H157=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H157)=0,"🟡 ما انزلت بنودها",IF(ROUND($I157-$J157,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I157-$J157,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M157">
+        <f>IF(AND($H157&lt;&gt;"",$H157&lt;&gt;0,LEFT($K157,1)&lt;&gt;"✅"),COUNT($M$6:M156)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N157">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="158" ht="21" customHeight="1">
       <c r="A158" s="9">
@@ -9569,6 +10791,14 @@
         <f>IF($H158="","",IF($H158=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H158)=0,"🟡 ما انزلت بنودها",IF(ROUND($I158-$J158,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I158-$J158,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M158">
+        <f>IF(AND($H158&lt;&gt;"",$H158&lt;&gt;0,LEFT($K158,1)&lt;&gt;"✅"),COUNT($M$6:M157)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N158">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="159" ht="21" customHeight="1">
       <c r="A159" s="9">
@@ -9599,6 +10829,14 @@
         <f>IF($H159="","",IF($H159=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H159)=0,"🟡 ما انزلت بنودها",IF(ROUND($I159-$J159,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I159-$J159,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M159">
+        <f>IF(AND($H159&lt;&gt;"",$H159&lt;&gt;0,LEFT($K159,1)&lt;&gt;"✅"),COUNT($M$6:M158)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N159">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="160" ht="21" customHeight="1">
       <c r="A160" s="9">
@@ -9629,6 +10867,14 @@
         <f>IF($H160="","",IF($H160=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H160)=0,"🟡 ما انزلت بنودها",IF(ROUND($I160-$J160,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I160-$J160,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M160">
+        <f>IF(AND($H160&lt;&gt;"",$H160&lt;&gt;0,LEFT($K160,1)&lt;&gt;"✅"),COUNT($M$6:M159)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N160">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="161" ht="21" customHeight="1">
       <c r="A161" s="9">
@@ -9659,6 +10905,14 @@
         <f>IF($H161="","",IF($H161=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H161)=0,"🟡 ما انزلت بنودها",IF(ROUND($I161-$J161,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I161-$J161,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M161">
+        <f>IF(AND($H161&lt;&gt;"",$H161&lt;&gt;0,LEFT($K161,1)&lt;&gt;"✅"),COUNT($M$6:M160)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N161">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="162" ht="21" customHeight="1">
       <c r="A162" s="9">
@@ -9689,6 +10943,14 @@
         <f>IF($H162="","",IF($H162=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H162)=0,"🟡 ما انزلت بنودها",IF(ROUND($I162-$J162,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I162-$J162,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M162">
+        <f>IF(AND($H162&lt;&gt;"",$H162&lt;&gt;0,LEFT($K162,1)&lt;&gt;"✅"),COUNT($M$6:M161)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N162">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="163" ht="21" customHeight="1">
       <c r="A163" s="9">
@@ -9719,6 +10981,14 @@
         <f>IF($H163="","",IF($H163=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H163)=0,"🟡 ما انزلت بنودها",IF(ROUND($I163-$J163,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I163-$J163,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M163">
+        <f>IF(AND($H163&lt;&gt;"",$H163&lt;&gt;0,LEFT($K163,1)&lt;&gt;"✅"),COUNT($M$6:M162)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N163">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="164" ht="21" customHeight="1">
       <c r="A164" s="9">
@@ -9749,6 +11019,14 @@
         <f>IF($H164="","",IF($H164=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H164)=0,"🟡 ما انزلت بنودها",IF(ROUND($I164-$J164,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I164-$J164,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M164">
+        <f>IF(AND($H164&lt;&gt;"",$H164&lt;&gt;0,LEFT($K164,1)&lt;&gt;"✅"),COUNT($M$6:M163)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N164">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="165" ht="21" customHeight="1">
       <c r="A165" s="9">
@@ -9779,6 +11057,14 @@
         <f>IF($H165="","",IF($H165=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H165)=0,"🟡 ما انزلت بنودها",IF(ROUND($I165-$J165,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I165-$J165,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M165">
+        <f>IF(AND($H165&lt;&gt;"",$H165&lt;&gt;0,LEFT($K165,1)&lt;&gt;"✅"),COUNT($M$6:M164)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N165">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="166" ht="21" customHeight="1">
       <c r="A166" s="9">
@@ -9809,6 +11095,14 @@
         <f>IF($H166="","",IF($H166=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H166)=0,"🟡 ما انزلت بنودها",IF(ROUND($I166-$J166,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I166-$J166,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M166">
+        <f>IF(AND($H166&lt;&gt;"",$H166&lt;&gt;0,LEFT($K166,1)&lt;&gt;"✅"),COUNT($M$6:M165)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N166">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="167" ht="21" customHeight="1">
       <c r="A167" s="9">
@@ -9839,6 +11133,14 @@
         <f>IF($H167="","",IF($H167=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H167)=0,"🟡 ما انزلت بنودها",IF(ROUND($I167-$J167,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I167-$J167,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M167">
+        <f>IF(AND($H167&lt;&gt;"",$H167&lt;&gt;0,LEFT($K167,1)&lt;&gt;"✅"),COUNT($M$6:M166)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N167">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="168" ht="21" customHeight="1">
       <c r="A168" s="9">
@@ -9869,6 +11171,14 @@
         <f>IF($H168="","",IF($H168=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H168)=0,"🟡 ما انزلت بنودها",IF(ROUND($I168-$J168,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I168-$J168,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M168">
+        <f>IF(AND($H168&lt;&gt;"",$H168&lt;&gt;0,LEFT($K168,1)&lt;&gt;"✅"),COUNT($M$6:M167)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N168">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="169" ht="21" customHeight="1">
       <c r="A169" s="9">
@@ -9899,6 +11209,14 @@
         <f>IF($H169="","",IF($H169=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H169)=0,"🟡 ما انزلت بنودها",IF(ROUND($I169-$J169,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I169-$J169,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M169">
+        <f>IF(AND($H169&lt;&gt;"",$H169&lt;&gt;0,LEFT($K169,1)&lt;&gt;"✅"),COUNT($M$6:M168)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N169">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="170" ht="21" customHeight="1">
       <c r="A170" s="9">
@@ -9929,6 +11247,14 @@
         <f>IF($H170="","",IF($H170=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H170)=0,"🟡 ما انزلت بنودها",IF(ROUND($I170-$J170,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I170-$J170,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M170">
+        <f>IF(AND($H170&lt;&gt;"",$H170&lt;&gt;0,LEFT($K170,1)&lt;&gt;"✅"),COUNT($M$6:M169)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N170">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="171" ht="21" customHeight="1">
       <c r="A171" s="9">
@@ -9959,6 +11285,14 @@
         <f>IF($H171="","",IF($H171=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H171)=0,"🟡 ما انزلت بنودها",IF(ROUND($I171-$J171,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I171-$J171,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M171">
+        <f>IF(AND($H171&lt;&gt;"",$H171&lt;&gt;0,LEFT($K171,1)&lt;&gt;"✅"),COUNT($M$6:M170)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N171">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="172" ht="21" customHeight="1">
       <c r="A172" s="9">
@@ -9989,6 +11323,14 @@
         <f>IF($H172="","",IF($H172=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H172)=0,"🟡 ما انزلت بنودها",IF(ROUND($I172-$J172,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I172-$J172,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M172">
+        <f>IF(AND($H172&lt;&gt;"",$H172&lt;&gt;0,LEFT($K172,1)&lt;&gt;"✅"),COUNT($M$6:M171)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N172">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="173" ht="21" customHeight="1">
       <c r="A173" s="9">
@@ -10019,6 +11361,14 @@
         <f>IF($H173="","",IF($H173=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H173)=0,"🟡 ما انزلت بنودها",IF(ROUND($I173-$J173,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I173-$J173,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M173">
+        <f>IF(AND($H173&lt;&gt;"",$H173&lt;&gt;0,LEFT($K173,1)&lt;&gt;"✅"),COUNT($M$6:M172)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N173">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="174" ht="21" customHeight="1">
       <c r="A174" s="9">
@@ -10049,6 +11399,14 @@
         <f>IF($H174="","",IF($H174=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H174)=0,"🟡 ما انزلت بنودها",IF(ROUND($I174-$J174,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I174-$J174,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M174">
+        <f>IF(AND($H174&lt;&gt;"",$H174&lt;&gt;0,LEFT($K174,1)&lt;&gt;"✅"),COUNT($M$6:M173)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N174">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="175" ht="21" customHeight="1">
       <c r="A175" s="9">
@@ -10079,6 +11437,14 @@
         <f>IF($H175="","",IF($H175=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H175)=0,"🟡 ما انزلت بنودها",IF(ROUND($I175-$J175,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I175-$J175,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M175">
+        <f>IF(AND($H175&lt;&gt;"",$H175&lt;&gt;0,LEFT($K175,1)&lt;&gt;"✅"),COUNT($M$6:M174)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N175">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="176" ht="21" customHeight="1">
       <c r="A176" s="9">
@@ -10109,6 +11475,14 @@
         <f>IF($H176="","",IF($H176=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H176)=0,"🟡 ما انزلت بنودها",IF(ROUND($I176-$J176,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I176-$J176,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M176">
+        <f>IF(AND($H176&lt;&gt;"",$H176&lt;&gt;0,LEFT($K176,1)&lt;&gt;"✅"),COUNT($M$6:M175)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N176">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="177" ht="21" customHeight="1">
       <c r="A177" s="9">
@@ -10139,6 +11513,14 @@
         <f>IF($H177="","",IF($H177=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H177)=0,"🟡 ما انزلت بنودها",IF(ROUND($I177-$J177,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I177-$J177,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M177">
+        <f>IF(AND($H177&lt;&gt;"",$H177&lt;&gt;0,LEFT($K177,1)&lt;&gt;"✅"),COUNT($M$6:M176)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N177">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="178" ht="21" customHeight="1">
       <c r="A178" s="9">
@@ -10169,6 +11551,14 @@
         <f>IF($H178="","",IF($H178=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H178)=0,"🟡 ما انزلت بنودها",IF(ROUND($I178-$J178,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I178-$J178,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M178">
+        <f>IF(AND($H178&lt;&gt;"",$H178&lt;&gt;0,LEFT($K178,1)&lt;&gt;"✅"),COUNT($M$6:M177)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N178">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="179" ht="21" customHeight="1">
       <c r="A179" s="9">
@@ -10199,6 +11589,14 @@
         <f>IF($H179="","",IF($H179=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H179)=0,"🟡 ما انزلت بنودها",IF(ROUND($I179-$J179,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I179-$J179,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M179">
+        <f>IF(AND($H179&lt;&gt;"",$H179&lt;&gt;0,LEFT($K179,1)&lt;&gt;"✅"),COUNT($M$6:M178)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N179">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="180" ht="21" customHeight="1">
       <c r="A180" s="9">
@@ -10229,6 +11627,14 @@
         <f>IF($H180="","",IF($H180=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H180)=0,"🟡 ما انزلت بنودها",IF(ROUND($I180-$J180,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I180-$J180,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M180">
+        <f>IF(AND($H180&lt;&gt;"",$H180&lt;&gt;0,LEFT($K180,1)&lt;&gt;"✅"),COUNT($M$6:M179)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N180">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="181" ht="21" customHeight="1">
       <c r="A181" s="9">
@@ -10259,6 +11665,14 @@
         <f>IF($H181="","",IF($H181=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H181)=0,"🟡 ما انزلت بنودها",IF(ROUND($I181-$J181,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I181-$J181,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M181">
+        <f>IF(AND($H181&lt;&gt;"",$H181&lt;&gt;0,LEFT($K181,1)&lt;&gt;"✅"),COUNT($M$6:M180)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N181">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="182" ht="21" customHeight="1">
       <c r="A182" s="9">
@@ -10289,6 +11703,14 @@
         <f>IF($H182="","",IF($H182=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H182)=0,"🟡 ما انزلت بنودها",IF(ROUND($I182-$J182,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I182-$J182,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M182">
+        <f>IF(AND($H182&lt;&gt;"",$H182&lt;&gt;0,LEFT($K182,1)&lt;&gt;"✅"),COUNT($M$6:M181)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N182">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="183" ht="21" customHeight="1">
       <c r="A183" s="9">
@@ -10319,6 +11741,14 @@
         <f>IF($H183="","",IF($H183=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H183)=0,"🟡 ما انزلت بنودها",IF(ROUND($I183-$J183,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I183-$J183,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M183">
+        <f>IF(AND($H183&lt;&gt;"",$H183&lt;&gt;0,LEFT($K183,1)&lt;&gt;"✅"),COUNT($M$6:M182)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N183">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="184" ht="21" customHeight="1">
       <c r="A184" s="9">
@@ -10349,6 +11779,14 @@
         <f>IF($H184="","",IF($H184=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H184)=0,"🟡 ما انزلت بنودها",IF(ROUND($I184-$J184,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I184-$J184,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M184">
+        <f>IF(AND($H184&lt;&gt;"",$H184&lt;&gt;0,LEFT($K184,1)&lt;&gt;"✅"),COUNT($M$6:M183)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N184">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="185" ht="21" customHeight="1">
       <c r="A185" s="9">
@@ -10379,6 +11817,14 @@
         <f>IF($H185="","",IF($H185=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H185)=0,"🟡 ما انزلت بنودها",IF(ROUND($I185-$J185,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I185-$J185,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M185">
+        <f>IF(AND($H185&lt;&gt;"",$H185&lt;&gt;0,LEFT($K185,1)&lt;&gt;"✅"),COUNT($M$6:M184)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N185">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="186" ht="21" customHeight="1">
       <c r="A186" s="9">
@@ -10409,6 +11855,14 @@
         <f>IF($H186="","",IF($H186=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H186)=0,"🟡 ما انزلت بنودها",IF(ROUND($I186-$J186,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I186-$J186,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M186">
+        <f>IF(AND($H186&lt;&gt;"",$H186&lt;&gt;0,LEFT($K186,1)&lt;&gt;"✅"),COUNT($M$6:M185)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N186">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="187" ht="21" customHeight="1">
       <c r="A187" s="9">
@@ -10439,6 +11893,14 @@
         <f>IF($H187="","",IF($H187=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H187)=0,"🟡 ما انزلت بنودها",IF(ROUND($I187-$J187,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I187-$J187,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M187">
+        <f>IF(AND($H187&lt;&gt;"",$H187&lt;&gt;0,LEFT($K187,1)&lt;&gt;"✅"),COUNT($M$6:M186)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N187">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="188" ht="21" customHeight="1">
       <c r="A188" s="9">
@@ -10469,6 +11931,14 @@
         <f>IF($H188="","",IF($H188=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H188)=0,"🟡 ما انزلت بنودها",IF(ROUND($I188-$J188,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I188-$J188,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M188">
+        <f>IF(AND($H188&lt;&gt;"",$H188&lt;&gt;0,LEFT($K188,1)&lt;&gt;"✅"),COUNT($M$6:M187)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N188">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="189" ht="21" customHeight="1">
       <c r="A189" s="9">
@@ -10499,6 +11969,14 @@
         <f>IF($H189="","",IF($H189=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H189)=0,"🟡 ما انزلت بنودها",IF(ROUND($I189-$J189,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I189-$J189,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M189">
+        <f>IF(AND($H189&lt;&gt;"",$H189&lt;&gt;0,LEFT($K189,1)&lt;&gt;"✅"),COUNT($M$6:M188)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N189">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="190" ht="21" customHeight="1">
       <c r="A190" s="9">
@@ -10529,6 +12007,14 @@
         <f>IF($H190="","",IF($H190=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H190)=0,"🟡 ما انزلت بنودها",IF(ROUND($I190-$J190,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I190-$J190,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M190">
+        <f>IF(AND($H190&lt;&gt;"",$H190&lt;&gt;0,LEFT($K190,1)&lt;&gt;"✅"),COUNT($M$6:M189)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N190">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="191" ht="21" customHeight="1">
       <c r="A191" s="9">
@@ -10559,6 +12045,14 @@
         <f>IF($H191="","",IF($H191=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H191)=0,"🟡 ما انزلت بنودها",IF(ROUND($I191-$J191,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I191-$J191,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M191">
+        <f>IF(AND($H191&lt;&gt;"",$H191&lt;&gt;0,LEFT($K191,1)&lt;&gt;"✅"),COUNT($M$6:M190)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N191">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="192" ht="21" customHeight="1">
       <c r="A192" s="9">
@@ -10589,6 +12083,14 @@
         <f>IF($H192="","",IF($H192=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H192)=0,"🟡 ما انزلت بنودها",IF(ROUND($I192-$J192,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I192-$J192,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M192">
+        <f>IF(AND($H192&lt;&gt;"",$H192&lt;&gt;0,LEFT($K192,1)&lt;&gt;"✅"),COUNT($M$6:M191)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N192">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="193" ht="21" customHeight="1">
       <c r="A193" s="9">
@@ -10619,6 +12121,14 @@
         <f>IF($H193="","",IF($H193=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H193)=0,"🟡 ما انزلت بنودها",IF(ROUND($I193-$J193,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I193-$J193,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M193">
+        <f>IF(AND($H193&lt;&gt;"",$H193&lt;&gt;0,LEFT($K193,1)&lt;&gt;"✅"),COUNT($M$6:M192)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N193">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="194" ht="21" customHeight="1">
       <c r="A194" s="9">
@@ -10649,6 +12159,14 @@
         <f>IF($H194="","",IF($H194=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H194)=0,"🟡 ما انزلت بنودها",IF(ROUND($I194-$J194,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I194-$J194,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M194">
+        <f>IF(AND($H194&lt;&gt;"",$H194&lt;&gt;0,LEFT($K194,1)&lt;&gt;"✅"),COUNT($M$6:M193)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N194">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="195" ht="21" customHeight="1">
       <c r="A195" s="9">
@@ -10679,6 +12197,14 @@
         <f>IF($H195="","",IF($H195=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H195)=0,"🟡 ما انزلت بنودها",IF(ROUND($I195-$J195,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I195-$J195,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M195">
+        <f>IF(AND($H195&lt;&gt;"",$H195&lt;&gt;0,LEFT($K195,1)&lt;&gt;"✅"),COUNT($M$6:M194)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N195">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="196" ht="21" customHeight="1">
       <c r="A196" s="9">
@@ -10709,6 +12235,14 @@
         <f>IF($H196="","",IF($H196=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H196)=0,"🟡 ما انزلت بنودها",IF(ROUND($I196-$J196,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I196-$J196,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M196">
+        <f>IF(AND($H196&lt;&gt;"",$H196&lt;&gt;0,LEFT($K196,1)&lt;&gt;"✅"),COUNT($M$6:M195)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N196">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="197" ht="21" customHeight="1">
       <c r="A197" s="9">
@@ -10739,6 +12273,14 @@
         <f>IF($H197="","",IF($H197=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H197)=0,"🟡 ما انزلت بنودها",IF(ROUND($I197-$J197,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I197-$J197,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M197">
+        <f>IF(AND($H197&lt;&gt;"",$H197&lt;&gt;0,LEFT($K197,1)&lt;&gt;"✅"),COUNT($M$6:M196)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N197">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="198" ht="21" customHeight="1">
       <c r="A198" s="9">
@@ -10769,6 +12311,14 @@
         <f>IF($H198="","",IF($H198=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H198)=0,"🟡 ما انزلت بنودها",IF(ROUND($I198-$J198,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I198-$J198,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M198">
+        <f>IF(AND($H198&lt;&gt;"",$H198&lt;&gt;0,LEFT($K198,1)&lt;&gt;"✅"),COUNT($M$6:M197)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N198">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="199" ht="21" customHeight="1">
       <c r="A199" s="9">
@@ -10799,6 +12349,14 @@
         <f>IF($H199="","",IF($H199=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H199)=0,"🟡 ما انزلت بنودها",IF(ROUND($I199-$J199,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I199-$J199,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M199">
+        <f>IF(AND($H199&lt;&gt;"",$H199&lt;&gt;0,LEFT($K199,1)&lt;&gt;"✅"),COUNT($M$6:M198)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N199">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="200" ht="21" customHeight="1">
       <c r="A200" s="9">
@@ -10829,6 +12387,14 @@
         <f>IF($H200="","",IF($H200=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H200)=0,"🟡 ما انزلت بنودها",IF(ROUND($I200-$J200,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I200-$J200,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M200">
+        <f>IF(AND($H200&lt;&gt;"",$H200&lt;&gt;0,LEFT($K200,1)&lt;&gt;"✅"),COUNT($M$6:M199)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N200">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="201" ht="21" customHeight="1">
       <c r="A201" s="9">
@@ -10859,6 +12425,14 @@
         <f>IF($H201="","",IF($H201=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H201)=0,"🟡 ما انزلت بنودها",IF(ROUND($I201-$J201,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I201-$J201,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M201">
+        <f>IF(AND($H201&lt;&gt;"",$H201&lt;&gt;0,LEFT($K201,1)&lt;&gt;"✅"),COUNT($M$6:M200)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N201">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="202" ht="21" customHeight="1">
       <c r="A202" s="9">
@@ -10889,6 +12463,14 @@
         <f>IF($H202="","",IF($H202=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H202)=0,"🟡 ما انزلت بنودها",IF(ROUND($I202-$J202,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I202-$J202,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M202">
+        <f>IF(AND($H202&lt;&gt;"",$H202&lt;&gt;0,LEFT($K202,1)&lt;&gt;"✅"),COUNT($M$6:M201)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N202">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="203" ht="21" customHeight="1">
       <c r="A203" s="9">
@@ -10919,6 +12501,14 @@
         <f>IF($H203="","",IF($H203=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H203)=0,"🟡 ما انزلت بنودها",IF(ROUND($I203-$J203,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I203-$J203,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M203">
+        <f>IF(AND($H203&lt;&gt;"",$H203&lt;&gt;0,LEFT($K203,1)&lt;&gt;"✅"),COUNT($M$6:M202)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N203">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="204" ht="21" customHeight="1">
       <c r="A204" s="9">
@@ -10949,6 +12539,14 @@
         <f>IF($H204="","",IF($H204=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H204)=0,"🟡 ما انزلت بنودها",IF(ROUND($I204-$J204,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I204-$J204,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M204">
+        <f>IF(AND($H204&lt;&gt;"",$H204&lt;&gt;0,LEFT($K204,1)&lt;&gt;"✅"),COUNT($M$6:M203)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N204">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="205" ht="21" customHeight="1">
       <c r="A205" s="9">
@@ -10979,6 +12577,14 @@
         <f>IF($H205="","",IF($H205=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H205)=0,"🟡 ما انزلت بنودها",IF(ROUND($I205-$J205,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I205-$J205,"0.000")))))</f>
         <v/>
       </c>
+      <c r="M205">
+        <f>IF(AND($H205&lt;&gt;"",$H205&lt;&gt;0,LEFT($K205,1)&lt;&gt;"✅"),COUNT($M$6:M204)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N205">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="206" ht="21" customHeight="1">
       <c r="A206" s="9">
@@ -11007,6 +12613,14 @@
       </c>
       <c r="K206" s="15">
         <f>IF($H206="","",IF($H206=0,"⛔ اكتب رقم الفاتورة",IF(COUNTIF($B$7:$B$606,$H206)=0,"🟡 ما انزلت بنودها",IF(ROUND($I206-$J206,3)=0,"✅ خلصت","⛔ فرق "&amp;TEXT($I206-$J206,"0.000")))))</f>
+        <v/>
+      </c>
+      <c r="M206">
+        <f>IF(AND($H206&lt;&gt;"",$H206&lt;&gt;0,LEFT($K206,1)&lt;&gt;"✅"),COUNT($M$6:M205)+1,"")</f>
+        <v/>
+      </c>
+      <c r="N206">
+        <f>IFERROR(INDEX($H$7:$H$206,MATCH(ROW()-6,$M$7:$M$206,0)),"")</f>
         <v/>
       </c>
     </row>
@@ -16672,8 +18286,8 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="B7:B606" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>='الفواتير'!$D$7:$D$206</formula1>
+    <dataValidation sqref="B7:B606" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="رقم غير موجود بالقائمة" error="اختر رقم فاتورة يدوية لسا ما خلصت من القائمة." type="list">
+      <formula1>=فواتير_مفتوحة</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
